--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.2%</t>
+          <t>-562.3%</t>
         </is>
       </c>
     </row>
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-231.6%</t>
+          <t>-231.7%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.1%</t>
+          <t>-32.2%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.2%</t>
+          <t>-165.3%</t>
         </is>
       </c>
     </row>
@@ -44095,7 +44095,7 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074623</v>
+        <v>3.251475576074624</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
@@ -44118,7 +44118,7 @@
         <v>45313</v>
       </c>
       <c r="B1851" t="n">
-        <v>3.233800325911639</v>
+        <v>3.23380032591164</v>
       </c>
       <c r="C1851" t="n">
         <v>3.110004566748314</v>
@@ -44141,7 +44141,7 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
@@ -44164,7 +44164,7 @@
         <v>45315</v>
       </c>
       <c r="B1853" t="n">
-        <v>3.231167537416045</v>
+        <v>3.231167537416046</v>
       </c>
       <c r="C1853" t="n">
         <v>3.13844160689565</v>
@@ -44187,7 +44187,7 @@
         <v>45316</v>
       </c>
       <c r="B1854" t="n">
-        <v>3.235981977382329</v>
+        <v>3.23598197738233</v>
       </c>
       <c r="C1854" t="n">
         <v>3.139547998939383</v>
@@ -44210,7 +44210,7 @@
         <v>45317</v>
       </c>
       <c r="B1855" t="n">
-        <v>3.278199702495499</v>
+        <v>3.2781997024955</v>
       </c>
       <c r="C1855" t="n">
         <v>3.138090537752246</v>
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347054</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44256,7 +44256,7 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130016</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
@@ -44279,7 +44279,7 @@
         <v>45320</v>
       </c>
       <c r="B1858" t="n">
-        <v>3.315884374178243</v>
+        <v>3.315884374178244</v>
       </c>
       <c r="C1858" t="n">
         <v>3.137738646563379</v>
@@ -44302,7 +44302,7 @@
         <v>45321</v>
       </c>
       <c r="B1859" t="n">
-        <v>3.305316798207812</v>
+        <v>3.305316798207813</v>
       </c>
       <c r="C1859" t="n">
         <v>3.124071534030784</v>
@@ -44325,7 +44325,7 @@
         <v>45322</v>
       </c>
       <c r="B1860" t="n">
-        <v>3.28461951331098</v>
+        <v>3.284619513310981</v>
       </c>
       <c r="C1860" t="n">
         <v>3.112356309032875</v>
@@ -44348,7 +44348,7 @@
         <v>45323</v>
       </c>
       <c r="B1861" t="n">
-        <v>3.305849539006531</v>
+        <v>3.305849539006532</v>
       </c>
       <c r="C1861" t="n">
         <v>3.11093690068884</v>
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309422</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970902</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.30081581833052</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191735</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097819</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199285</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969592</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44601,7 +44601,7 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297749</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
@@ -44647,7 +44647,7 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737169</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341312</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776676</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611694</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199884</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910626</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078593</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880265</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44877,7 +44877,7 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860579</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767393</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792538</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44946,7 +44946,7 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628916</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240573</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085276</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282097</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116212</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081563</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425324</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702408</v>
+        <v>3.747699084702409</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906224</v>
+        <v>3.766313503906225</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
@@ -45176,7 +45176,7 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781945</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
@@ -45222,7 +45222,7 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.78930753648777</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
@@ -45245,7 +45245,7 @@
         <v>45362</v>
       </c>
       <c r="B1900" t="n">
-        <v>3.833249172309722</v>
+        <v>3.833249172309724</v>
       </c>
       <c r="C1900" t="n">
         <v>3.148222793893841</v>
@@ -45268,7 +45268,7 @@
         <v>45363</v>
       </c>
       <c r="B1901" t="n">
-        <v>3.839370871858726</v>
+        <v>3.839370871858728</v>
       </c>
       <c r="C1901" t="n">
         <v>3.148566417781682</v>
@@ -45291,7 +45291,7 @@
         <v>45364</v>
       </c>
       <c r="B1902" t="n">
-        <v>3.856158176096471</v>
+        <v>3.856158176096473</v>
       </c>
       <c r="C1902" t="n">
         <v>3.147933239002439</v>
@@ -45314,7 +45314,7 @@
         <v>45365</v>
       </c>
       <c r="B1903" t="n">
-        <v>3.787326853761805</v>
+        <v>3.787326853761807</v>
       </c>
       <c r="C1903" t="n">
         <v>3.155857667840292</v>
@@ -45337,7 +45337,7 @@
         <v>45366</v>
       </c>
       <c r="B1904" t="n">
-        <v>3.801633547255783</v>
+        <v>3.801633547255785</v>
       </c>
       <c r="C1904" t="n">
         <v>3.152965457527332</v>
@@ -45360,7 +45360,7 @@
         <v>45367</v>
       </c>
       <c r="B1905" t="n">
-        <v>3.763178672860423</v>
+        <v>3.763178672860425</v>
       </c>
       <c r="C1905" t="n">
         <v>3.14833294427436</v>
@@ -45383,7 +45383,7 @@
         <v>45368</v>
       </c>
       <c r="B1906" t="n">
-        <v>3.784715218575948</v>
+        <v>3.78471521857595</v>
       </c>
       <c r="C1906" t="n">
         <v>3.151148004961996</v>
@@ -45406,7 +45406,7 @@
         <v>45369</v>
       </c>
       <c r="B1907" t="n">
-        <v>3.753878996430983</v>
+        <v>3.753878996430985</v>
       </c>
       <c r="C1907" t="n">
         <v>3.164054346185655</v>
@@ -45429,7 +45429,7 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.69292828007764</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
@@ -45452,7 +45452,7 @@
         <v>45371</v>
       </c>
       <c r="B1909" t="n">
-        <v>3.770419008457898</v>
+        <v>3.7704190084579</v>
       </c>
       <c r="C1909" t="n">
         <v>3.084622758463523</v>
@@ -45475,7 +45475,7 @@
         <v>45372</v>
       </c>
       <c r="B1910" t="n">
-        <v>3.760330111180807</v>
+        <v>3.760330111180808</v>
       </c>
       <c r="C1910" t="n">
         <v>3.088001770449517</v>
@@ -45498,7 +45498,7 @@
         <v>45373</v>
       </c>
       <c r="B1911" t="n">
-        <v>3.723562653879199</v>
+        <v>3.723562653879201</v>
       </c>
       <c r="C1911" t="n">
         <v>3.079287784196039</v>
@@ -45521,7 +45521,7 @@
         <v>45374</v>
       </c>
       <c r="B1912" t="n">
-        <v>3.729966140568103</v>
+        <v>3.729966140568105</v>
       </c>
       <c r="C1912" t="n">
         <v>3.072327172100946</v>
@@ -45544,7 +45544,7 @@
         <v>45375</v>
       </c>
       <c r="B1913" t="n">
-        <v>3.782918957963414</v>
+        <v>3.782918957963416</v>
       </c>
       <c r="C1913" t="n">
         <v>3.086789526482089</v>
@@ -45567,7 +45567,7 @@
         <v>45376</v>
       </c>
       <c r="B1914" t="n">
-        <v>3.82854791119281</v>
+        <v>3.828547911192812</v>
       </c>
       <c r="C1914" t="n">
         <v>3.081321646941284</v>
@@ -45590,7 +45590,7 @@
         <v>45377</v>
       </c>
       <c r="B1915" t="n">
-        <v>3.82804935326204</v>
+        <v>3.828049353262042</v>
       </c>
       <c r="C1915" t="n">
         <v>3.078819740951861</v>
@@ -45613,7 +45613,7 @@
         <v>45378</v>
       </c>
       <c r="B1916" t="n">
-        <v>3.812450103389902</v>
+        <v>3.812450103389904</v>
       </c>
       <c r="C1916" t="n">
         <v>3.086520719189187</v>
@@ -45636,7 +45636,7 @@
         <v>45379</v>
       </c>
       <c r="B1917" t="n">
-        <v>3.748324832788088</v>
+        <v>3.748324832788089</v>
       </c>
       <c r="C1917" t="n">
         <v>3.082301427536237</v>
@@ -45659,7 +45659,7 @@
         <v>45380</v>
       </c>
       <c r="B1918" t="n">
-        <v>3.82430765752752</v>
+        <v>3.824307657527521</v>
       </c>
       <c r="C1918" t="n">
         <v>3.084425741456253</v>
@@ -45682,7 +45682,7 @@
         <v>45381</v>
       </c>
       <c r="B1919" t="n">
-        <v>3.826351398749178</v>
+        <v>3.82635139874918</v>
       </c>
       <c r="C1919" t="n">
         <v>3.077167816439955</v>
@@ -45705,7 +45705,7 @@
         <v>45382</v>
       </c>
       <c r="B1920" t="n">
-        <v>3.835954411481492</v>
+        <v>3.835954411481493</v>
       </c>
       <c r="C1920" t="n">
         <v>3.080766939960604</v>
@@ -45728,7 +45728,7 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862981</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
@@ -45751,7 +45751,7 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102775</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
@@ -45774,7 +45774,7 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353068</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
@@ -45797,7 +45797,7 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544777</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
@@ -45820,7 +45820,7 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712288</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
@@ -45843,7 +45843,7 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837679</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
@@ -45866,7 +45866,7 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.82232342234996</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
@@ -45889,7 +45889,7 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972333</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
@@ -45912,7 +45912,7 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145933</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
@@ -45935,7 +45935,7 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009945</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
@@ -45958,7 +45958,7 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966253</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
@@ -45981,7 +45981,7 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046989</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
@@ -46004,7 +46004,7 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412095</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
@@ -46027,7 +46027,7 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144508</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.419341354637822</v>
+        <v>3.419341354637824</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.00641501863984</v>
+        <v>-4.007179916421292</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.445950350893795</v>
+        <v>1.445644391781214</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4016925369203111</v>
+        <v>-0.4024574347017633</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.807857260511291</v>
+        <v>2.80739832184242</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>65.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.4%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.4%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>56.8%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>55.7%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.6%</t>
+          <t>-78.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.4%</t>
+          <t>118.4%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,7 +949,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.3%</t>
+          <t>137.5%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-57.8%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.0%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>794.7%</t>
+          <t>755.8%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>0.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.3%</t>
+          <t>-540.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.7%</t>
+          <t>13.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.9%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-45.2%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>10.8%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.3%</t>
+          <t>-20.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-115.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-231.7%</t>
+          <t>-222.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.2%</t>
+          <t>-28.0%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.44</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>70.9%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.3%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-338.4%</t>
+          <t>-317.9%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-38.5%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-25.8%</t>
+          <t>-20.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.1%</t>
+          <t>34.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.8%</t>
+          <t>-158.2%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-264.2%</t>
+          <t>-242.0%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>51.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>51.4%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>62.8%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-203.4%</t>
+          <t>-191.1%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.3%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>42.7%</t>
+          <t>45.6%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>42.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.9%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-165.3%</t>
+          <t>-152.0%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7261617299540171</v>
+        <v>-0.5211698841151966</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.826259333655675</v>
+        <v>2.908256071991203</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.113125306410575</v>
+        <v>1.318117152249395</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.784955633797375</v>
+        <v>3.907950741300667</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9477836635121346</v>
+        <v>-0.7427918176733141</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.73747677683135</v>
+        <v>2.819473515166878</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.075599172723206</v>
+        <v>1.280591018562026</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.762306170183875</v>
+        <v>3.885301277687167</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.155787721865212</v>
+        <v>-0.9507958760263914</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.659167298044044</v>
+        <v>2.741164036379573</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.075599172723206</v>
+        <v>1.280591018562026</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.7671983147378</v>
+        <v>3.890193422241092</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.426187684574097</v>
+        <v>-1.221195838735277</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.546088769298478</v>
+        <v>2.628085507634006</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8051992100143204</v>
+        <v>1.010191055853141</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.600039793450457</v>
+        <v>3.723034900953749</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.765346062162619</v>
+        <v>-1.560354216323799</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.403509717569519</v>
+        <v>2.485506455905047</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4660408324257983</v>
+        <v>0.6710326782646185</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.389629066203793</v>
+        <v>3.512624173707085</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.093363283890098</v>
+        <v>-1.888371438051278</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.292641118617295</v>
+        <v>2.374637856952823</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1380236106983191</v>
+        <v>0.3430154565371394</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.213157022906074</v>
+        <v>3.336152130409366</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.586688155425276</v>
+        <v>-2.381696309586456</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.103409920411792</v>
+        <v>2.185406658747321</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.03303749645870041</v>
+        <v>0.2380293422975207</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.158264104770871</v>
+        <v>3.281259212274163</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.079073183449373</v>
+        <v>-2.874081337610553</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.907562301245886</v>
+        <v>1.989559039581414</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4593475315653963</v>
+        <v>-0.2543556857265761</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.863939480000145</v>
+        <v>2.986934587503437</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.464253574379446</v>
+        <v>-3.259261728540625</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.75203268368672</v>
+        <v>1.834029422022248</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4593475315653963</v>
+        <v>-0.2543556857265761</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.862482018813008</v>
+        <v>2.9854771263163</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.807936347606109</v>
+        <v>-3.602944501767288</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.616328697850671</v>
+        <v>1.6983254361862</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5672535835926145</v>
+        <v>-0.3622617377537943</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.799507511051294</v>
+        <v>2.922502618554586</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.165586697844457</v>
+        <v>-3.960594852005636</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.46937461641159</v>
+        <v>1.551371354747118</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9249039338309626</v>
+        <v>-0.7199120879921423</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.581023359564543</v>
+        <v>2.704018467067835</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.474820800840508</v>
+        <v>-4.269828955001687</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.347453901913429</v>
+        <v>1.429450640248957</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9249039338309626</v>
+        <v>-0.7199120879921423</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.582796286264802</v>
+        <v>2.705791393768094</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.906626593990295</v>
+        <v>-4.701634748151474</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.161064472120918</v>
+        <v>1.243061210456447</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.06132143027223</v>
+        <v>-0.8563295844334093</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.487278675867446</v>
+        <v>2.610273783370738</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.233059122858039</v>
+        <v>-5.028067277019218</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.018776235575912</v>
+        <v>1.10077297391144</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.143789680779378</v>
+        <v>-0.9387978349405575</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.426082500565248</v>
+        <v>2.54907760806854</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.568721770088492</v>
+        <v>-5.363729924249671</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8830917683396957</v>
+        <v>0.9650885066752242</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.143789680779378</v>
+        <v>-0.9387978349405575</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.424663092221214</v>
+        <v>2.547658199724506</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.932348014988805</v>
+        <v>-5.727356169149984</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7441288306138119</v>
+        <v>0.8261255689493403</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.242011317646504</v>
+        <v>-1.037019471807683</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.372217670335179</v>
+        <v>2.495212777838471</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.297475397627552</v>
+        <v>-6.092483551788731</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5973323925641445</v>
+        <v>0.679329130899673</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.538322101945516</v>
+        <v>-1.333330256106696</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.193685714761603</v>
+        <v>2.316680822264896</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.70606417480823</v>
+        <v>-6.501072328969409</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4326584257066326</v>
+        <v>0.5146551640421606</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.741919033287374</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.947293992467955</v>
+        <v>2.070289099971248</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.119046658949324</v>
+        <v>-6.914054813110503</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2626508645216554</v>
+        <v>0.3446476028571839</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.741919033287374</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.942479424939416</v>
+        <v>2.065474532442708</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.535438533236321</v>
+        <v>-7.3304466873975</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09408816541573373</v>
+        <v>0.1760849037512622</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.741919033287374</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.940473475548293</v>
+        <v>2.063468583051586</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.912115543766165</v>
+        <v>-7.707123697927345</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04632394812752505</v>
+        <v>0.0356727902080034</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.741919033287374</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.950732166216972</v>
+        <v>2.073727273720265</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.257990365750974</v>
+        <v>-8.052998519912153</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1885743117757532</v>
+        <v>-0.1065775734402248</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.741919033287374</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.946831731362668</v>
+        <v>2.06982683886596</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.570815164995953</v>
+        <v>-8.365823319157132</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3152993114187437</v>
+        <v>-0.2333025730832152</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.741919033287374</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.945236651417669</v>
+        <v>2.068231758920961</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.867476506806151</v>
+        <v>-8.66248466096733</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4301848722136148</v>
+        <v>-0.3481881338780863</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.810662169021253</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.907769745906549</v>
+        <v>2.030764853409842</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.300825614916386</v>
+        <v>-9.095833769077565</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6075508199921118</v>
+        <v>-0.5255540816565833</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.810662169021253</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.903743441372146</v>
+        <v>2.026738548875438</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.683827003659017</v>
+        <v>-9.478835157820196</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7608534768107482</v>
+        <v>-0.6788567384752202</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.810662169021253</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.903641340050562</v>
+        <v>2.026636447553854</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.05881232983029</v>
+        <v>-9.853820483991473</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9082760913078292</v>
+        <v>-0.8262793529723007</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.39063934103135</v>
+        <v>-2.18564749519253</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.681221660319226</v>
+        <v>1.804216767822518</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.4183426523343</v>
+        <v>-10.21335080649547</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.04673791701138</v>
+        <v>-0.9647411786758511</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.39063934103135</v>
+        <v>-2.18564749519253</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.686571963617276</v>
+        <v>1.809567071120568</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.74474268099931</v>
+        <v>-10.53975083516049</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.169381908520208</v>
+        <v>-1.087385170184679</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.717039369696364</v>
+        <v>-2.512047523857543</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.498647966375446</v>
+        <v>1.621643073878738</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.96389164907351</v>
+        <v>-10.75889980323469</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.253999745128117</v>
+        <v>-1.172003006792589</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.936188337770561</v>
+        <v>-2.731196491931741</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.370200336152696</v>
+        <v>1.493195443655988</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.9602007241171</v>
+        <v>-10.75520887827827</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.252523375145553</v>
+        <v>-1.170526636810024</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.936188337770561</v>
+        <v>-2.731196491931741</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.370200336152696</v>
+        <v>1.493195443655988</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.16445889944696</v>
+        <v>-10.95946705360814</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.328713448158856</v>
+        <v>-1.246716709823328</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.06382728238455</v>
+        <v>-2.85883543654573</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.299130166502945</v>
+        <v>1.422125274006237</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.38249667107814</v>
+        <v>-11.17750482523932</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.411446002326891</v>
+        <v>-1.329449263991363</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.238598050480449</v>
+        <v>-3.033606204641629</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.198750260129842</v>
+        <v>1.321745367633134</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.30902683941069</v>
+        <v>-11.10403499357187</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.366686368166491</v>
+        <v>-1.284689629830962</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.165128218813</v>
+        <v>-2.96013637297418</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.258203860623732</v>
+        <v>1.381198968127024</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.48415125679723</v>
+        <v>-11.27915941095841</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.422180914373591</v>
+        <v>-1.340184176038063</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.340252636199544</v>
+        <v>-3.135260790360724</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.167684430939323</v>
+        <v>1.290679538442615</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.71860335081172</v>
+        <v>-11.5136115049729</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.523180916880983</v>
+        <v>-1.441184178545454</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.340252636199544</v>
+        <v>-3.135260790360724</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.160465266037727</v>
+        <v>1.283460373541019</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.00640719534896</v>
+        <v>-11.80141534951014</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.644974645469854</v>
+        <v>-1.562977907134326</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.628056480736782</v>
+        <v>-3.423064634897962</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.9811107685414076</v>
+        <v>1.1041058760447</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.23623164251278</v>
+        <v>-12.03123979667396</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.735788634496829</v>
+        <v>-1.6537918961613</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.790704017806943</v>
+        <v>-3.585712171968123</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.8846380361378676</v>
+        <v>1.00763314364116</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.46826056224905</v>
+        <v>-12.26326871641023</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.825906473762218</v>
+        <v>-1.74390973542669</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.647724869156546</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8501241464539282</v>
+        <v>0.9731192539572202</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.41624504828023</v>
+        <v>-12.21125320244141</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.801109932488292</v>
+        <v>-1.719113194152764</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.647724869156546</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.854114482140329</v>
+        <v>0.977109589643621</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.55791689000435</v>
+        <v>-12.35292504416553</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.859253896076682</v>
+        <v>-1.777257157741154</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.647724869156546</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8526392552415873</v>
+        <v>0.9756343627448794</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.65682363046363</v>
+        <v>-12.45183178462481</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.883763182095521</v>
+        <v>-1.801766443759992</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.951623455454641</v>
+        <v>-3.746631609615821</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8083486211308948</v>
+        <v>0.9313437286341868</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.45767152322653</v>
+        <v>-12.25267967738771</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.817153472847364</v>
+        <v>-1.735156734511835</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.786300929504828</v>
+        <v>-3.581309083666008</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.8944910030540996</v>
+        <v>1.017486110557392</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.23182637050712</v>
+        <v>-12.0268345246683</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.71723633872339</v>
+        <v>-1.635239600387863</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.744374253917664</v>
+        <v>-3.539382408078844</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9292260814426063</v>
+        <v>1.052221188945898</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.94555155818442</v>
+        <v>-11.7405597123456</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.601587269238253</v>
+        <v>-1.519590530902726</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.744374253917664</v>
+        <v>-3.539382408078844</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9303652259986652</v>
+        <v>1.053360333501957</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.99844684622871</v>
+        <v>-11.79345500038989</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.62011161029386</v>
+        <v>-1.538114871958332</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.739418907829218</v>
+        <v>-3.534427061990398</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9359722078138408</v>
+        <v>1.058967315317133</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.71453811529996</v>
+        <v>-11.50954626946114</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.500814413683724</v>
+        <v>-1.418817675348197</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.739418907829218</v>
+        <v>-3.534427061990398</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9417059120524773</v>
+        <v>1.064701019555769</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.46755086510701</v>
+        <v>-11.26255901926819</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.411756776000408</v>
+        <v>-1.329760037664881</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.492431657636266</v>
+        <v>-3.287439811797446</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.080160999774383</v>
+        <v>1.203156107277675</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.20371399790294</v>
+        <v>-10.99872215206412</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.316105510431688</v>
+        <v>-1.234108772096161</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.492431657636266</v>
+        <v>-3.287439811797446</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.070277518461475</v>
+        <v>1.193272625964767</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.93647219703454</v>
+        <v>-10.73148035119572</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.211043350583703</v>
+        <v>-1.129046612248175</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.492431657636266</v>
+        <v>-3.287439811797446</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.068442957962102</v>
+        <v>1.191438065465394</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.66066303363406</v>
+        <v>-10.45567118779524</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.10102000019697</v>
+        <v>-1.019023261861442</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.403412349357533</v>
+        <v>-3.198420503518713</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.121554227955881</v>
+        <v>1.244549335459173</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.6367094926581</v>
+        <v>-10.43171764681928</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.090770077661093</v>
+        <v>-1.008773339325565</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.379458808381575</v>
+        <v>-3.174466962542755</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.136594858686949</v>
+        <v>1.259589966190241</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.3726495543353</v>
+        <v>-10.16765770849648</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.998406418493726</v>
+        <v>-0.9164096801581989</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.115398870058779</v>
+        <v>-2.910407024219959</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.281770505518875</v>
+        <v>1.404765613022167</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.665569930830465</v>
+        <v>-9.460578084991646</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7183616027520925</v>
+        <v>-0.6363648644165645</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.115398870058779</v>
+        <v>-2.910407024219959</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.278983471858574</v>
+        <v>1.401978579361866</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.625385632464274</v>
+        <v>-9.420393786625455</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7019442595177749</v>
+        <v>-0.6199475211822469</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.075214571692588</v>
+        <v>-2.870222725853768</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.30343767476613</v>
+        <v>1.426432782269422</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.54531583692647</v>
+        <v>-9.340323991087651</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6705495200818961</v>
+        <v>-0.5885527817463685</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.995144776154784</v>
+        <v>-2.790152930315964</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.350846373309569</v>
+        <v>1.473841480812861</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.31183461469687</v>
+        <v>-9.106842768858051</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5692326023522041</v>
+        <v>-0.4872358640166761</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.761663553925186</v>
+        <v>-2.556671708086366</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.498859535485181</v>
+        <v>1.621854642988473</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.132126084552997</v>
+        <v>-8.927134238714178</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5002414006076137</v>
+        <v>-0.4182446622720861</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.70449204976249</v>
+        <v>-2.49950020392367</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.530270227669839</v>
+        <v>1.653265335173131</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.99985061092211</v>
+        <v>-8.794858765083291</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4519637244082317</v>
+        <v>-0.3699669860727042</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.572216576131603</v>
+        <v>-2.367224730292783</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.605002998595398</v>
+        <v>1.72799810609869</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.809250936248956</v>
+        <v>-8.604259090410137</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3729087938513338</v>
+        <v>-0.2909120555158058</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.381616901458451</v>
+        <v>-2.176625055619631</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.722177864086926</v>
+        <v>1.845172971590218</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.560251137565375</v>
+        <v>-8.355259291726556</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2604025331542426</v>
+        <v>-0.178405794818715</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.381616901458451</v>
+        <v>-2.176625055619631</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.735084205310585</v>
+        <v>1.858079312813877</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.66584112733848</v>
+        <v>-8.460849281499661</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4306144586627028</v>
+        <v>-0.3486177203271752</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.487206891231555</v>
+        <v>-2.282215045392735</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.543754281847503</v>
+        <v>1.666749389350795</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.684576029457077</v>
+        <v>-8.479584183618257</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3895640776330556</v>
+        <v>-0.3075673392975276</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.487206891231555</v>
+        <v>-2.282215045392735</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.59229862372459</v>
+        <v>1.715293731227882</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.407837854786264</v>
+        <v>-8.202846008947445</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2754897957787357</v>
+        <v>-0.1934930574432081</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.305390230121629</v>
+        <v>-2.100398384282809</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70476763237654</v>
+        <v>1.827762739879832</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.280945448351194</v>
+        <v>-8.075953602512374</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2334468194581856</v>
+        <v>-0.151450081122658</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.97350597784774</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.772189089984104</v>
+        <v>1.895184197487396</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.237397041580502</v>
+        <v>-8.032405195741683</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2229880688450021</v>
+        <v>-0.1409913305094745</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.97350597784774</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.765228477889011</v>
+        <v>1.888223585392303</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.995248648126644</v>
+        <v>-7.790256802287825</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1116663570823158</v>
+        <v>-0.0296696187467882</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.97350597784774</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.779690832270154</v>
+        <v>1.902685939773446</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.932019276358296</v>
+        <v>-7.727027430519477</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.09184248791578176</v>
+        <v>-0.009845749580253749</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.97350597784774</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.774222952729349</v>
+        <v>1.897218060232641</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.74553158398129</v>
+        <v>-7.540539738142471</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.0197493169544023</v>
+        <v>0.06224742138112527</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.992010131309553</v>
+        <v>-1.787018285470733</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.883613662166129</v>
+        <v>2.006608769669421</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.724382385077846</v>
+        <v>-7.519390539239027</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.003588659155699503</v>
+        <v>0.0784080791798285</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.97086093240611</v>
+        <v>-1.76586908656729</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.904004159745521</v>
+        <v>2.026999267248813</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.480616943094402</v>
+        <v>-7.275625097255583</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08969822598472899</v>
+        <v>0.1716949643202565</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.97086093240611</v>
+        <v>-1.76586908656729</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.899784868092572</v>
+        <v>2.022779975595864</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.216588875901142</v>
+        <v>-7.011597030062322</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1974337667820492</v>
+        <v>0.2794305051175767</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.768995533590156</v>
+        <v>-1.564003687751336</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.023028421302159</v>
+        <v>2.146023528805452</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.966738481952067</v>
+        <v>-6.761746636113248</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2901159993453812</v>
+        <v>0.3721127376809088</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.768995533590156</v>
+        <v>-1.564003687751336</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.015770496285862</v>
+        <v>2.138765603789154</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.663170992948088</v>
+        <v>-6.458179147109269</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4151421184676214</v>
+        <v>0.497138856803149</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.768995533590156</v>
+        <v>-1.564003687751336</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.01936961980651</v>
+        <v>2.142364727309803</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.589691084096074</v>
+        <v>-6.384699238257255</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4578615880629808</v>
+        <v>0.5398583263985084</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.695515624738142</v>
+        <v>-1.490523778899322</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.076785071172273</v>
+        <v>2.199780178675565</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.364658084427251</v>
+        <v>-6.159666238588432</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5468952655468069</v>
+        <v>0.6288920038823345</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.470482625069319</v>
+        <v>-1.265490779230499</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.210825348589863</v>
+        <v>2.333820456093155</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.150023706790845</v>
+        <v>-5.945031860952025</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6374438176556869</v>
+        <v>0.7194405559912145</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.255848247432912</v>
+        <v>-1.050856401594092</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.344300776226025</v>
+        <v>2.467295883729317</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.883423349816493</v>
+        <v>-5.678431503977674</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7252782192292235</v>
+        <v>0.8072749575647511</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.255848247432912</v>
+        <v>-1.050856401594092</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.325495035009821</v>
+        <v>2.448490142513113</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.642992853011632</v>
+        <v>-5.438001007172813</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8231934945760448</v>
+        <v>0.9051902329115724</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.015417750628052</v>
+        <v>-0.8104259047892319</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.471496409717614</v>
+        <v>2.594491517220906</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.400202045362187</v>
+        <v>-5.195210199523368</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9242391314706433</v>
+        <v>1.006235869806171</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.015417750628052</v>
+        <v>-0.8104259047892319</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.475425723552434</v>
+        <v>2.598420831055726</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.160596953755098</v>
+        <v>-4.955605107916279</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.020759752030819</v>
+        <v>1.102756490366346</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9483698029595574</v>
+        <v>-0.7433779571207374</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.516333076070871</v>
+        <v>2.639328183574163</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.917941365331934</v>
+        <v>-4.712949519493115</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.114820058620078</v>
+        <v>1.196816796955605</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9483698029595574</v>
+        <v>-0.7433779571207374</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.513331147290865</v>
+        <v>2.636326254794157</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.697920567294924</v>
+        <v>-4.492928721456105</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.204407414845496</v>
+        <v>1.286404153181024</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8071499578915772</v>
+        <v>-0.6021581120527572</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.599642091342267</v>
+        <v>2.722637198845559</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.498671937390115</v>
+        <v>-4.293680091551296</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.300001049609243</v>
+        <v>1.381997787944771</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8071499578915772</v>
+        <v>-0.6021581120527572</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.61553627414409</v>
+        <v>2.738531381647382</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.339156833870745</v>
+        <v>-4.134164988031926</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.364952935457293</v>
+        <v>1.44694967379282</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6476348543722072</v>
+        <v>-0.4426430085333872</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.712391180696014</v>
+        <v>2.835386288199306</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.194484688771007</v>
+        <v>-3.989492842932188</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.432909896058628</v>
+        <v>1.514906634394155</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5029627092724698</v>
+        <v>-0.2979708634336498</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.809282570317296</v>
+        <v>2.932277677820589</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.176715229840052</v>
+        <v>-3.971723384001233</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.355357371717732</v>
+        <v>1.437354110053259</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4851932503415142</v>
+        <v>-0.2802014045026943</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.735283937762591</v>
+        <v>2.858279045265884</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.089915732061042</v>
+        <v>-3.884923886222224</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.412477664151901</v>
+        <v>1.494474402487429</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4851932503415142</v>
+        <v>-0.2802014045026943</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.757684431085158</v>
+        <v>2.88067953858845</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.419341354637824</v>
+        <v>3.849265884330078</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.007179916421292</v>
+        <v>-3.785231271493212</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.445644391781214</v>
+        <v>1.534423849752446</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.4024574347017633</v>
+        <v>-0.1805087897736825</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.80739832184242</v>
+        <v>2.940567508799269</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -600,22 +600,22 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.5%</t>
+          <t>50.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>67.8%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.4%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>68.6%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-13.0%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>56.8%</t>
+          <t>13.9%</t>
         </is>
       </c>
     </row>
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>55.7%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.5</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.8%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.4%</t>
+          <t>-79.9%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.4%</t>
+          <t>119.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.5%</t>
+          <t>139.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>97.8%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.4%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.8%</t>
+          <t>-58.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-76.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.2%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>755.8%</t>
+          <t>794.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.1%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-540.1%</t>
+          <t>-569.8%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>11.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.9%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.2%</t>
+          <t>-45.9%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10.8%</t>
+          <t>8.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.2%</t>
+          <t>-25.1%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-115.0%</t>
+          <t>-19.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-222.8%</t>
+          <t>-234.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.0%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>72.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.9%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.0%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-317.9%</t>
+          <t>-338.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.5%</t>
+          <t>-39.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-20.7%</t>
+          <t>-27.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>60.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.4</t>
+          <t>-0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.5%</t>
+          <t>33.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.2%</t>
+          <t>-161.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-242.0%</t>
+          <t>-271.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>51.2%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>51.4%</t>
+          <t>52.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.8%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.8%</t>
+          <t>41.7%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.3%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-191.1%</t>
+          <t>-203.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.3%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.3%</t>
+          <t>-34.4%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>45.6%</t>
+          <t>41.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-16.8%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-169.8%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.5211698841151966</v>
+        <v>-0.7261617299540171</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.908256071991203</v>
+        <v>2.826259333655675</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.318117152249395</v>
+        <v>1.113125306410575</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.907950741300667</v>
+        <v>3.784955633797375</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7427918176733141</v>
+        <v>-0.9477836635121346</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.819473515166878</v>
+        <v>2.73747677683135</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.280591018562026</v>
+        <v>1.075599172723206</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.885301277687167</v>
+        <v>3.762306170183875</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9507958760263914</v>
+        <v>-1.155787721865212</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.741164036379573</v>
+        <v>2.659167298044044</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.280591018562026</v>
+        <v>1.075599172723206</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.890193422241092</v>
+        <v>3.7671983147378</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.221195838735277</v>
+        <v>-1.426187684574097</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.628085507634006</v>
+        <v>2.546088769298478</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.010191055853141</v>
+        <v>0.8051992100143204</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.723034900953749</v>
+        <v>3.600039793450457</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.560354216323799</v>
+        <v>-1.765346062162619</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.485506455905047</v>
+        <v>2.403509717569519</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.6710326782646185</v>
+        <v>0.4660408324257983</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.512624173707085</v>
+        <v>3.389629066203793</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.888371438051278</v>
+        <v>-2.093363283890098</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.374637856952823</v>
+        <v>2.292641118617295</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3430154565371394</v>
+        <v>0.1380236106983191</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.336152130409366</v>
+        <v>3.213157022906074</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.381696309586456</v>
+        <v>-2.586688155425276</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.185406658747321</v>
+        <v>2.103409920411792</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2380293422975207</v>
+        <v>0.03303749645870041</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.281259212274163</v>
+        <v>3.158264104770871</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.874081337610553</v>
+        <v>-3.079073183449373</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.989559039581414</v>
+        <v>1.907562301245886</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2543556857265761</v>
+        <v>-0.4593475315653963</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.986934587503437</v>
+        <v>2.863939480000145</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.259261728540625</v>
+        <v>-3.464253574379446</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.834029422022248</v>
+        <v>1.75203268368672</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2543556857265761</v>
+        <v>-0.4593475315653963</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.9854771263163</v>
+        <v>2.862482018813008</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.602944501767288</v>
+        <v>-3.807936347606109</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.6983254361862</v>
+        <v>1.616328697850671</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3622617377537943</v>
+        <v>-0.5672535835926145</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.922502618554586</v>
+        <v>2.799507511051294</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.960594852005636</v>
+        <v>-4.165586697844457</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.551371354747118</v>
+        <v>1.46937461641159</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.7199120879921423</v>
+        <v>-0.9249039338309626</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.704018467067835</v>
+        <v>2.581023359564543</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.269828955001687</v>
+        <v>-4.474820800840508</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.429450640248957</v>
+        <v>1.347453901913429</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.7199120879921423</v>
+        <v>-0.9249039338309626</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.705791393768094</v>
+        <v>2.582796286264802</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.701634748151474</v>
+        <v>-4.906626593990295</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.243061210456447</v>
+        <v>1.161064472120918</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8563295844334093</v>
+        <v>-1.06132143027223</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.610273783370738</v>
+        <v>2.487278675867446</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.028067277019218</v>
+        <v>-5.233059122858039</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.10077297391144</v>
+        <v>1.018776235575912</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9387978349405575</v>
+        <v>-1.143789680779378</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.54907760806854</v>
+        <v>2.426082500565248</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.363729924249671</v>
+        <v>-5.568721770088492</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9650885066752242</v>
+        <v>0.8830917683396957</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9387978349405575</v>
+        <v>-1.143789680779378</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.547658199724506</v>
+        <v>2.424663092221214</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.727356169149984</v>
+        <v>-5.932348014988805</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8261255689493403</v>
+        <v>0.7441288306138119</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.037019471807683</v>
+        <v>-1.242011317646504</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.495212777838471</v>
+        <v>2.372217670335179</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.092483551788731</v>
+        <v>-6.297475397627552</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.679329130899673</v>
+        <v>0.5973323925641445</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.333330256106696</v>
+        <v>-1.538322101945516</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.316680822264896</v>
+        <v>2.193685714761603</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.501072328969409</v>
+        <v>-6.70606417480823</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5146551640421606</v>
+        <v>0.4326584257066326</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.741919033287374</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.070289099971248</v>
+        <v>1.947293992467955</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.914054813110503</v>
+        <v>-7.119046658949324</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3446476028571839</v>
+        <v>0.2626508645216554</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.741919033287374</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.065474532442708</v>
+        <v>1.942479424939416</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.3304466873975</v>
+        <v>-7.535438533236321</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1760849037512622</v>
+        <v>0.09408816541573373</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.741919033287374</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.063468583051586</v>
+        <v>1.940473475548293</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.707123697927345</v>
+        <v>-7.912115543766165</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.0356727902080034</v>
+        <v>-0.04632394812752505</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.741919033287374</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.073727273720265</v>
+        <v>1.950732166216972</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.052998519912153</v>
+        <v>-8.257990365750974</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1065775734402248</v>
+        <v>-0.1885743117757532</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.741919033287374</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.06982683886596</v>
+        <v>1.946831731362668</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.365823319157132</v>
+        <v>-8.570815164995953</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2333025730832152</v>
+        <v>-0.3152993114187437</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.741919033287374</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.068231758920961</v>
+        <v>1.945236651417669</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.66248466096733</v>
+        <v>-8.867476506806151</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3481881338780863</v>
+        <v>-0.4301848722136148</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.810662169021253</v>
+        <v>-2.015654014860073</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.030764853409842</v>
+        <v>1.907769745906549</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.095833769077565</v>
+        <v>-9.300825614916386</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5255540816565833</v>
+        <v>-0.6075508199921118</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.810662169021253</v>
+        <v>-2.015654014860073</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.026738548875438</v>
+        <v>1.903743441372146</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.478835157820196</v>
+        <v>-9.683827003659017</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6788567384752202</v>
+        <v>-0.7608534768107482</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.810662169021253</v>
+        <v>-2.015654014860073</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.026636447553854</v>
+        <v>1.903641340050562</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.853820483991473</v>
+        <v>-10.05881232983029</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8262793529723007</v>
+        <v>-0.9082760913078292</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.18564749519253</v>
+        <v>-2.39063934103135</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.804216767822518</v>
+        <v>1.681221660319226</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.21335080649547</v>
+        <v>-10.4183426523343</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.9647411786758511</v>
+        <v>-1.04673791701138</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.18564749519253</v>
+        <v>-2.39063934103135</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.809567071120568</v>
+        <v>1.686571963617276</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.53975083516049</v>
+        <v>-10.74474268099931</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.087385170184679</v>
+        <v>-1.169381908520208</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.512047523857543</v>
+        <v>-2.717039369696364</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.621643073878738</v>
+        <v>1.498647966375446</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.75889980323469</v>
+        <v>-10.96389164907351</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.172003006792589</v>
+        <v>-1.253999745128117</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.731196491931741</v>
+        <v>-2.936188337770561</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.493195443655988</v>
+        <v>1.370200336152696</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.75520887827827</v>
+        <v>-10.9602007241171</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.170526636810024</v>
+        <v>-1.252523375145553</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.731196491931741</v>
+        <v>-2.936188337770561</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.493195443655988</v>
+        <v>1.370200336152696</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.95946705360814</v>
+        <v>-11.16445889944696</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.246716709823328</v>
+        <v>-1.328713448158856</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.85883543654573</v>
+        <v>-3.06382728238455</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.422125274006237</v>
+        <v>1.299130166502945</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.17750482523932</v>
+        <v>-11.38249667107814</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.329449263991363</v>
+        <v>-1.411446002326891</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.033606204641629</v>
+        <v>-3.238598050480449</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.321745367633134</v>
+        <v>1.198750260129842</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.10403499357187</v>
+        <v>-11.30902683941069</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.284689629830962</v>
+        <v>-1.366686368166491</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.96013637297418</v>
+        <v>-3.165128218813</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.381198968127024</v>
+        <v>1.258203860623732</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.27915941095841</v>
+        <v>-11.48415125679723</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.340184176038063</v>
+        <v>-1.422180914373591</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.135260790360724</v>
+        <v>-3.340252636199544</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.290679538442615</v>
+        <v>1.167684430939323</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.5136115049729</v>
+        <v>-11.71860335081172</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.441184178545454</v>
+        <v>-1.523180916880983</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.135260790360724</v>
+        <v>-3.340252636199544</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.283460373541019</v>
+        <v>1.160465266037727</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.80141534951014</v>
+        <v>-12.00640719534896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.562977907134326</v>
+        <v>-1.644974645469854</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.423064634897962</v>
+        <v>-3.628056480736782</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.1041058760447</v>
+        <v>0.9811107685414076</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.03123979667396</v>
+        <v>-12.23623164251278</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.6537918961613</v>
+        <v>-1.735788634496829</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.585712171968123</v>
+        <v>-3.790704017806943</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.00763314364116</v>
+        <v>0.8846380361378676</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.26326871641023</v>
+        <v>-12.46826056224905</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.74390973542669</v>
+        <v>-1.825906473762218</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.647724869156546</v>
+        <v>-3.852716714995366</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9731192539572202</v>
+        <v>0.8501241464539282</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.21125320244141</v>
+        <v>-12.41624504828023</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.719113194152764</v>
+        <v>-1.801109932488292</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.647724869156546</v>
+        <v>-3.852716714995366</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.977109589643621</v>
+        <v>0.854114482140329</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.35292504416553</v>
+        <v>-12.55791689000435</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.777257157741154</v>
+        <v>-1.859253896076682</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.647724869156546</v>
+        <v>-3.852716714995366</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9756343627448794</v>
+        <v>0.8526392552415873</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.45183178462481</v>
+        <v>-12.65682363046363</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.801766443759992</v>
+        <v>-1.883763182095521</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.746631609615821</v>
+        <v>-3.951623455454641</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9313437286341868</v>
+        <v>0.8083486211308948</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.25267967738771</v>
+        <v>-12.45767152322653</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.735156734511835</v>
+        <v>-1.817153472847364</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.581309083666008</v>
+        <v>-3.786300929504828</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.017486110557392</v>
+        <v>0.8944910030540996</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.0268345246683</v>
+        <v>-12.23182637050712</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.635239600387863</v>
+        <v>-1.71723633872339</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.539382408078844</v>
+        <v>-3.744374253917664</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.052221188945898</v>
+        <v>0.9292260814426063</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.7405597123456</v>
+        <v>-11.94555155818442</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.519590530902726</v>
+        <v>-1.601587269238253</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.539382408078844</v>
+        <v>-3.744374253917664</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.053360333501957</v>
+        <v>0.9303652259986652</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.79345500038989</v>
+        <v>-11.99844684622871</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.538114871958332</v>
+        <v>-1.62011161029386</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.534427061990398</v>
+        <v>-3.739418907829218</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.058967315317133</v>
+        <v>0.9359722078138408</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.50954626946114</v>
+        <v>-11.71453811529996</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.418817675348197</v>
+        <v>-1.500814413683724</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.534427061990398</v>
+        <v>-3.739418907829218</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.064701019555769</v>
+        <v>0.9417059120524773</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.26255901926819</v>
+        <v>-11.46755086510701</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.329760037664881</v>
+        <v>-1.411756776000408</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.287439811797446</v>
+        <v>-3.492431657636266</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.203156107277675</v>
+        <v>1.080160999774383</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.99872215206412</v>
+        <v>-11.20371399790294</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.234108772096161</v>
+        <v>-1.316105510431688</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.287439811797446</v>
+        <v>-3.492431657636266</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.193272625964767</v>
+        <v>1.070277518461475</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.73148035119572</v>
+        <v>-10.93647219703454</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.129046612248175</v>
+        <v>-1.211043350583703</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.287439811797446</v>
+        <v>-3.492431657636266</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.191438065465394</v>
+        <v>1.068442957962102</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.45567118779524</v>
+        <v>-10.66066303363406</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.019023261861442</v>
+        <v>-1.10102000019697</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.198420503518713</v>
+        <v>-3.403412349357533</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.244549335459173</v>
+        <v>1.121554227955881</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.43171764681928</v>
+        <v>-10.6367094926581</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.008773339325565</v>
+        <v>-1.090770077661093</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.174466962542755</v>
+        <v>-3.379458808381575</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.259589966190241</v>
+        <v>1.136594858686949</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.16765770849648</v>
+        <v>-10.3726495543353</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9164096801581989</v>
+        <v>-0.998406418493726</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.910407024219959</v>
+        <v>-3.115398870058779</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.404765613022167</v>
+        <v>1.281770505518875</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.460578084991646</v>
+        <v>-9.665569930830465</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6363648644165645</v>
+        <v>-0.7183616027520925</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.910407024219959</v>
+        <v>-3.115398870058779</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.401978579361866</v>
+        <v>1.278983471858574</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.420393786625455</v>
+        <v>-9.625385632464274</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6199475211822469</v>
+        <v>-0.7019442595177749</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.870222725853768</v>
+        <v>-3.075214571692588</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.426432782269422</v>
+        <v>1.30343767476613</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.340323991087651</v>
+        <v>-9.54531583692647</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5885527817463685</v>
+        <v>-0.6705495200818961</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.790152930315964</v>
+        <v>-2.995144776154784</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.473841480812861</v>
+        <v>1.350846373309569</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.106842768858051</v>
+        <v>-9.31183461469687</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4872358640166761</v>
+        <v>-0.5692326023522041</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.556671708086366</v>
+        <v>-2.761663553925186</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.621854642988473</v>
+        <v>1.498859535485181</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.927134238714178</v>
+        <v>-9.132126084552997</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4182446622720861</v>
+        <v>-0.5002414006076137</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.49950020392367</v>
+        <v>-2.70449204976249</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.653265335173131</v>
+        <v>1.530270227669839</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.794858765083291</v>
+        <v>-8.99985061092211</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3699669860727042</v>
+        <v>-0.4519637244082317</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.367224730292783</v>
+        <v>-2.572216576131603</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.72799810609869</v>
+        <v>1.605002998595398</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.604259090410137</v>
+        <v>-8.809250936248956</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2909120555158058</v>
+        <v>-0.3729087938513338</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.176625055619631</v>
+        <v>-2.381616901458451</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.845172971590218</v>
+        <v>1.722177864086926</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.355259291726556</v>
+        <v>-8.560251137565375</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.178405794818715</v>
+        <v>-0.2604025331542426</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.176625055619631</v>
+        <v>-2.381616901458451</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.858079312813877</v>
+        <v>1.735084205310585</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.460849281499661</v>
+        <v>-8.66584112733848</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3486177203271752</v>
+        <v>-0.4306144586627028</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.282215045392735</v>
+        <v>-2.487206891231555</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.666749389350795</v>
+        <v>1.543754281847503</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.479584183618257</v>
+        <v>-8.684576029457077</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3075673392975276</v>
+        <v>-0.3895640776330556</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.282215045392735</v>
+        <v>-2.487206891231555</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.715293731227882</v>
+        <v>1.59229862372459</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.202846008947445</v>
+        <v>-8.407837854786264</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1934930574432081</v>
+        <v>-0.2754897957787357</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.100398384282809</v>
+        <v>-2.305390230121629</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.827762739879832</v>
+        <v>1.70476763237654</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.075953602512374</v>
+        <v>-8.280945448351194</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.151450081122658</v>
+        <v>-0.2334468194581856</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.97350597784774</v>
+        <v>-2.17849782368656</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.895184197487396</v>
+        <v>1.772189089984104</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.032405195741683</v>
+        <v>-8.237397041580502</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1409913305094745</v>
+        <v>-0.2229880688450021</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.97350597784774</v>
+        <v>-2.17849782368656</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.888223585392303</v>
+        <v>1.765228477889011</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.790256802287825</v>
+        <v>-7.995248648126644</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.0296696187467882</v>
+        <v>-0.1116663570823158</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.97350597784774</v>
+        <v>-2.17849782368656</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.902685939773446</v>
+        <v>1.779690832270154</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.727027430519477</v>
+        <v>-7.932019276358296</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.009845749580253749</v>
+        <v>-0.09184248791578176</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.97350597784774</v>
+        <v>-2.17849782368656</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.897218060232641</v>
+        <v>1.774222952729349</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.540539738142471</v>
+        <v>-7.74553158398129</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.06224742138112527</v>
+        <v>-0.0197493169544023</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.787018285470733</v>
+        <v>-1.992010131309553</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.006608769669421</v>
+        <v>1.883613662166129</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.519390539239027</v>
+        <v>-7.724382385077846</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.0784080791798285</v>
+        <v>-0.003588659155699503</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.76586908656729</v>
+        <v>-1.97086093240611</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.026999267248813</v>
+        <v>1.904004159745521</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.275625097255583</v>
+        <v>-7.480616943094402</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1716949643202565</v>
+        <v>0.08969822598472899</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.76586908656729</v>
+        <v>-1.97086093240611</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.022779975595864</v>
+        <v>1.899784868092572</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.011597030062322</v>
+        <v>-7.216588875901142</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2794305051175767</v>
+        <v>0.1974337667820492</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.564003687751336</v>
+        <v>-1.768995533590156</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.146023528805452</v>
+        <v>2.023028421302159</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.761746636113248</v>
+        <v>-6.966738481952067</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3721127376809088</v>
+        <v>0.2901159993453812</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.564003687751336</v>
+        <v>-1.768995533590156</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.138765603789154</v>
+        <v>2.015770496285862</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.458179147109269</v>
+        <v>-6.663170992948088</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.497138856803149</v>
+        <v>0.4151421184676214</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.564003687751336</v>
+        <v>-1.768995533590156</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.142364727309803</v>
+        <v>2.01936961980651</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.384699238257255</v>
+        <v>-6.589691084096074</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5398583263985084</v>
+        <v>0.4578615880629808</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.490523778899322</v>
+        <v>-1.695515624738142</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.199780178675565</v>
+        <v>2.076785071172273</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.159666238588432</v>
+        <v>-6.364658084427251</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6288920038823345</v>
+        <v>0.5468952655468069</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.265490779230499</v>
+        <v>-1.470482625069319</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.333820456093155</v>
+        <v>2.210825348589863</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.945031860952025</v>
+        <v>-6.150023706790845</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7194405559912145</v>
+        <v>0.6374438176556869</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.050856401594092</v>
+        <v>-1.255848247432912</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.467295883729317</v>
+        <v>2.344300776226025</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.678431503977674</v>
+        <v>-5.883423349816493</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8072749575647511</v>
+        <v>0.7252782192292235</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.050856401594092</v>
+        <v>-1.255848247432912</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.448490142513113</v>
+        <v>2.325495035009821</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.438001007172813</v>
+        <v>-5.642992853011632</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9051902329115724</v>
+        <v>0.8231934945760448</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8104259047892319</v>
+        <v>-1.015417750628052</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.594491517220906</v>
+        <v>2.471496409717614</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.195210199523368</v>
+        <v>-5.400202045362187</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.006235869806171</v>
+        <v>0.9242391314706433</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8104259047892319</v>
+        <v>-1.015417750628052</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.598420831055726</v>
+        <v>2.475425723552434</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.955605107916279</v>
+        <v>-5.160596953755098</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.102756490366346</v>
+        <v>1.020759752030819</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7433779571207374</v>
+        <v>-0.9483698029595574</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.639328183574163</v>
+        <v>2.516333076070871</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.712949519493115</v>
+        <v>-4.917941365331934</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.196816796955605</v>
+        <v>1.114820058620078</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7433779571207374</v>
+        <v>-0.9483698029595574</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.636326254794157</v>
+        <v>2.513331147290865</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.492928721456105</v>
+        <v>-4.697920567294924</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.286404153181024</v>
+        <v>1.204407414845496</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6021581120527572</v>
+        <v>-0.8071499578915772</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.722637198845559</v>
+        <v>2.599642091342267</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.293680091551296</v>
+        <v>-4.498671937390115</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.381997787944771</v>
+        <v>1.300001049609243</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6021581120527572</v>
+        <v>-0.8071499578915772</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.738531381647382</v>
+        <v>2.61553627414409</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.134164988031926</v>
+        <v>-4.339156833870745</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.44694967379282</v>
+        <v>1.364952935457293</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4426430085333872</v>
+        <v>-0.6476348543722072</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.835386288199306</v>
+        <v>2.712391180696014</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.989492842932188</v>
+        <v>-4.194484688771007</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.514906634394155</v>
+        <v>1.432909896058628</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2979708634336498</v>
+        <v>-0.5029627092724698</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.932277677820589</v>
+        <v>2.809282570317296</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.971723384001233</v>
+        <v>-4.176715229840052</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.437354110053259</v>
+        <v>1.355357371717732</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2802014045026943</v>
+        <v>-0.4851932503415142</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.858279045265884</v>
+        <v>2.735283937762591</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.884923886222224</v>
+        <v>-4.089915732061042</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.494474402487429</v>
+        <v>1.412477664151901</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2802014045026943</v>
+        <v>-0.4851932503415142</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.88067953858845</v>
+        <v>2.757684431085158</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.849265884330078</v>
+        <v>3.419341354637824</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.785231271493212</v>
+        <v>-4.081774129674884</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.534423849752446</v>
+        <v>1.415806706479777</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.1805087897736825</v>
+        <v>-0.477051647955356</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.940567508799269</v>
+        <v>2.762641793890265</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>50.4%</t>
+          <t>65.4%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>66.4%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -619,7 +619,7 @@
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.6%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.3%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-13.0%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>57.3%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>76.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>30.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.6%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -815,7 +815,7 @@
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
@@ -824,17 +824,17 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.6%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.3%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>7.0%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>57.8%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>24.0%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.8%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.1%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-6.7%</t>
+          <t>12.1%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.9%</t>
+          <t>-78.6%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.3%</t>
+          <t>118.2%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.67</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.3%</t>
+          <t>137.3%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-57.7%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-76.5%</t>
+          <t>-74.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>794.5%</t>
+          <t>749.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>0.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-569.8%</t>
+          <t>-546.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.0%</t>
+          <t>13.3%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>65.8%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.8%</t>
+          <t>99.7%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1155,7 +1155,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.9%</t>
+          <t>-45.1%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.6%</t>
+          <t>10.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.3%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.1%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-19.3%</t>
+          <t>-202.3%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-234.6%</t>
+          <t>-225.3%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-28.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.3%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.41</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>70.6%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1289,11 +1289,11 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-338.4%</t>
+          <t>-315.0%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1313,7 +1313,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.8%</t>
+          <t>-38.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-27.3%</t>
+          <t>-21.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>60.1%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.5</t>
+          <t>-0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>33.5%</t>
+          <t>34.7%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-161.8%</t>
+          <t>-154.9%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-271.7%</t>
+          <t>-248.3%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>58.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>52.2%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>1.10</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.1%</t>
+          <t>59.2%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,22 +1418,22 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-04-15</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.5%</t>
+          <t>62.7%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.7%</t>
+          <t>45.5%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>98.3%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1447,11 +1447,11 @@
         </is>
       </c>
       <c r="N7" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-203.4%</t>
+          <t>-189.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>13.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-34.4%</t>
+          <t>-33.1%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>41.0%</t>
+          <t>51.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>43.6%</t>
+          <t>44.3%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.8%</t>
+          <t>-17.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-169.8%</t>
+          <t>-123.0%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1935"/>
+  <dimension ref="A1:G1936"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.7261617299540171</v>
+        <v>-0.492201737938974</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.826259333655675</v>
+        <v>2.919843330461692</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.113125306410575</v>
+        <v>1.347085298425618</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.784955633797375</v>
+        <v>3.925331629006401</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9477836635121346</v>
+        <v>-0.7138236714970915</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.73747677683135</v>
+        <v>2.831060773637367</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.075599172723206</v>
+        <v>1.309559164738249</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.762306170183875</v>
+        <v>3.902682165392901</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.155787721865212</v>
+        <v>-0.9218277298501687</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.659167298044044</v>
+        <v>2.752751294850062</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.075599172723206</v>
+        <v>1.309559164738249</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.7671983147378</v>
+        <v>3.907574309946826</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.426187684574097</v>
+        <v>-1.192227692559054</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.546088769298478</v>
+        <v>2.639672766104495</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8051992100143204</v>
+        <v>1.039159202029363</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.600039793450457</v>
+        <v>3.740415788659483</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.765346062162619</v>
+        <v>-1.531386070147576</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.403509717569519</v>
+        <v>2.497093714375536</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4660408324257983</v>
+        <v>0.7000008244408413</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.389629066203793</v>
+        <v>3.530005061412819</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.093363283890098</v>
+        <v>-1.859403291875055</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.292641118617295</v>
+        <v>2.386225115423312</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1380236106983191</v>
+        <v>0.3719836027133622</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.213157022906074</v>
+        <v>3.353533018115099</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.586688155425276</v>
+        <v>-2.352728163410234</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.103409920411792</v>
+        <v>2.19699391721781</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.03303749645870041</v>
+        <v>0.2669974884737434</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.158264104770871</v>
+        <v>3.298640099979897</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.079073183449373</v>
+        <v>-2.845113191434331</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.907562301245886</v>
+        <v>2.001146298051903</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4593475315653963</v>
+        <v>-0.2253875395503533</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.863939480000145</v>
+        <v>3.004315475209171</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.464253574379446</v>
+        <v>-3.230293582364403</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.75203268368672</v>
+        <v>1.845616680492737</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4593475315653963</v>
+        <v>-0.2253875395503533</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.862482018813008</v>
+        <v>3.002858014022034</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.807936347606109</v>
+        <v>-3.573976355591066</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.616328697850671</v>
+        <v>1.709912694656688</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5672535835926145</v>
+        <v>-0.3332935915775715</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.799507511051294</v>
+        <v>2.939883506260319</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.165586697844457</v>
+        <v>-3.931626705829414</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.46937461641159</v>
+        <v>1.562958613217607</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9249039338309626</v>
+        <v>-0.6909439418159196</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.581023359564543</v>
+        <v>2.721399354773569</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.474820800840508</v>
+        <v>-4.240860808825465</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.347453901913429</v>
+        <v>1.441037898719446</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9249039338309626</v>
+        <v>-0.6909439418159196</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.582796286264802</v>
+        <v>2.723172281473828</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.906626593990295</v>
+        <v>-4.672666601975252</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.161064472120918</v>
+        <v>1.254648468926936</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.06132143027223</v>
+        <v>-0.8273614382571866</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.487278675867446</v>
+        <v>2.627654671076472</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.233059122858039</v>
+        <v>-4.999099130842996</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.018776235575912</v>
+        <v>1.112360232381929</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.143789680779378</v>
+        <v>-0.9098296887643347</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.426082500565248</v>
+        <v>2.566458495774274</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.568721770088492</v>
+        <v>-5.334761778073449</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8830917683396957</v>
+        <v>0.9766757651457127</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.143789680779378</v>
+        <v>-0.9098296887643347</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.424663092221214</v>
+        <v>2.565039087430239</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.932348014988805</v>
+        <v>-5.698388022973762</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7441288306138119</v>
+        <v>0.8377128274198293</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.242011317646504</v>
+        <v>-1.00805132563146</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.372217670335179</v>
+        <v>2.512593665544205</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.297475397627552</v>
+        <v>-6.063515405612509</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5973323925641445</v>
+        <v>0.690916389370162</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.538322101945516</v>
+        <v>-1.304362109930473</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.193685714761603</v>
+        <v>2.334061709970629</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.70606417480823</v>
+        <v>-6.472104182793187</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4326584257066326</v>
+        <v>0.5262424225126496</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.712950887111151</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.947293992467955</v>
+        <v>2.087669987676981</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.119046658949324</v>
+        <v>-6.885086666934281</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2626508645216554</v>
+        <v>0.3562348613276729</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.712950887111151</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.942479424939416</v>
+        <v>2.082855420148442</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.535438533236321</v>
+        <v>-7.301478541221278</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09408816541573373</v>
+        <v>0.1876721622217512</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.712950887111151</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.940473475548293</v>
+        <v>2.080849470757319</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.912115543766165</v>
+        <v>-7.678155551751122</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04632394812752505</v>
+        <v>0.04726004867849243</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.712950887111151</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.950732166216972</v>
+        <v>2.091108161425998</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.257990365750974</v>
+        <v>-8.024030373735931</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1885743117757532</v>
+        <v>-0.09499031496973576</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.712950887111151</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.946831731362668</v>
+        <v>2.087207726571693</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.570815164995953</v>
+        <v>-8.33685517298091</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3152993114187437</v>
+        <v>-0.2217153146127262</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.712950887111151</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.945236651417669</v>
+        <v>2.085612646626694</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.867476506806151</v>
+        <v>-8.633516514791108</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4301848722136148</v>
+        <v>-0.3366008754075973</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.78169402284503</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.907769745906549</v>
+        <v>2.048145741115575</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.300825614916386</v>
+        <v>-9.066865622901343</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6075508199921118</v>
+        <v>-0.5139668231860948</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.78169402284503</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.903743441372146</v>
+        <v>2.044119436581172</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.683827003659017</v>
+        <v>-9.449867011643974</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7608534768107482</v>
+        <v>-0.6672694800047312</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.78169402284503</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.903641340050562</v>
+        <v>2.044017335259588</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.05881232983029</v>
+        <v>-9.824852337815251</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9082760913078292</v>
+        <v>-0.8146920945018121</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.39063934103135</v>
+        <v>-2.156679349016307</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.681221660319226</v>
+        <v>1.821597655528252</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.4183426523343</v>
+        <v>-10.18438266031925</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.04673791701138</v>
+        <v>-0.953153920205362</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.39063934103135</v>
+        <v>-2.156679349016307</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.686571963617276</v>
+        <v>1.826947958826302</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.74474268099931</v>
+        <v>-10.51078268898427</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.169381908520208</v>
+        <v>-1.07579791171419</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.717039369696364</v>
+        <v>-2.48307937768132</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.498647966375446</v>
+        <v>1.639023961584472</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.96389164907351</v>
+        <v>-10.72993165705846</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.253999745128117</v>
+        <v>-1.1604157483221</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.936188337770561</v>
+        <v>-2.702228345755518</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.370200336152696</v>
+        <v>1.510576331361722</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.9602007241171</v>
+        <v>-10.72624073210205</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.252523375145553</v>
+        <v>-1.158939378339536</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.936188337770561</v>
+        <v>-2.702228345755518</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.370200336152696</v>
+        <v>1.510576331361722</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.16445889944696</v>
+        <v>-10.93049890743192</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.328713448158856</v>
+        <v>-1.235129451352839</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.06382728238455</v>
+        <v>-2.829867290369507</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.299130166502945</v>
+        <v>1.439506161711971</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.38249667107814</v>
+        <v>-11.14853667906309</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.411446002326891</v>
+        <v>-1.317862005520874</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.238598050480449</v>
+        <v>-3.004638058465406</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.198750260129842</v>
+        <v>1.339126255338868</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.30902683941069</v>
+        <v>-11.07506684739564</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.366686368166491</v>
+        <v>-1.273102371360474</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.165128218813</v>
+        <v>-2.931168226797957</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.258203860623732</v>
+        <v>1.398579855832758</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.48415125679723</v>
+        <v>-11.25019126478219</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.422180914373591</v>
+        <v>-1.328596917567574</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.340252636199544</v>
+        <v>-3.106292644184501</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.167684430939323</v>
+        <v>1.308060426148348</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.71860335081172</v>
+        <v>-11.48464335879668</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.523180916880983</v>
+        <v>-1.429596920074966</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.340252636199544</v>
+        <v>-3.106292644184501</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.160465266037727</v>
+        <v>1.300841261246752</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.00640719534896</v>
+        <v>-11.77244720333392</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.644974645469854</v>
+        <v>-1.551390648663837</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.628056480736782</v>
+        <v>-3.394096488721739</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.9811107685414076</v>
+        <v>1.121486763750434</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.23623164251278</v>
+        <v>-12.00227165049774</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.735788634496829</v>
+        <v>-1.642204637690811</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.790704017806943</v>
+        <v>-3.5567440257919</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.8846380361378676</v>
+        <v>1.025014031346893</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.46826056224905</v>
+        <v>-12.234300570234</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.825906473762218</v>
+        <v>-1.732322476956201</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.618756722980323</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8501241464539282</v>
+        <v>0.9905001416629542</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.41624504828023</v>
+        <v>-12.18228505626519</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.801109932488292</v>
+        <v>-1.707525935682275</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.618756722980323</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.854114482140329</v>
+        <v>0.994490477349355</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.55791689000435</v>
+        <v>-12.32395689798931</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.859253896076682</v>
+        <v>-1.765669899270665</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.618756722980323</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8526392552415873</v>
+        <v>0.9930152504506133</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.65682363046363</v>
+        <v>-12.42286363844859</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.883763182095521</v>
+        <v>-1.790179185289503</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.951623455454641</v>
+        <v>-3.717663463439598</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8083486211308948</v>
+        <v>0.9487246163399203</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.45767152322653</v>
+        <v>-12.22371153121149</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.817153472847364</v>
+        <v>-1.723569476041347</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.786300929504828</v>
+        <v>-3.552340937489785</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.8944910030540996</v>
+        <v>1.034866998263126</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.23182637050712</v>
+        <v>-11.99786637849208</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.71723633872339</v>
+        <v>-1.623652341917374</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.744374253917664</v>
+        <v>-3.510414261902621</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9292260814426063</v>
+        <v>1.069602076651632</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.94555155818442</v>
+        <v>-11.71159156616938</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.601587269238253</v>
+        <v>-1.508003272432237</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.744374253917664</v>
+        <v>-3.510414261902621</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9303652259986652</v>
+        <v>1.070741221207691</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.99844684622871</v>
+        <v>-11.76448685421367</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.62011161029386</v>
+        <v>-1.526527613487843</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.739418907829218</v>
+        <v>-3.505458915814175</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9359722078138408</v>
+        <v>1.076348203022866</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.71453811529996</v>
+        <v>-11.48057812328492</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.500814413683724</v>
+        <v>-1.407230416877708</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.739418907829218</v>
+        <v>-3.505458915814175</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9417059120524773</v>
+        <v>1.082081907261503</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.46755086510701</v>
+        <v>-11.23359087309197</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.411756776000408</v>
+        <v>-1.318172779194392</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.492431657636266</v>
+        <v>-3.258471665621223</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.080160999774383</v>
+        <v>1.220536994983409</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.20371399790294</v>
+        <v>-10.9697540058879</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.316105510431688</v>
+        <v>-1.222521513625672</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.492431657636266</v>
+        <v>-3.258471665621223</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.070277518461475</v>
+        <v>1.210653513670501</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.93647219703454</v>
+        <v>-10.7025122050195</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.211043350583703</v>
+        <v>-1.117459353777686</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.492431657636266</v>
+        <v>-3.258471665621223</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.068442957962102</v>
+        <v>1.208818953171128</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.66066303363406</v>
+        <v>-10.42670304161902</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.10102000019697</v>
+        <v>-1.007436003390953</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.403412349357533</v>
+        <v>-3.16945235734249</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.121554227955881</v>
+        <v>1.261930223164907</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.6367094926581</v>
+        <v>-10.40274950064306</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.090770077661093</v>
+        <v>-0.9971860808550761</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.379458808381575</v>
+        <v>-3.145498816366532</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.136594858686949</v>
+        <v>1.276970853895975</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.3726495543353</v>
+        <v>-10.13868956232026</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.998406418493726</v>
+        <v>-0.9048224216877099</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.115398870058779</v>
+        <v>-2.881438878043736</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.281770505518875</v>
+        <v>1.4221465007279</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.665569930830465</v>
+        <v>-9.431609938815424</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7183616027520925</v>
+        <v>-0.6247776059460759</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.115398870058779</v>
+        <v>-2.881438878043736</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.278983471858574</v>
+        <v>1.4193594670676</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.625385632464274</v>
+        <v>-9.391425640449233</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7019442595177749</v>
+        <v>-0.6083602627117584</v>
       </c>
       <c r="F1901" t="n">
-        <v>-3.075214571692588</v>
+        <v>-2.841254579677545</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.30343767476613</v>
+        <v>1.443813669975156</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.54531583692647</v>
+        <v>-9.311355844911429</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6705495200818961</v>
+        <v>-0.5769655232758795</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.995144776154784</v>
+        <v>-2.761184784139741</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.350846373309569</v>
+        <v>1.491222368518595</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.31183461469687</v>
+        <v>-9.077874622681829</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5692326023522041</v>
+        <v>-0.4756486055461875</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.761663553925186</v>
+        <v>-2.527703561910143</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.498859535485181</v>
+        <v>1.639235530694206</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.132126084552997</v>
+        <v>-8.898166092537956</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.5002414006076137</v>
+        <v>-0.4066574038015971</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.70449204976249</v>
+        <v>-2.470532057747447</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.530270227669839</v>
+        <v>1.670646222878865</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.99985061092211</v>
+        <v>-8.765890618907068</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4519637244082317</v>
+        <v>-0.3583797276022151</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.572216576131603</v>
+        <v>-2.33825658411656</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.605002998595398</v>
+        <v>1.745378993804424</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.809250936248956</v>
+        <v>-8.575290944233915</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3729087938513338</v>
+        <v>-0.2793247970453172</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.381616901458451</v>
+        <v>-2.147656909443408</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.722177864086926</v>
+        <v>1.862553859295952</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.560251137565375</v>
+        <v>-8.326291145550334</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2604025331542426</v>
+        <v>-0.166818536348226</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.381616901458451</v>
+        <v>-2.147656909443408</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.735084205310585</v>
+        <v>1.875460200519611</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.66584112733848</v>
+        <v>-8.431881135323438</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4306144586627028</v>
+        <v>-0.3370304618566866</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.487206891231555</v>
+        <v>-2.253246899216512</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.543754281847503</v>
+        <v>1.684130277056529</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.684576029457077</v>
+        <v>-8.450616037442035</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3895640776330556</v>
+        <v>-0.295980080827039</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.487206891231555</v>
+        <v>-2.253246899216512</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.59229862372459</v>
+        <v>1.732674618933616</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.407837854786264</v>
+        <v>-8.173877862771223</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2754897957787357</v>
+        <v>-0.1819057989727191</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.305390230121629</v>
+        <v>-2.071430238106586</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.70476763237654</v>
+        <v>1.845143627585566</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.280945448351194</v>
+        <v>-8.046985456336152</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2334468194581856</v>
+        <v>-0.139862822652169</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.944537831671517</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.772189089984104</v>
+        <v>1.91256508519313</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.237397041580502</v>
+        <v>-8.003437049565463</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2229880688450021</v>
+        <v>-0.129404072038986</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.944537831671517</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.765228477889011</v>
+        <v>1.905604473098036</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.995248648126644</v>
+        <v>-7.761288656111605</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1116663570823158</v>
+        <v>-0.01808236027629961</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.944537831671517</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.779690832270154</v>
+        <v>1.92006682747918</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.932019276358296</v>
+        <v>-7.698059284343256</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.09184248791578176</v>
+        <v>0.001741508890234389</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.17849782368656</v>
+        <v>-1.944537831671517</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.774222952729349</v>
+        <v>1.914598947938375</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.74553158398129</v>
+        <v>-7.51157159196625</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.0197493169544023</v>
+        <v>0.07383467985161385</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.992010131309553</v>
+        <v>-1.75805013929451</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.883613662166129</v>
+        <v>2.023989657375155</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.724382385077846</v>
+        <v>-7.490422393062807</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.003588659155699503</v>
+        <v>0.08999533765031664</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.97086093240611</v>
+        <v>-1.736900940391067</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.904004159745521</v>
+        <v>2.044380154954547</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.480616943094402</v>
+        <v>-7.246656951079363</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.08969822598472899</v>
+        <v>0.1832822227907451</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.97086093240611</v>
+        <v>-1.736900940391067</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.899784868092572</v>
+        <v>2.040160863301598</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.216588875901142</v>
+        <v>-6.982628883886103</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1974337667820492</v>
+        <v>0.2910177635880649</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.768995533590156</v>
+        <v>-1.535035541575113</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.023028421302159</v>
+        <v>2.163404416511185</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.966738481952067</v>
+        <v>-6.732778489937028</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2901159993453812</v>
+        <v>0.3836999961513969</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.768995533590156</v>
+        <v>-1.535035541575113</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.015770496285862</v>
+        <v>2.156146491494888</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.663170992948088</v>
+        <v>-6.42921100093305</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4151421184676214</v>
+        <v>0.5087261152736371</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.768995533590156</v>
+        <v>-1.535035541575113</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.01936961980651</v>
+        <v>2.159745615015536</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.589691084096074</v>
+        <v>-6.355731092081036</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4578615880629808</v>
+        <v>0.5514455848689965</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.695515624738142</v>
+        <v>-1.461555632723099</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.076785071172273</v>
+        <v>2.217161066381299</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.364658084427251</v>
+        <v>-6.130698092412213</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5468952655468069</v>
+        <v>0.6404792623528226</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.470482625069319</v>
+        <v>-1.236522633054276</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.210825348589863</v>
+        <v>2.351201343798889</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.150023706790845</v>
+        <v>-5.916063714775806</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6374438176556869</v>
+        <v>0.7310278144617026</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.255848247432912</v>
+        <v>-1.021888255417869</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.344300776226025</v>
+        <v>2.484676771435051</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.883423349816493</v>
+        <v>-5.649463357801454</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7252782192292235</v>
+        <v>0.8188622160352392</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.255848247432912</v>
+        <v>-1.021888255417869</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.325495035009821</v>
+        <v>2.465871030218846</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.642992853011632</v>
+        <v>-5.409032860996594</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8231934945760448</v>
+        <v>0.9167774913820605</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.015417750628052</v>
+        <v>-0.7814577586130089</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.471496409717614</v>
+        <v>2.61187240492664</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.400202045362187</v>
+        <v>-5.166242053347148</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9242391314706433</v>
+        <v>1.017823128276659</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.015417750628052</v>
+        <v>-0.7814577586130089</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.475425723552434</v>
+        <v>2.61580171876146</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.160596953755098</v>
+        <v>-4.926636961740059</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.020759752030819</v>
+        <v>1.114343748836835</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.9483698029595574</v>
+        <v>-0.7144098109445144</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.516333076070871</v>
+        <v>2.656709071279897</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.917941365331934</v>
+        <v>-4.683981373316896</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.114820058620078</v>
+        <v>1.208404055426094</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.9483698029595574</v>
+        <v>-0.7144098109445144</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.513331147290865</v>
+        <v>2.65370714249989</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.697920567294924</v>
+        <v>-4.463960575279885</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.204407414845496</v>
+        <v>1.297991411651512</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8071499578915772</v>
+        <v>-0.5731899658765341</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.599642091342267</v>
+        <v>2.740018086551293</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.498671937390115</v>
+        <v>-4.264711945375076</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.300001049609243</v>
+        <v>1.393585046415259</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8071499578915772</v>
+        <v>-0.5731899658765341</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.61553627414409</v>
+        <v>2.755912269353116</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.339156833870745</v>
+        <v>-4.105196841855706</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.364952935457293</v>
+        <v>1.458536932263309</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.6476348543722072</v>
+        <v>-0.4136748623571642</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.712391180696014</v>
+        <v>2.85276717590504</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.194484688771007</v>
+        <v>-3.960524696755969</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.432909896058628</v>
+        <v>1.526493892864643</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5029627092724698</v>
+        <v>-0.2690027172574268</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.809282570317296</v>
+        <v>2.949658565526322</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.176715229840052</v>
+        <v>-3.942755237825013</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.355357371717732</v>
+        <v>1.448941368523747</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4851932503415142</v>
+        <v>-0.2512332583264713</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.735283937762591</v>
+        <v>2.875659932971617</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.089915732061042</v>
+        <v>-3.855955740046005</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.412477664151901</v>
+        <v>1.506061660957917</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4851932503415142</v>
+        <v>-0.2512332583264713</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.757684431085158</v>
+        <v>2.898060426294183</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,45 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.419341354637824</v>
+        <v>3.729142822900687</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.081774129674884</v>
+        <v>-3.847814137659847</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.415806706479777</v>
+        <v>1.509390703285792</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.477051647955356</v>
+        <v>-0.243091655940313</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.762641793890265</v>
+        <v>2.90301778909929</v>
+      </c>
+    </row>
+    <row r="1936">
+      <c r="A1936" s="2" t="n">
+        <v>45398</v>
+      </c>
+      <c r="B1936" t="n">
+        <v>3.853429626382484</v>
+      </c>
+      <c r="C1936" t="n">
+        <v>3.2369261577697</v>
+      </c>
+      <c r="D1936" t="n">
+        <v>-3.847814137659847</v>
+      </c>
+      <c r="E1936" t="n">
+        <v>1.509390703285792</v>
+      </c>
+      <c r="F1936" t="n">
+        <v>-0.243091655940313</v>
+      </c>
+      <c r="G1936" t="n">
+        <v>3.229989954756068</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.4%</t>
+          <t>58.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.4%</t>
+          <t>66.3%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.3%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-19.9%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-15.4%</t>
+          <t>-17.5%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.3%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-11.9%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>57.3%</t>
+          <t>35.4%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.0%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>30.1%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>29.5%</t>
+          <t>27.8%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,7 +834,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>7.0%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -849,12 +849,12 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>59.8%</t>
+          <t>58.2%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.0%</t>
+          <t>23.3%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -869,12 +869,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-5.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.5%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>-1.3%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-78.6%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.2%</t>
+          <t>118.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-0.67</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>137.3%</t>
+          <t>139.2%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.8%</t>
+          <t>97.1%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.4%</t>
+          <t>29.3%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-57.7%</t>
+          <t>-58.6%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-74.2%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>98.6%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>749.2%</t>
+          <t>795.6%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-546.4%</t>
+          <t>-570.4%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>13.3%</t>
+          <t>11.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.4%</t>
+          <t>55.6%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,17 +1107,17 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>65.8%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.1%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>99.7%</t>
+          <t>99.8%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.1%</t>
+          <t>-45.8%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>10.4%</t>
+          <t>8.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.3%</t>
+          <t>46.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.5%</t>
+          <t>-27.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-202.3%</t>
+          <t>-17.9%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-225.3%</t>
+          <t>-234.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-28.6%</t>
+          <t>-32.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>71.9%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.41</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.6%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>70.6%</t>
+          <t>73.4%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.0%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-315.0%</t>
+          <t>-329.8%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.3%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-21.3%</t>
+          <t>-26.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>59.7%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-158.7%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-248.3%</t>
+          <t>-269.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>58.5%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.1%</t>
+          <t>53.8%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.10</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>62.7%</t>
+          <t>64.6%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.2%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-189.4%</t>
+          <t>-198.3%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,47 +1466,47 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>13.0%</t>
+          <t>12.9%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.1%</t>
+          <t>-33.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>51.1%</t>
+          <t>50.1%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.3%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>1.1</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-17.0%</t>
+          <t>-18.5%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>33.8%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-123.0%</t>
+          <t>-136.4%</t>
         </is>
       </c>
     </row>
@@ -44032,16 +44032,16 @@
         <v>3.117080449951029</v>
       </c>
       <c r="D1847" t="n">
-        <v>-0.492201737938974</v>
+        <v>-0.7261617299540171</v>
       </c>
       <c r="E1847" t="n">
-        <v>2.919843330461692</v>
+        <v>2.826259333655675</v>
       </c>
       <c r="F1847" t="n">
-        <v>1.347085298425618</v>
+        <v>1.113125306410575</v>
       </c>
       <c r="G1847" t="n">
-        <v>3.925331629006401</v>
+        <v>3.784955633797375</v>
       </c>
     </row>
     <row r="1848">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.7138236714970915</v>
+        <v>-0.9307309757871566</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.831060773637367</v>
+        <v>2.744297851921341</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.309559164738249</v>
+        <v>1.161150391720504</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.902682165392901</v>
+        <v>3.813636901582254</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-0.9218277298501687</v>
+        <v>-1.138735034140234</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.752751294850062</v>
+        <v>2.665988373134036</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.309559164738249</v>
+        <v>1.161150391720504</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.907574309946826</v>
+        <v>3.818529046136179</v>
       </c>
     </row>
     <row r="1850">
@@ -44095,22 +44095,22 @@
         <v>45312</v>
       </c>
       <c r="B1850" t="n">
-        <v>3.251475576074624</v>
+        <v>3.251475576074623</v>
       </c>
       <c r="C1850" t="n">
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.192227692559054</v>
+        <v>-1.409134996849119</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.639672766104495</v>
+        <v>2.552909844388469</v>
       </c>
       <c r="F1850" t="n">
-        <v>1.039159202029363</v>
+        <v>0.890750429011619</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.740415788659483</v>
+        <v>3.651370524848836</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.531386070147576</v>
+        <v>-1.748293374437641</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.497093714375536</v>
+        <v>2.41033079265951</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.7000008244408413</v>
+        <v>0.551592051423097</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.530005061412819</v>
+        <v>3.440959797602172</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-1.859403291875055</v>
+        <v>-2.07631059616512</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.386225115423312</v>
+        <v>2.299462193707286</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.3719836027133622</v>
+        <v>0.2235748296956178</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.353533018115099</v>
+        <v>3.264487754304453</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.352728163410234</v>
+        <v>-2.569635467700298</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.19699391721781</v>
+        <v>2.110230995501784</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.2669974884737434</v>
+        <v>0.1185887154559991</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.298640099979897</v>
+        <v>3.20959483616925</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-2.845113191434331</v>
+        <v>-3.062020495724395</v>
       </c>
       <c r="E1854" t="n">
-        <v>2.001146298051903</v>
+        <v>1.914383376335877</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.2253875395503533</v>
+        <v>-0.3737963125680976</v>
       </c>
       <c r="G1854" t="n">
-        <v>3.004315475209171</v>
+        <v>2.915270211398524</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.230293582364403</v>
+        <v>-3.447200886654468</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.845616680492737</v>
+        <v>1.758853758776711</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.2253875395503533</v>
+        <v>-0.3737963125680976</v>
       </c>
       <c r="G1855" t="n">
-        <v>3.002858014022034</v>
+        <v>2.913812750211388</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.573976355591066</v>
+        <v>-3.790883659881131</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.709912694656688</v>
+        <v>1.623149772940662</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.3332935915775715</v>
+        <v>-0.4817023645953158</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.939883506260319</v>
+        <v>2.850838242449673</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-3.931626705829414</v>
+        <v>-4.148534010119478</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.562958613217607</v>
+        <v>1.476195691501581</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.6909439418159196</v>
+        <v>-0.8393527148336639</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.721399354773569</v>
+        <v>2.632354090962922</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.240860808825465</v>
+        <v>-4.457768113115529</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.441037898719446</v>
+        <v>1.35427497700342</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.6909439418159196</v>
+        <v>-0.8393527148336639</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.723172281473828</v>
+        <v>2.634127017663181</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.672666601975252</v>
+        <v>-4.889573906265317</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.254648468926936</v>
+        <v>1.16788554721091</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.8273614382571866</v>
+        <v>-0.9757702112749309</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.627654671076472</v>
+        <v>2.538609407265826</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-4.999099130842996</v>
+        <v>-5.21600643513306</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.112360232381929</v>
+        <v>1.025597310665903</v>
       </c>
       <c r="F1860" t="n">
-        <v>-0.9098296887643347</v>
+        <v>-1.058238461782079</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.566458495774274</v>
+        <v>2.477413231963627</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.334761778073449</v>
+        <v>-5.551669082363513</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.9766757651457127</v>
+        <v>0.8899128434296868</v>
       </c>
       <c r="F1861" t="n">
-        <v>-0.9098296887643347</v>
+        <v>-1.058238461782079</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.565039087430239</v>
+        <v>2.475993823619592</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.698388022973762</v>
+        <v>-5.915295327263826</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.8377128274198293</v>
+        <v>0.7509499057038029</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.00805132563146</v>
+        <v>-1.156460098649205</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.512593665544205</v>
+        <v>2.423548401733559</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.063515405612509</v>
+        <v>-6.280422709902573</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.690916389370162</v>
+        <v>0.6041534676541356</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.304362109930473</v>
+        <v>-1.452770882948217</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.334061709970629</v>
+        <v>2.245016446159982</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.472104182793187</v>
+        <v>-6.689011487083252</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.5262424225126496</v>
+        <v>0.4394795007966232</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.712950887111151</v>
+        <v>-1.861359660128896</v>
       </c>
       <c r="G1864" t="n">
-        <v>2.087669987676981</v>
+        <v>1.998624723866334</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-6.885086666934281</v>
+        <v>-7.101993971224346</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.3562348613276729</v>
+        <v>0.2694719396116465</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.712950887111151</v>
+        <v>-1.861359660128896</v>
       </c>
       <c r="G1865" t="n">
-        <v>2.082855420148442</v>
+        <v>1.993810156337795</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.301478541221278</v>
+        <v>-7.518385845511343</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1876721622217512</v>
+        <v>0.1009092405057248</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.712950887111151</v>
+        <v>-1.861359660128896</v>
       </c>
       <c r="G1866" t="n">
-        <v>2.080849470757319</v>
+        <v>1.991804206946672</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.678155551751122</v>
+        <v>-7.895062856041188</v>
       </c>
       <c r="E1867" t="n">
-        <v>0.04726004867849243</v>
+        <v>-0.03950287303753397</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.712950887111151</v>
+        <v>-1.861359660128896</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.091108161425998</v>
+        <v>2.002062897615351</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.024030373735931</v>
+        <v>-8.240937678025997</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.09499031496973576</v>
+        <v>-0.1817532366857622</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.712950887111151</v>
+        <v>-1.861359660128896</v>
       </c>
       <c r="G1868" t="n">
-        <v>2.087207726571693</v>
+        <v>1.998162462761047</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.33685517298091</v>
+        <v>-8.553762477270975</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.2217153146127262</v>
+        <v>-0.3084782363287526</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.712950887111151</v>
+        <v>-1.861359660128896</v>
       </c>
       <c r="G1869" t="n">
-        <v>2.085612646626694</v>
+        <v>1.996567382816048</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.633516514791108</v>
+        <v>-8.850423819081174</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.3366008754075973</v>
+        <v>-0.4233637971236237</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.78169402284503</v>
+        <v>-1.930102795862774</v>
       </c>
       <c r="G1870" t="n">
-        <v>2.048145741115575</v>
+        <v>1.959100477304929</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.066865622901343</v>
+        <v>-9.283772927191409</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.5139668231860948</v>
+        <v>-0.6007297449021212</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.78169402284503</v>
+        <v>-1.930102795862774</v>
       </c>
       <c r="G1871" t="n">
-        <v>2.044119436581172</v>
+        <v>1.955074172770526</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.449867011643974</v>
+        <v>-9.66677431593404</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.6672694800047312</v>
+        <v>-0.7540324017207576</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.78169402284503</v>
+        <v>-1.930102795862774</v>
       </c>
       <c r="G1872" t="n">
-        <v>2.044017335259588</v>
+        <v>1.954972071448942</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-9.824852337815251</v>
+        <v>-10.04175964210532</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.8146920945018121</v>
+        <v>-0.9014550162178385</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.156679349016307</v>
+        <v>-2.305088122034052</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.821597655528252</v>
+        <v>1.732552391717605</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.18438266031925</v>
+        <v>-10.40128996460932</v>
       </c>
       <c r="E1874" t="n">
-        <v>-0.953153920205362</v>
+        <v>-1.039916841921388</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.156679349016307</v>
+        <v>-2.305088122034052</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.826947958826302</v>
+        <v>1.737902695015655</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.51078268898427</v>
+        <v>-10.72768999327433</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.07579791171419</v>
+        <v>-1.162560833430217</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.48307937768132</v>
+        <v>-2.631488150699065</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.639023961584472</v>
+        <v>1.549978697773825</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.72993165705846</v>
+        <v>-10.94683896134853</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.1604157483221</v>
+        <v>-1.247178670038127</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.702228345755518</v>
+        <v>-2.850637118773262</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.510576331361722</v>
+        <v>1.421531067551076</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.72624073210205</v>
+        <v>-10.94314803639212</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.158939378339536</v>
+        <v>-1.245702300055563</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.702228345755518</v>
+        <v>-2.850637118773262</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.510576331361722</v>
+        <v>1.421531067551076</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-10.93049890743192</v>
+        <v>-11.14740621172198</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.235129451352839</v>
+        <v>-1.321892373068866</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.829867290369507</v>
+        <v>-2.978276063387251</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.439506161711971</v>
+        <v>1.350460897901324</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.14853667906309</v>
+        <v>-11.36544398335316</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.317862005520874</v>
+        <v>-1.4046249272369</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.004638058465406</v>
+        <v>-3.15304683148315</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.339126255338868</v>
+        <v>1.250080991528221</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.07506684739564</v>
+        <v>-11.29197415168571</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.273102371360474</v>
+        <v>-1.3598652930765</v>
       </c>
       <c r="F1880" t="n">
-        <v>-2.931168226797957</v>
+        <v>-3.079576999815702</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.398579855832758</v>
+        <v>1.309534592022111</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.25019126478219</v>
+        <v>-11.46709856907225</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.328596917567574</v>
+        <v>-1.4153598392836</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.106292644184501</v>
+        <v>-3.254701417202245</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.308060426148348</v>
+        <v>1.219015162337702</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.48464335879668</v>
+        <v>-11.70155066308674</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.429596920074966</v>
+        <v>-1.516359841790992</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.106292644184501</v>
+        <v>-3.254701417202245</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.300841261246752</v>
+        <v>1.211795997436106</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.77244720333392</v>
+        <v>-11.98935450762398</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.551390648663837</v>
+        <v>-1.638153570379864</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.394096488721739</v>
+        <v>-3.542505261739484</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.121486763750434</v>
+        <v>1.032441499939787</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.00227165049774</v>
+        <v>-12.21917895478781</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.642204637690811</v>
+        <v>-1.728967559406837</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.5567440257919</v>
+        <v>-3.705152798809644</v>
       </c>
       <c r="G1884" t="n">
-        <v>1.025014031346893</v>
+        <v>0.9359687675362469</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.234300570234</v>
+        <v>-12.45120787452407</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.732322476956201</v>
+        <v>-1.819085398672228</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.618756722980323</v>
+        <v>-3.767165495998067</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9905001416629542</v>
+        <v>0.9014548778523075</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.18228505626519</v>
+        <v>-12.39919236055526</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.707525935682275</v>
+        <v>-1.794288857398302</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.618756722980323</v>
+        <v>-3.767165495998067</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.994490477349355</v>
+        <v>0.9054452135387083</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.32395689798931</v>
+        <v>-12.54086420227938</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.765669899270665</v>
+        <v>-1.852432820986691</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.618756722980323</v>
+        <v>-3.767165495998067</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9930152504506133</v>
+        <v>0.9039699866399666</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.42286363844859</v>
+        <v>-12.63977094273865</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.790179185289503</v>
+        <v>-1.876942107005529</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.717663463439598</v>
+        <v>-3.866072236457343</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9487246163399203</v>
+        <v>0.8596793525292736</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.22371153121149</v>
+        <v>-12.44061883550155</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.723569476041347</v>
+        <v>-1.810332397757373</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.552340937489785</v>
+        <v>-3.70074971050753</v>
       </c>
       <c r="G1889" t="n">
-        <v>1.034866998263126</v>
+        <v>0.9458217344524784</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-11.99786637849208</v>
+        <v>-12.21477368278214</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.623652341917374</v>
+        <v>-1.710415263633399</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.510414261902621</v>
+        <v>-3.658823034920366</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.069602076651632</v>
+        <v>0.9805568128409852</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.71159156616938</v>
+        <v>-11.92849887045945</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.508003272432237</v>
+        <v>-1.594766194148262</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.510414261902621</v>
+        <v>-3.658823034920366</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.070741221207691</v>
+        <v>0.9816959573970441</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.76448685421367</v>
+        <v>-11.98139415850373</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.526527613487843</v>
+        <v>-1.613290535203869</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.505458915814175</v>
+        <v>-3.65386768883192</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.076348203022866</v>
+        <v>0.9873029392122197</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.48057812328492</v>
+        <v>-11.69748542757498</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.407230416877708</v>
+        <v>-1.493993338593733</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.505458915814175</v>
+        <v>-3.65386768883192</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.082081907261503</v>
+        <v>0.9930366434508562</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.23359087309197</v>
+        <v>-11.45049817738203</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.318172779194392</v>
+        <v>-1.404935700910418</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.258471665621223</v>
+        <v>-3.406880438638968</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.220536994983409</v>
+        <v>1.131491731172762</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-10.9697540058879</v>
+        <v>-11.18666131017796</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.222521513625672</v>
+        <v>-1.309284435341697</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.258471665621223</v>
+        <v>-3.406880438638968</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.210653513670501</v>
+        <v>1.121608249859854</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.7025122050195</v>
+        <v>-10.91941950930956</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.117459353777686</v>
+        <v>-1.204222275493712</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.258471665621223</v>
+        <v>-3.406880438638968</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.208818953171128</v>
+        <v>1.119773689360481</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.42670304161902</v>
+        <v>-10.64361034590908</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.007436003390953</v>
+        <v>-1.094198925106979</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.16945235734249</v>
+        <v>-3.317861130360234</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.261930223164907</v>
+        <v>1.17288495935426</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.40274950064306</v>
+        <v>-10.61965680493312</v>
       </c>
       <c r="E1898" t="n">
-        <v>-0.9971860808550761</v>
+        <v>-1.083949002571102</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.145498816366532</v>
+        <v>-3.293907589384277</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.276970853895975</v>
+        <v>1.187925590085328</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.13868956232026</v>
+        <v>-10.35559686661033</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9048224216877099</v>
+        <v>-0.9915853434037354</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.881438878043736</v>
+        <v>-3.029847651061481</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.4221465007279</v>
+        <v>1.333101236917254</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.431609938815424</v>
+        <v>-9.648517243105488</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6247776059460759</v>
+        <v>-0.7115405276621014</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.881438878043736</v>
+        <v>-3.029847651061481</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.4193594670676</v>
+        <v>1.330314203256953</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.391425640449233</v>
+        <v>-9.608332944739297</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6083602627117584</v>
+        <v>-0.6951231844277839</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.841254579677545</v>
+        <v>-2.98966335269529</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.443813669975156</v>
+        <v>1.354768406164509</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.311355844911429</v>
+        <v>-9.528263149201493</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.5769655232758795</v>
+        <v>-0.6637284449919054</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.761184784139741</v>
+        <v>-2.909593557157486</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.491222368518595</v>
+        <v>1.402177104707948</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.077874622681829</v>
+        <v>-9.294781926971893</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.4756486055461875</v>
+        <v>-0.562411527262213</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.527703561910143</v>
+        <v>-2.676112334927887</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.639235530694206</v>
+        <v>1.550190266883559</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.898166092537956</v>
+        <v>-9.11507339682802</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4066574038015971</v>
+        <v>-0.493420325517623</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.470532057747447</v>
+        <v>-2.618940830765192</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.670646222878865</v>
+        <v>1.581600959068218</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.765890618907068</v>
+        <v>-8.982797923197133</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3583797276022151</v>
+        <v>-0.4451426493182411</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.33825658411656</v>
+        <v>-2.486665357134305</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.745378993804424</v>
+        <v>1.656333729993777</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.575290944233915</v>
+        <v>-8.792198248523979</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.2793247970453172</v>
+        <v>-0.3660877187613427</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.147656909443408</v>
+        <v>-2.296065682461153</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.862553859295952</v>
+        <v>1.773508595485305</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.326291145550334</v>
+        <v>-8.543198449840398</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.166818536348226</v>
+        <v>-0.2535814580642515</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.147656909443408</v>
+        <v>-2.296065682461153</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.875460200519611</v>
+        <v>1.786414936708964</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.431881135323438</v>
+        <v>-8.648788439613503</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3370304618566866</v>
+        <v>-0.4237933835727121</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.253246899216512</v>
+        <v>-2.401655672234257</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.684130277056529</v>
+        <v>1.595085013245882</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.450616037442035</v>
+        <v>-8.6675233417321</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.295980080827039</v>
+        <v>-0.3827430025430645</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.253246899216512</v>
+        <v>-2.401655672234257</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.732674618933616</v>
+        <v>1.643629355122969</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.173877862771223</v>
+        <v>-8.390785167061287</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.1819057989727191</v>
+        <v>-0.2686687206887446</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.071430238106586</v>
+        <v>-2.219839011124331</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.845143627585566</v>
+        <v>1.756098363774919</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.046985456336152</v>
+        <v>-8.263892760626216</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.139862822652169</v>
+        <v>-0.2266257443681949</v>
       </c>
       <c r="F1911" t="n">
-        <v>-1.944537831671517</v>
+        <v>-2.092946604689261</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.91256508519313</v>
+        <v>1.823519821382483</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.003437049565463</v>
+        <v>-8.220344353855525</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.129404072038986</v>
+        <v>-0.2161669937550115</v>
       </c>
       <c r="F1912" t="n">
-        <v>-1.944537831671517</v>
+        <v>-2.092946604689261</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.905604473098036</v>
+        <v>1.816559209287389</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.761288656111605</v>
+        <v>-7.978195960401667</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.01808236027629961</v>
+        <v>-0.1048452819923251</v>
       </c>
       <c r="F1913" t="n">
-        <v>-1.944537831671517</v>
+        <v>-2.092946604689261</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.92006682747918</v>
+        <v>1.831021563668533</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.698059284343256</v>
+        <v>-7.914966588633319</v>
       </c>
       <c r="E1914" t="n">
-        <v>0.001741508890234389</v>
+        <v>-0.08502141282579068</v>
       </c>
       <c r="F1914" t="n">
-        <v>-1.944537831671517</v>
+        <v>-2.092946604689261</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.914598947938375</v>
+        <v>1.825553684127728</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.51157159196625</v>
+        <v>-7.728478896256313</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.07383467985161385</v>
+        <v>-0.01292824186441166</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.75805013929451</v>
+        <v>-1.906458912312255</v>
       </c>
       <c r="G1915" t="n">
-        <v>2.023989657375155</v>
+        <v>1.934944393564508</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.490422393062807</v>
+        <v>-7.707329697352869</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.08999533765031664</v>
+        <v>0.003232415934291577</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.736900940391067</v>
+        <v>-1.885309713408812</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.044380154954547</v>
+        <v>1.9553348911439</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.246656951079363</v>
+        <v>-7.463564255369425</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1832822227907451</v>
+        <v>0.09651930107472007</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.736900940391067</v>
+        <v>-1.885309713408812</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.040160863301598</v>
+        <v>1.951115599490951</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-6.982628883886103</v>
+        <v>-7.314149659730926</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2910177635880649</v>
+        <v>0.1584094532501354</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.535035541575113</v>
+        <v>-1.841075588984271</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.163404416511185</v>
+        <v>1.979780388065691</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.732778489937028</v>
+        <v>-7.064299265781852</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3836999961513969</v>
+        <v>0.2510916858134675</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.535035541575113</v>
+        <v>-1.841075588984271</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.156146491494888</v>
+        <v>1.972522463049393</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.42921100093305</v>
+        <v>-6.760731776777873</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.5087261152736371</v>
+        <v>0.3761178049357077</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.535035541575113</v>
+        <v>-1.841075588984271</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.159745615015536</v>
+        <v>1.976121586570042</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.355731092081036</v>
+        <v>-6.687251867925859</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5514455848689965</v>
+        <v>0.4188372745310667</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.461555632723099</v>
+        <v>-1.767595680132256</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.217161066381299</v>
+        <v>2.033537037935805</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.130698092412213</v>
+        <v>-6.462218868257036</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6404792623528226</v>
+        <v>0.5078709520148932</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.236522633054276</v>
+        <v>-1.542562680463433</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.351201343798889</v>
+        <v>2.167577315353395</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.916063714775806</v>
+        <v>-6.247584490620629</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7310278144617026</v>
+        <v>0.5984195041237732</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.021888255417869</v>
+        <v>-1.327928302827027</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.484676771435051</v>
+        <v>2.301052742989556</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.649463357801454</v>
+        <v>-5.980984133646277</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.8188622160352392</v>
+        <v>0.6862539056973094</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.021888255417869</v>
+        <v>-1.327928302827027</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.465871030218846</v>
+        <v>2.282247001773352</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.409032860996594</v>
+        <v>-5.740553636841417</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.9167774913820605</v>
+        <v>0.7841691810441311</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.7814577586130089</v>
+        <v>-1.087497806022166</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.61187240492664</v>
+        <v>2.428248376481146</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.166242053347148</v>
+        <v>-5.497762829191972</v>
       </c>
       <c r="E1926" t="n">
-        <v>1.017823128276659</v>
+        <v>0.8852148179387291</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.7814577586130089</v>
+        <v>-1.087497806022166</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.61580171876146</v>
+        <v>2.432177690315966</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.926636961740059</v>
+        <v>-5.258157737584883</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.114343748836835</v>
+        <v>0.9817354384989048</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7144098109445144</v>
+        <v>-1.020449858353672</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.656709071279897</v>
+        <v>2.473085042834402</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.683981373316896</v>
+        <v>-5.015502149161719</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.208404055426094</v>
+        <v>1.075795745088164</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7144098109445144</v>
+        <v>-1.020449858353672</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.65370714249989</v>
+        <v>2.470083114054396</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.463960575279885</v>
+        <v>-4.795481351124709</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.297991411651512</v>
+        <v>1.165383101313582</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.5731899658765341</v>
+        <v>-0.8792300132856916</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.740018086551293</v>
+        <v>2.556394058105798</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.264711945375076</v>
+        <v>-4.596232721219899</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.393585046415259</v>
+        <v>1.260976736077329</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.5731899658765341</v>
+        <v>-0.8792300132856916</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.755912269353116</v>
+        <v>2.572288240907621</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.105196841855706</v>
+        <v>-4.43671761770053</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.458536932263309</v>
+        <v>1.325928621925379</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4136748623571642</v>
+        <v>-0.7197149097663217</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.85276717590504</v>
+        <v>2.669143147459546</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-3.960524696755969</v>
+        <v>-4.292045472600792</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.526493892864643</v>
+        <v>1.393885582526714</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.2690027172574268</v>
+        <v>-0.5750427646665843</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.949658565526322</v>
+        <v>2.766034537080828</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-3.942755237825013</v>
+        <v>-4.274276013669836</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.448941368523747</v>
+        <v>1.316333058185818</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.2512332583264713</v>
+        <v>-0.5572733057356287</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.875659932971617</v>
+        <v>2.692035904526123</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.855955740046005</v>
+        <v>-4.187476515890827</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.506061660957917</v>
+        <v>1.373453350619988</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.2512332583264713</v>
+        <v>-0.5572733057356287</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.898060426294183</v>
+        <v>2.714436397848689</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900687</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.847814137659847</v>
+        <v>-4.087783901161815</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.509390703285792</v>
+        <v>1.413402797885004</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.243091655940313</v>
+        <v>-0.457580691006617</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.90301778909929</v>
+        <v>2.774324368059508</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.853429626382484</v>
+        <v>3.635130337990593</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.2369261577697</v>
+        <v>3.103308429829164</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.847814137659847</v>
+        <v>-4.087783901161815</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.509390703285792</v>
+        <v>1.413402797885004</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.243091655940313</v>
+        <v>-0.457580691006617</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.229989954756068</v>
+        <v>3.096372226815532</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.8%</t>
+          <t>-79.5%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>118.9%</t>
+          <t>119.3%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.1%</t>
+          <t>97.9%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.3%</t>
+          <t>29.6%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.9%</t>
+          <t>-75.6%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>98.6%</t>
+          <t>99.0%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>795.6%</t>
+          <t>798.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.4%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-570.4%</t>
+          <t>-560.1%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.1%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.6%</t>
+          <t>55.8%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.20</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.5%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.1%</t>
+          <t>46.4%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.5%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>9.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.5%</t>
+          <t>46.6%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-27.2%</t>
+          <t>-25.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-17.9%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-234.9%</t>
+          <t>-230.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-32.6%</t>
+          <t>-30.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>71.9%</t>
+          <t>72.4%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.43</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>68.9%</t>
+          <t>70.4%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-329.8%</t>
+          <t>-330.2%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.1%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-26.0%</t>
+          <t>-24.3%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>59.7%</t>
+          <t>60.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>34.3%</t>
+          <t>36.4%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-158.7%</t>
+          <t>-159.4%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-269.8%</t>
+          <t>-254.4%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>54.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.8%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.00</t>
+          <t>1.02</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>43.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-198.3%</t>
+          <t>-198.5%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>50.1%</t>
+          <t>49.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>45.0%</t>
+          <t>44.4%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1496,17 +1496,17 @@
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.5%</t>
+          <t>-18.0%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.8%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9307309757871566</v>
+        <v>-0.9430734250892931</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.744297851921341</v>
+        <v>2.739360872200487</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.161150391720504</v>
+        <v>1.15709845023947</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.813636901582254</v>
+        <v>3.811205736693633</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.138735034140234</v>
+        <v>-1.15107748344237</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.665988373134036</v>
+        <v>2.661051393413181</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.161150391720504</v>
+        <v>1.15709845023947</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.818529046136179</v>
+        <v>3.816097881247559</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.409134996849119</v>
+        <v>-1.421477446151256</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.552909844388469</v>
+        <v>2.547972864667615</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.890750429011619</v>
+        <v>0.8866984875305843</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.651370524848836</v>
+        <v>3.648939359960215</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.748293374437641</v>
+        <v>-1.760635823739778</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.41033079265951</v>
+        <v>2.405393812938655</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.551592051423097</v>
+        <v>0.5475401099420623</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.440959797602172</v>
+        <v>3.438528632713551</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213496</v>
+        <v>3.223539378213497</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.07631059616512</v>
+        <v>-2.088653045467256</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.299462193707286</v>
+        <v>2.294525213986432</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2235748296956178</v>
+        <v>0.2195228882145831</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.264487754304453</v>
+        <v>3.262056589415832</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.569635467700298</v>
+        <v>-2.581977917002435</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.110230995501784</v>
+        <v>2.105294015780929</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1185887154559991</v>
+        <v>0.1145367739749644</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.20959483616925</v>
+        <v>3.207163671280629</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.062020495724395</v>
+        <v>-3.074362945026532</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.914383376335877</v>
+        <v>1.909446396615023</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3737963125680976</v>
+        <v>-0.3778482540491324</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.915270211398524</v>
+        <v>2.912839046509903</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.447200886654468</v>
+        <v>-3.459543335956604</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.758853758776711</v>
+        <v>1.753916779055857</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3737963125680976</v>
+        <v>-0.3778482540491324</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.913812750211388</v>
+        <v>2.911381585322767</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347055</v>
+        <v>3.299136146347056</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.790883659881131</v>
+        <v>-3.803226109183267</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.623149772940662</v>
+        <v>1.618212793219808</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4817023645953158</v>
+        <v>-0.4857543060763506</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.850838242449673</v>
+        <v>2.848407077561052</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130017</v>
+        <v>3.287377576130018</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.148534010119478</v>
+        <v>-4.160876459421615</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.476195691501581</v>
+        <v>1.471258711780727</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8393527148336639</v>
+        <v>-0.8434046563146986</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.632354090962922</v>
+        <v>2.629922926074301</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.457768113115529</v>
+        <v>-4.470110562417666</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.35427497700342</v>
+        <v>1.349337997282566</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8393527148336639</v>
+        <v>-0.8434046563146986</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.634127017663181</v>
+        <v>2.63169585277456</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.889573906265317</v>
+        <v>-4.901916355567454</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.16788554721091</v>
+        <v>1.162948567490055</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9757702112749309</v>
+        <v>-0.9798221527559656</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.538609407265826</v>
+        <v>2.536178242377205</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.21600643513306</v>
+        <v>-5.228348884435198</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.025597310665903</v>
+        <v>1.020660330945048</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.058238461782079</v>
+        <v>-1.062290403263114</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.477413231963627</v>
+        <v>2.474982067075007</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.551669082363513</v>
+        <v>-5.56401153166565</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8899128434296868</v>
+        <v>0.8849758637088323</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.058238461782079</v>
+        <v>-1.062290403263114</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.475993823619592</v>
+        <v>2.473562658730972</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309423</v>
+        <v>3.311086391309424</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.915295327263826</v>
+        <v>-5.927637776565963</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7509499057038029</v>
+        <v>0.7460129259829484</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.156460098649205</v>
+        <v>-1.16051204013024</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.423548401733559</v>
+        <v>2.421117236844938</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970903</v>
+        <v>3.304715716970905</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.280422709902573</v>
+        <v>-6.29276515920471</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.6041534676541356</v>
+        <v>0.5992164879332811</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.452770882948217</v>
+        <v>-1.456822824429252</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.245016446159982</v>
+        <v>2.242585281271362</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330521</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.689011487083252</v>
+        <v>-6.701353936385388</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4394795007966232</v>
+        <v>0.4345425210757692</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.861359660128896</v>
+        <v>-1.86541160160993</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.998624723866334</v>
+        <v>1.996193558977714</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191736</v>
+        <v>3.302618194191738</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.101993971224346</v>
+        <v>-7.114336420526482</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2694719396116465</v>
+        <v>0.264534959890792</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.861359660128896</v>
+        <v>-1.86541160160993</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.993810156337795</v>
+        <v>1.991378991449174</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108638</v>
+        <v>3.30502326510864</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.518385845511343</v>
+        <v>-7.530728294813479</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.1009092405057248</v>
+        <v>0.09597226078487076</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.861359660128896</v>
+        <v>-1.86541160160993</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.991804206946672</v>
+        <v>1.989373042058052</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.34137872309782</v>
+        <v>3.341378723097822</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.895062856041188</v>
+        <v>-7.907405305343324</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.03950287303753397</v>
+        <v>-0.04443985275838802</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.861359660128896</v>
+        <v>-1.86541160160993</v>
       </c>
       <c r="G1867" t="n">
-        <v>2.002062897615351</v>
+        <v>1.999631732726731</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094116</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.240937678025997</v>
+        <v>-8.253280127328132</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1817532366857622</v>
+        <v>-0.1866902164066162</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.861359660128896</v>
+        <v>-1.86541160160993</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.998162462761047</v>
+        <v>1.995731297872426</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199286</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.553762477270975</v>
+        <v>-8.566104926573111</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3084782363287526</v>
+        <v>-0.3134152160496071</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.861359660128896</v>
+        <v>-1.86541160160993</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.996567382816048</v>
+        <v>1.994136217927427</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969593</v>
+        <v>3.424633354969595</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.850423819081174</v>
+        <v>-8.862766268383309</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4233637971236237</v>
+        <v>-0.4283007768444782</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.930102795862774</v>
+        <v>-1.934154737343809</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.959100477304929</v>
+        <v>1.956669312416308</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923086</v>
+        <v>3.419979433923088</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.283772927191409</v>
+        <v>-9.296115376493544</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6007297449021212</v>
+        <v>-0.6056667246229752</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.930102795862774</v>
+        <v>-1.934154737343809</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.955074172770526</v>
+        <v>1.952643007881905</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.45810009129775</v>
+        <v>3.458100091297752</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.66677431593404</v>
+        <v>-9.679116765236175</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7540324017207576</v>
+        <v>-0.7589693814416116</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.930102795862774</v>
+        <v>-1.934154737343809</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.954972071448942</v>
+        <v>1.952540906560321</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317616</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.04175964210532</v>
+        <v>-10.05410209140745</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9014550162178385</v>
+        <v>-0.9063919959386921</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.305088122034052</v>
+        <v>-2.309140063515086</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.732552391717605</v>
+        <v>1.730121226828985</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.50351550673717</v>
+        <v>3.503515506737172</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.40128996460932</v>
+        <v>-10.41363241391145</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.039916841921388</v>
+        <v>-1.044853821642243</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.305088122034052</v>
+        <v>-2.309140063515086</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.737902695015655</v>
+        <v>1.735471530127035</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341313</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.72768999327433</v>
+        <v>-10.74003244257647</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.162560833430217</v>
+        <v>-1.16749781315107</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.631488150699065</v>
+        <v>-2.635540092180099</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.549978697773825</v>
+        <v>1.547547532885204</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.94683896134853</v>
+        <v>-10.95918141065066</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.247178670038127</v>
+        <v>-1.252115649758981</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.850637118773262</v>
+        <v>-2.854689060254297</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.421531067551076</v>
+        <v>1.419099902662455</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407492</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.94314803639212</v>
+        <v>-10.95549048569425</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.245702300055563</v>
+        <v>-1.250639279776416</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.850637118773262</v>
+        <v>-2.854689060254297</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.421531067551076</v>
+        <v>1.419099902662455</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611695</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.14740621172198</v>
+        <v>-11.15974866102412</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.321892373068866</v>
+        <v>-1.326829352789719</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.978276063387251</v>
+        <v>-2.982328004868286</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.350460897901324</v>
+        <v>1.348029733012704</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.36544398335316</v>
+        <v>-11.3777864326553</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.4046249272369</v>
+        <v>-1.409561906957755</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.15304683148315</v>
+        <v>-3.157098772964185</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.250080991528221</v>
+        <v>1.2476498266396</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910627</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.29197415168571</v>
+        <v>-11.30431660098785</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.3598652930765</v>
+        <v>-1.364802272797354</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.079576999815702</v>
+        <v>-3.083628941296736</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.309534592022111</v>
+        <v>1.307103427133491</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078594</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.46709856907225</v>
+        <v>-11.47944101837439</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.4153598392836</v>
+        <v>-1.420296819004454</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.254701417202245</v>
+        <v>-3.25875335868328</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.219015162337702</v>
+        <v>1.216583997449081</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880266</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.70155066308674</v>
+        <v>-11.71389311238888</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.516359841790992</v>
+        <v>-1.521296821511846</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.254701417202245</v>
+        <v>-3.25875335868328</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.211795997436106</v>
+        <v>1.209364832547485</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.48068891723439</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-11.98935450762398</v>
+        <v>-12.00169695692612</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.638153570379864</v>
+        <v>-1.643090550100718</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.542505261739484</v>
+        <v>-3.546557203220518</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.032441499939787</v>
+        <v>1.030010335051166</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.49371243886058</v>
+        <v>3.493712438860582</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.21917895478781</v>
+        <v>-12.23152140408994</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.728967559406837</v>
+        <v>-1.733904539127692</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.705152798809644</v>
+        <v>-3.709204740290679</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9359687675362469</v>
+        <v>0.9335376026476259</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767394</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.45120787452407</v>
+        <v>-12.4635503238262</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.819085398672228</v>
+        <v>-1.824022378393082</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.767165495998067</v>
+        <v>-3.771217437479102</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.9014548778523075</v>
+        <v>0.8990237129636869</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.573670449792541</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.39919236055526</v>
+        <v>-12.41153480985739</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.794288857398302</v>
+        <v>-1.799225837119156</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.767165495998067</v>
+        <v>-3.771217437479102</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9054452135387083</v>
+        <v>0.9030140486500877</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628917</v>
+        <v>3.600034689628918</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.54086420227938</v>
+        <v>-12.55320665158151</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.852432820986691</v>
+        <v>-1.857369800707546</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.767165495998067</v>
+        <v>-3.771217437479102</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.9039699866399666</v>
+        <v>0.901538821751346</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410716</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.63977094273865</v>
+        <v>-12.65211339204079</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.876942107005529</v>
+        <v>-1.881879086726383</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.866072236457343</v>
+        <v>-3.870124177938377</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.8596793525292736</v>
+        <v>0.857248187640653</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240576</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.44061883550155</v>
+        <v>-12.45296128480369</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.810332397757373</v>
+        <v>-1.815269377478227</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.70074971050753</v>
+        <v>-3.704801651988564</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9458217344524784</v>
+        <v>0.9433905695638583</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085279</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.21477368278214</v>
+        <v>-12.22711613208428</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.710415263633399</v>
+        <v>-1.715352243354254</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.658823034920366</v>
+        <v>-3.6628749764014</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.9805568128409852</v>
+        <v>0.978125647952365</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282098</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.92849887045945</v>
+        <v>-11.94084131976158</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.594766194148262</v>
+        <v>-1.599703173869117</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.658823034920366</v>
+        <v>-3.6628749764014</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9816959573970441</v>
+        <v>0.9792647925084239</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116213</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.98139415850373</v>
+        <v>-11.99373660780587</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.613290535203869</v>
+        <v>-1.618227514924723</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.65386768883192</v>
+        <v>-3.657919630312954</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9873029392122197</v>
+        <v>0.9848717743235991</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081564</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.69748542757498</v>
+        <v>-11.70982787687712</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.493993338593733</v>
+        <v>-1.498930318314588</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.65386768883192</v>
+        <v>-3.657919630312954</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9930366434508562</v>
+        <v>0.9906054785622356</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425325</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.45049817738203</v>
+        <v>-11.46284062668417</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.404935700910418</v>
+        <v>-1.409872680631272</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.406880438638968</v>
+        <v>-3.410932380120002</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.131491731172762</v>
+        <v>1.129060566284142</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.18666131017796</v>
+        <v>-11.1990037594801</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.309284435341697</v>
+        <v>-1.314221415062552</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.406880438638968</v>
+        <v>-3.410932380120002</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.121608249859854</v>
+        <v>1.119177084971234</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.91941950930956</v>
+        <v>-10.9317619586117</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.204222275493712</v>
+        <v>-1.209159255214566</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.406880438638968</v>
+        <v>-3.410932380120002</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.119773689360481</v>
+        <v>1.11734252447186</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781946</v>
+        <v>3.784680945781947</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.64361034590908</v>
+        <v>-10.65595279521122</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.094198925106979</v>
+        <v>-1.099135904827833</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.317861130360234</v>
+        <v>-3.321913071841268</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.17288495935426</v>
+        <v>1.17045379446564</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567241</v>
+        <v>3.800825778567242</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.61965680493312</v>
+        <v>-10.63199925423526</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.083949002571102</v>
+        <v>-1.088885982291956</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.293907589384277</v>
+        <v>-3.297959530865311</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.187925590085328</v>
+        <v>1.185494425196708</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487771</v>
+        <v>3.789307536487772</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.35559686661033</v>
+        <v>-10.36793931591246</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9915853434037354</v>
+        <v>-0.9965223231245899</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.029847651061481</v>
+        <v>-3.033899592542515</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.333101236917254</v>
+        <v>1.330670072028633</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.648517243105488</v>
+        <v>-9.660859692407623</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7115405276621014</v>
+        <v>-0.7164775073829555</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.029847651061481</v>
+        <v>-3.033899592542515</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.330314203256953</v>
+        <v>1.327883038368332</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.608332944739297</v>
+        <v>-9.620675394041433</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.6951231844277839</v>
+        <v>-0.7000601641486379</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.98966335269529</v>
+        <v>-2.993715294176324</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.354768406164509</v>
+        <v>1.352337241275888</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.528263149201493</v>
+        <v>-9.540605598503628</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6637284449919054</v>
+        <v>-0.6686654247127595</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.909593557157486</v>
+        <v>-2.91364549863852</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.402177104707948</v>
+        <v>1.399745939819327</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.294781926971893</v>
+        <v>-9.307124376274029</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.562411527262213</v>
+        <v>-0.567348506983067</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.676112334927887</v>
+        <v>-2.680164276408922</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.550190266883559</v>
+        <v>1.547759101994939</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.11507339682802</v>
+        <v>-9.127415846130155</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.493420325517623</v>
+        <v>-0.4983573052384771</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.618940830765192</v>
+        <v>-2.622992772246226</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.581600959068218</v>
+        <v>1.579169794179597</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.982797923197133</v>
+        <v>-8.995140372499268</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4451426493182411</v>
+        <v>-0.4500796290390952</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.486665357134305</v>
+        <v>-2.490717298615339</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.656333729993777</v>
+        <v>1.653902565105156</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.792198248523979</v>
+        <v>-8.804540697826114</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3660877187613427</v>
+        <v>-0.3710246984821968</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.296065682461153</v>
+        <v>-2.300117623942187</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.773508595485305</v>
+        <v>1.771077430596685</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.543198449840398</v>
+        <v>-8.555540899142533</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.2535814580642515</v>
+        <v>-0.258518437785106</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.296065682461153</v>
+        <v>-2.300117623942187</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.786414936708964</v>
+        <v>1.783983771820343</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077643</v>
+        <v>3.692928280077642</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.648788439613503</v>
+        <v>-8.661130888915638</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4237933835727121</v>
+        <v>-0.4287303632935662</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.401655672234257</v>
+        <v>-2.405707613715291</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.595085013245882</v>
+        <v>1.592653848357262</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.6675233417321</v>
+        <v>-8.679865791034235</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3827430025430645</v>
+        <v>-0.3876799822639185</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.401655672234257</v>
+        <v>-2.405707613715291</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.643629355122969</v>
+        <v>1.641198190234348</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.390785167061287</v>
+        <v>-8.403127616363422</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2686687206887446</v>
+        <v>-0.2736057004095991</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.219839011124331</v>
+        <v>-2.223890952605365</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.756098363774919</v>
+        <v>1.753667198886298</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.263892760626216</v>
+        <v>-8.276235209928352</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.2266257443681949</v>
+        <v>-0.231562724089049</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.092946604689261</v>
+        <v>-2.096998546170295</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.823519821382483</v>
+        <v>1.821088656493862</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.220344353855525</v>
+        <v>-8.232686803157661</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2161669937550115</v>
+        <v>-0.2211039734758655</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.092946604689261</v>
+        <v>-2.096998546170295</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.816559209287389</v>
+        <v>1.814128044398769</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.978195960401667</v>
+        <v>-7.990538409703802</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1048452819923251</v>
+        <v>-0.1097822617131792</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.092946604689261</v>
+        <v>-2.096998546170295</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.831021563668533</v>
+        <v>1.828590398779912</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.914966588633319</v>
+        <v>-7.927309037935454</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08502141282579068</v>
+        <v>-0.08995839254664473</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.092946604689261</v>
+        <v>-2.096998546170295</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.825553684127728</v>
+        <v>1.823122519239107</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.728478896256313</v>
+        <v>-7.740821345558448</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01292824186441166</v>
+        <v>-0.01786522158526571</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.906458912312255</v>
+        <v>-1.910510853793289</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.934944393564508</v>
+        <v>1.932513228675888</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.707329697352869</v>
+        <v>-7.719672146655005</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.003232415934291577</v>
+        <v>-0.001704563786562474</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.885309713408812</v>
+        <v>-1.889361654889846</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.9553348911439</v>
+        <v>1.95290372625528</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.463564255369425</v>
+        <v>-7.47590670467156</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.09651930107472007</v>
+        <v>0.09158232135386557</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.885309713408812</v>
+        <v>-1.889361654889846</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.951115599490951</v>
+        <v>1.94868443460233</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.314149659730926</v>
+        <v>-7.2118786374783</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1584094532501354</v>
+        <v>0.1993178621511857</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.841075588984271</v>
+        <v>-1.687496256073892</v>
       </c>
       <c r="G1918" t="n">
-        <v>1.979780388065691</v>
+        <v>2.071927987811918</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-7.064299265781852</v>
+        <v>-6.962028243529225</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2510916858134675</v>
+        <v>0.2920000947145178</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.841075588984271</v>
+        <v>-1.687496256073892</v>
       </c>
       <c r="G1919" t="n">
-        <v>1.972522463049393</v>
+        <v>2.064670062795621</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.760731776777873</v>
+        <v>-6.658460754525247</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.3761178049357077</v>
+        <v>0.417026213836758</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.841075588984271</v>
+        <v>-1.687496256073892</v>
       </c>
       <c r="G1920" t="n">
-        <v>1.976121586570042</v>
+        <v>2.068269186316269</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862982</v>
+        <v>3.780930335862983</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.687251867925859</v>
+        <v>-6.584980845673233</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4188372745310667</v>
+        <v>0.4597456834321174</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.767595680132256</v>
+        <v>-1.614016347221878</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.033537037935805</v>
+        <v>2.125684637682031</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102777</v>
+        <v>3.773761647102778</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.462218868257036</v>
+        <v>-6.35994784600441</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5078709520148932</v>
+        <v>0.5487793609159435</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.542562680463433</v>
+        <v>-1.388983347553055</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.167577315353395</v>
+        <v>2.259724915099622</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.76461430435307</v>
+        <v>3.764614304353071</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.247584490620629</v>
+        <v>-6.145313468368003</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.5984195041237732</v>
+        <v>0.6393279130248235</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.327928302827027</v>
+        <v>-1.174348969916648</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.301052742989556</v>
+        <v>2.393200342735784</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544778</v>
+        <v>3.798811195544779</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.980984133646277</v>
+        <v>-5.878713111393651</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.6862539056973094</v>
+        <v>0.7271623145983601</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.327928302827027</v>
+        <v>-1.174348969916648</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.282247001773352</v>
+        <v>2.374394601519579</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.79769130871229</v>
+        <v>3.797691308712292</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.740553636841417</v>
+        <v>-5.638282614588791</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.7841691810441311</v>
+        <v>0.8250775899451814</v>
       </c>
       <c r="F1925" t="n">
-        <v>-1.087497806022166</v>
+        <v>-0.9339184731117878</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.428248376481146</v>
+        <v>2.520395976227373</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.82158993383768</v>
+        <v>3.821589933837682</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.497762829191972</v>
+        <v>-5.395491806939345</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.8852148179387291</v>
+        <v>0.9261232268397799</v>
       </c>
       <c r="F1926" t="n">
-        <v>-1.087497806022166</v>
+        <v>-0.9339184731117878</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.432177690315966</v>
+        <v>2.524325290062193</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349962</v>
+        <v>3.822323422349964</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.258157737584883</v>
+        <v>-5.155886715332256</v>
       </c>
       <c r="E1927" t="n">
-        <v>0.9817354384989048</v>
+        <v>1.022643847399956</v>
       </c>
       <c r="F1927" t="n">
-        <v>-1.020449858353672</v>
+        <v>-0.8668705254432932</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.473085042834402</v>
+        <v>2.56523264258063</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972335</v>
+        <v>3.848613050972337</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-5.015502149161719</v>
+        <v>-4.913231126909093</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.075795745088164</v>
+        <v>1.116704153989214</v>
       </c>
       <c r="F1928" t="n">
-        <v>-1.020449858353672</v>
+        <v>-0.8668705254432932</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.470083114054396</v>
+        <v>2.562230713800623</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145935</v>
+        <v>3.818665376145937</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.795481351124709</v>
+        <v>-4.693210328872082</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.165383101313582</v>
+        <v>1.206291510214633</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.8792300132856916</v>
+        <v>-0.725650680375313</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.556394058105798</v>
+        <v>2.648541657852026</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009947</v>
+        <v>3.843270952009949</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.596232721219899</v>
+        <v>-4.493961698967273</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.260976736077329</v>
+        <v>1.30188514497838</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.8792300132856916</v>
+        <v>-0.725650680375313</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.572288240907621</v>
+        <v>2.664435840653849</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966255</v>
+        <v>3.845043810966256</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.43671761770053</v>
+        <v>-4.334446595447903</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.325928621925379</v>
+        <v>1.366837030826429</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.7197149097663217</v>
+        <v>-0.5661355768559431</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.669143147459546</v>
+        <v>2.761290747205773</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046991</v>
+        <v>3.791269976046992</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.292045472600792</v>
+        <v>-4.189774450348166</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.393885582526714</v>
+        <v>1.434793991427764</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.5750427646665843</v>
+        <v>-0.4214634317562057</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.766034537080828</v>
+        <v>2.858182136827055</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412097</v>
+        <v>3.735835647412099</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.274276013669836</v>
+        <v>-4.17200499141721</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.316333058185818</v>
+        <v>1.357241467086868</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.5572733057356287</v>
+        <v>-0.4036939728252501</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.692035904526123</v>
+        <v>2.78418350427235</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.76264390214451</v>
+        <v>3.762643902144512</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.187476515890827</v>
+        <v>-4.085205493638201</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.373453350619988</v>
+        <v>1.414361759521038</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.5572733057356287</v>
+        <v>-0.4036939728252501</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.714436397848689</v>
+        <v>2.806583997594916</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900688</v>
+        <v>3.729142822900689</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-4.087783901161815</v>
+        <v>-3.985512878909189</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.413402797885004</v>
+        <v>1.454311206786055</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.457580691006617</v>
+        <v>-0.3040013580962383</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.774324368059508</v>
+        <v>2.866471967805735</v>
       </c>
     </row>
     <row r="1936">
@@ -46079,13 +46079,13 @@
         <v>3.103308429829164</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.087783901161815</v>
+        <v>-3.985512878909189</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.413402797885004</v>
+        <v>1.454311206786055</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.457580691006617</v>
+        <v>-0.3040013580962383</v>
       </c>
       <c r="G1936" t="n">
         <v>3.096372226815532</v>

--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>58.8%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.3%</t>
+          <t>65.1%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.3%</t>
+          <t>67.6%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -666,22 +666,22 @@
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>-19.9%</t>
+          <t>-19.5%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-17.5%</t>
+          <t>-15.4%</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.7%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-11.9%</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.4%</t>
+          <t>55.8%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>72.0%</t>
+          <t>70.7%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.1%</t>
+          <t>29.0%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>27.8%</t>
+          <t>27.6%</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -834,12 +834,12 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-3.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>58.2%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.3%</t>
+          <t>23.2%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.5</t>
+          <t>2.4</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.0%</t>
+          <t>-4.9%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-1.3%</t>
+          <t>-5.6%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.5%</t>
+          <t>-79.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.3%</t>
+          <t>119.6%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.2%</t>
+          <t>139.7%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>97.9%</t>
+          <t>98.0%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,15 +969,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-722.5%</t>
+          <t>-705.7%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -992,12 +992,12 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>29.6%</t>
+          <t>29.1%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.6%</t>
+          <t>-58.0%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1012,7 +1012,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>99.0%</t>
+          <t>99.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>798.5%</t>
+          <t>802.4%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.4%</t>
+          <t>-2.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-560.1%</t>
+          <t>-562.3%</t>
         </is>
       </c>
     </row>
@@ -1079,7 +1079,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>66.7%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1127,15 +1127,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-27</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-283.6%</t>
+          <t>-276.9%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.5%</t>
+          <t>14.4%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.8%</t>
+          <t>-45.3%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,12 +1165,12 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.6%</t>
+          <t>46.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-25.4%</t>
+          <t>-20.8%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-19.8%</t>
+          <t>-74.0%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.8%</t>
+          <t>-230.6%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.9%</t>
+          <t>-30.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.43</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.4%</t>
+          <t>73.3%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.4%</t>
+          <t>70.5%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,15 +1285,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-330.2%</t>
+          <t>-338.4%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-39.3%</t>
+          <t>-38.8%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-24.3%</t>
+          <t>-23.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>36.4%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-159.4%</t>
+          <t>-163.3%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-254.4%</t>
+          <t>-250.7%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>54.2%</t>
+          <t>49.2%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>52.3%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,12 +1423,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>43.8%</t>
+          <t>41.9%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-28</t>
+          <t>2024-02-25</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-198.5%</t>
+          <t>-203.4%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,32 +1466,32 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.9%</t>
+          <t>12.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.9%</t>
+          <t>-33.5%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>49.8%</t>
+          <t>43.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.4%</t>
+          <t>43.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.1</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-18.0%</t>
+          <t>-16.4%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.2%</t>
+          <t>34.9%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-136.4%</t>
+          <t>-156.0%</t>
         </is>
       </c>
     </row>
@@ -44055,16 +44055,16 @@
         <v>3.116946666549951</v>
       </c>
       <c r="D1848" t="n">
-        <v>-0.9430734250892931</v>
+        <v>-0.9477836635121346</v>
       </c>
       <c r="E1848" t="n">
-        <v>2.739360872200487</v>
+        <v>2.73747677683135</v>
       </c>
       <c r="F1848" t="n">
-        <v>1.15709845023947</v>
+        <v>1.075599172723206</v>
       </c>
       <c r="G1848" t="n">
-        <v>3.811205736693633</v>
+        <v>3.762306170183875</v>
       </c>
     </row>
     <row r="1849">
@@ -44078,16 +44078,16 @@
         <v>3.121838811103876</v>
       </c>
       <c r="D1849" t="n">
-        <v>-1.15107748344237</v>
+        <v>-1.155787721865212</v>
       </c>
       <c r="E1849" t="n">
-        <v>2.661051393413181</v>
+        <v>2.659167298044044</v>
       </c>
       <c r="F1849" t="n">
-        <v>1.15709845023947</v>
+        <v>1.075599172723206</v>
       </c>
       <c r="G1849" t="n">
-        <v>3.816097881247559</v>
+        <v>3.7671983147378</v>
       </c>
     </row>
     <row r="1850">
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.421477446151256</v>
+        <v>-1.426187684574097</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.547972864667615</v>
+        <v>2.546088769298478</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8866984875305843</v>
+        <v>0.8051992100143204</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.648939359960215</v>
+        <v>3.600039793450457</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.760635823739778</v>
+        <v>-1.765346062162619</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.405393812938655</v>
+        <v>2.403509717569519</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.5475401099420623</v>
+        <v>0.4660408324257983</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.438528632713551</v>
+        <v>3.389629066203793</v>
       </c>
     </row>
     <row r="1852">
@@ -44141,22 +44141,22 @@
         <v>45314</v>
       </c>
       <c r="B1852" t="n">
-        <v>3.223539378213497</v>
+        <v>3.223539378213496</v>
       </c>
       <c r="C1852" t="n">
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.088653045467256</v>
+        <v>-2.093363283890098</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.294525213986432</v>
+        <v>2.292641118617295</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.2195228882145831</v>
+        <v>0.1380236106983191</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.262056589415832</v>
+        <v>3.213157022906074</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.581977917002435</v>
+        <v>-2.586688155425276</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.105294015780929</v>
+        <v>2.103409920411792</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.1145367739749644</v>
+        <v>0.03303749645870041</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.207163671280629</v>
+        <v>3.158264104770871</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.074362945026532</v>
+        <v>-3.079073183449373</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.909446396615023</v>
+        <v>1.907562301245886</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.3778482540491324</v>
+        <v>-0.4593475315653963</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.912839046509903</v>
+        <v>2.863939480000145</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.459543335956604</v>
+        <v>-3.464253574379446</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.753916779055857</v>
+        <v>1.75203268368672</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.3778482540491324</v>
+        <v>-0.4593475315653963</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.911381585322767</v>
+        <v>2.862482018813008</v>
       </c>
     </row>
     <row r="1856">
@@ -44233,22 +44233,22 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.299136146347056</v>
+        <v>3.299136146347055</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.803226109183267</v>
+        <v>-3.807936347606109</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.618212793219808</v>
+        <v>1.616328697850671</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.4857543060763506</v>
+        <v>-0.5672535835926145</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.848407077561052</v>
+        <v>2.799507511051294</v>
       </c>
     </row>
     <row r="1857">
@@ -44256,22 +44256,22 @@
         <v>45319</v>
       </c>
       <c r="B1857" t="n">
-        <v>3.287377576130018</v>
+        <v>3.287377576130017</v>
       </c>
       <c r="C1857" t="n">
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.160876459421615</v>
+        <v>-4.165586697844457</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.471258711780727</v>
+        <v>1.46937461641159</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.8434046563146986</v>
+        <v>-0.9249039338309626</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.629922926074301</v>
+        <v>2.581023359564543</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.470110562417666</v>
+        <v>-4.474820800840508</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.349337997282566</v>
+        <v>1.347453901913429</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.8434046563146986</v>
+        <v>-0.9249039338309626</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.63169585277456</v>
+        <v>2.582796286264802</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.901916355567454</v>
+        <v>-4.906626593990295</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.162948567490055</v>
+        <v>1.161064472120918</v>
       </c>
       <c r="F1859" t="n">
-        <v>-0.9798221527559656</v>
+        <v>-1.06132143027223</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.536178242377205</v>
+        <v>2.487278675867446</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.228348884435198</v>
+        <v>-5.233059122858039</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.020660330945048</v>
+        <v>1.018776235575912</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.062290403263114</v>
+        <v>-1.143789680779378</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.474982067075007</v>
+        <v>2.426082500565248</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.56401153166565</v>
+        <v>-5.568721770088492</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8849758637088323</v>
+        <v>0.8830917683396957</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.062290403263114</v>
+        <v>-1.143789680779378</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.473562658730972</v>
+        <v>2.424663092221214</v>
       </c>
     </row>
     <row r="1862">
@@ -44371,22 +44371,22 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309424</v>
+        <v>3.311086391309423</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.927637776565963</v>
+        <v>-5.932348014988805</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7460129259829484</v>
+        <v>0.7441288306138119</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.16051204013024</v>
+        <v>-1.242011317646504</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.421117236844938</v>
+        <v>2.372217670335179</v>
       </c>
     </row>
     <row r="1863">
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970905</v>
+        <v>3.304715716970903</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.29276515920471</v>
+        <v>-6.297475397627552</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5992164879332811</v>
+        <v>0.5973323925641445</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.456822824429252</v>
+        <v>-1.538322101945516</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.242585281271362</v>
+        <v>2.193685714761603</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330521</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.701353936385388</v>
+        <v>-6.70606417480823</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4345425210757692</v>
+        <v>0.4326584257066326</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.86541160160993</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.996193558977714</v>
+        <v>1.947293992467955</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191738</v>
+        <v>3.302618194191736</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.114336420526482</v>
+        <v>-7.119046658949324</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.264534959890792</v>
+        <v>0.2626508645216554</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.86541160160993</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.991378991449174</v>
+        <v>1.942479424939416</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.30502326510864</v>
+        <v>3.305023265108638</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.530728294813479</v>
+        <v>-7.535438533236321</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09597226078487076</v>
+        <v>0.09408816541573373</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.86541160160993</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.989373042058052</v>
+        <v>1.940473475548293</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097822</v>
+        <v>3.34137872309782</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.907405305343324</v>
+        <v>-7.912115543766165</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04443985275838802</v>
+        <v>-0.04632394812752505</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.86541160160993</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.999631732726731</v>
+        <v>1.950732166216972</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094116</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.253280127328132</v>
+        <v>-8.257990365750974</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1866902164066162</v>
+        <v>-0.1885743117757532</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.86541160160993</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.995731297872426</v>
+        <v>1.946831731362668</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199286</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.566104926573111</v>
+        <v>-8.570815164995953</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3134152160496071</v>
+        <v>-0.3152993114187437</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.86541160160993</v>
+        <v>-1.946910879126194</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.994136217927427</v>
+        <v>1.945236651417669</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969595</v>
+        <v>3.424633354969593</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.862766268383309</v>
+        <v>-8.867476506806151</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4283007768444782</v>
+        <v>-0.4301848722136148</v>
       </c>
       <c r="F1870" t="n">
-        <v>-1.934154737343809</v>
+        <v>-2.015654014860073</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.956669312416308</v>
+        <v>1.907769745906549</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923088</v>
+        <v>3.419979433923086</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.296115376493544</v>
+        <v>-9.300825614916386</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6056667246229752</v>
+        <v>-0.6075508199921118</v>
       </c>
       <c r="F1871" t="n">
-        <v>-1.934154737343809</v>
+        <v>-2.015654014860073</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.952643007881905</v>
+        <v>1.903743441372146</v>
       </c>
     </row>
     <row r="1872">
@@ -44601,22 +44601,22 @@
         <v>45334</v>
       </c>
       <c r="B1872" t="n">
-        <v>3.458100091297752</v>
+        <v>3.45810009129775</v>
       </c>
       <c r="C1872" t="n">
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.679116765236175</v>
+        <v>-9.683827003659017</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7589693814416116</v>
+        <v>-0.7608534768107482</v>
       </c>
       <c r="F1872" t="n">
-        <v>-1.934154737343809</v>
+        <v>-2.015654014860073</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.952540906560321</v>
+        <v>1.903641340050562</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317616</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.05410209140745</v>
+        <v>-10.05881232983029</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9063919959386921</v>
+        <v>-0.9082760913078292</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.309140063515086</v>
+        <v>-2.39063934103135</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.730121226828985</v>
+        <v>1.681221660319226</v>
       </c>
     </row>
     <row r="1874">
@@ -44647,22 +44647,22 @@
         <v>45336</v>
       </c>
       <c r="B1874" t="n">
-        <v>3.503515506737172</v>
+        <v>3.50351550673717</v>
       </c>
       <c r="C1874" t="n">
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.41363241391145</v>
+        <v>-10.4183426523343</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.044853821642243</v>
+        <v>-1.04673791701138</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.309140063515086</v>
+        <v>-2.39063934103135</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.735471530127035</v>
+        <v>1.686571963617276</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341313</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.74003244257647</v>
+        <v>-10.74474268099931</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.16749781315107</v>
+        <v>-1.169381908520208</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.635540092180099</v>
+        <v>-2.717039369696364</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.547547532885204</v>
+        <v>1.498647966375446</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.95918141065066</v>
+        <v>-10.96389164907351</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.252115649758981</v>
+        <v>-1.253999745128117</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.854689060254297</v>
+        <v>-2.936188337770561</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.419099902662455</v>
+        <v>1.370200336152696</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407492</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.95549048569425</v>
+        <v>-10.9602007241171</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.250639279776416</v>
+        <v>-1.252523375145553</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.854689060254297</v>
+        <v>-2.936188337770561</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.419099902662455</v>
+        <v>1.370200336152696</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611695</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.15974866102412</v>
+        <v>-11.16445889944696</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.326829352789719</v>
+        <v>-1.328713448158856</v>
       </c>
       <c r="F1878" t="n">
-        <v>-2.982328004868286</v>
+        <v>-3.06382728238455</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.348029733012704</v>
+        <v>1.299130166502945</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.3777864326553</v>
+        <v>-11.38249667107814</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.409561906957755</v>
+        <v>-1.411446002326891</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.157098772964185</v>
+        <v>-3.238598050480449</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.2476498266396</v>
+        <v>1.198750260129842</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910627</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.30431660098785</v>
+        <v>-11.30902683941069</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.364802272797354</v>
+        <v>-1.366686368166491</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.083628941296736</v>
+        <v>-3.165128218813</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.307103427133491</v>
+        <v>1.258203860623732</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078594</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.47944101837439</v>
+        <v>-11.48415125679723</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.420296819004454</v>
+        <v>-1.422180914373591</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.25875335868328</v>
+        <v>-3.340252636199544</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.216583997449081</v>
+        <v>1.167684430939323</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880266</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.71389311238888</v>
+        <v>-11.71860335081172</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.521296821511846</v>
+        <v>-1.523180916880983</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.25875335868328</v>
+        <v>-3.340252636199544</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.209364832547485</v>
+        <v>1.160465266037727</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.48068891723439</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.00169695692612</v>
+        <v>-12.00640719534896</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.643090550100718</v>
+        <v>-1.644974645469854</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.546557203220518</v>
+        <v>-3.628056480736782</v>
       </c>
       <c r="G1883" t="n">
-        <v>1.030010335051166</v>
+        <v>0.9811107685414076</v>
       </c>
     </row>
     <row r="1884">
@@ -44877,22 +44877,22 @@
         <v>45346</v>
       </c>
       <c r="B1884" t="n">
-        <v>3.493712438860582</v>
+        <v>3.49371243886058</v>
       </c>
       <c r="C1884" t="n">
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.23152140408994</v>
+        <v>-12.23623164251278</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.733904539127692</v>
+        <v>-1.735788634496829</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.709204740290679</v>
+        <v>-3.790704017806943</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.9335376026476259</v>
+        <v>0.8846380361378676</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767394</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.4635503238262</v>
+        <v>-12.46826056224905</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.824022378393082</v>
+        <v>-1.825906473762218</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.771217437479102</v>
+        <v>-3.852716714995366</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8990237129636869</v>
+        <v>0.8501241464539282</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792541</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.41153480985739</v>
+        <v>-12.41624504828023</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.799225837119156</v>
+        <v>-1.801109932488292</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.771217437479102</v>
+        <v>-3.852716714995366</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.9030140486500877</v>
+        <v>0.854114482140329</v>
       </c>
     </row>
     <row r="1887">
@@ -44946,22 +44946,22 @@
         <v>45349</v>
       </c>
       <c r="B1887" t="n">
-        <v>3.600034689628918</v>
+        <v>3.600034689628917</v>
       </c>
       <c r="C1887" t="n">
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.55320665158151</v>
+        <v>-12.55791689000435</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.857369800707546</v>
+        <v>-1.859253896076682</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.771217437479102</v>
+        <v>-3.852716714995366</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.901538821751346</v>
+        <v>0.8526392552415873</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410716</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.65211339204079</v>
+        <v>-12.48969465407134</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.881879086726383</v>
+        <v>-1.816911591538603</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.870124177938377</v>
+        <v>-3.784494479062348</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.857248187640653</v>
+        <v>0.9086260069662706</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240576</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.45296128480369</v>
+        <v>-12.29054254683424</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.815269377478227</v>
+        <v>-1.750301882290446</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.704801651988564</v>
+        <v>-3.619171953112534</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9433905695638583</v>
+        <v>0.9947683888894758</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085279</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.22711613208428</v>
+        <v>-12.06469739411483</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.715352243354254</v>
+        <v>-1.650384748166474</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.6628749764014</v>
+        <v>-3.577245277525371</v>
       </c>
       <c r="G1890" t="n">
-        <v>0.978125647952365</v>
+        <v>1.029503467277983</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282098</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.94084131976158</v>
+        <v>-11.77842258179213</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.599703173869117</v>
+        <v>-1.534735678681337</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.6628749764014</v>
+        <v>-3.577245277525371</v>
       </c>
       <c r="G1891" t="n">
-        <v>0.9792647925084239</v>
+        <v>1.030642611834041</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116213</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.99373660780587</v>
+        <v>-11.83131786983642</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.618227514924723</v>
+        <v>-1.553260019736943</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.657919630312954</v>
+        <v>-3.572289931436925</v>
       </c>
       <c r="G1892" t="n">
-        <v>0.9848717743235991</v>
+        <v>1.036249593649217</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081564</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.70982787687712</v>
+        <v>-11.54740913890767</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.498930318314588</v>
+        <v>-1.433962823126808</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.657919630312954</v>
+        <v>-3.572289931436925</v>
       </c>
       <c r="G1893" t="n">
-        <v>0.9906054785622356</v>
+        <v>1.041983297887853</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425325</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.46284062668417</v>
+        <v>-11.30042188871472</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.409872680631272</v>
+        <v>-1.344905185443492</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.410932380120002</v>
+        <v>-3.325302681243973</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.129060566284142</v>
+        <v>1.180438385609759</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.1990037594801</v>
+        <v>-11.03658502151065</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.314221415062552</v>
+        <v>-1.249253919874772</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.410932380120002</v>
+        <v>-3.325302681243973</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.119177084971234</v>
+        <v>1.170554904296852</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.9317619586117</v>
+        <v>-10.76934322064225</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.209159255214566</v>
+        <v>-1.144191760026786</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.410932380120002</v>
+        <v>-3.325302681243973</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.11734252447186</v>
+        <v>1.168720343797478</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,22 +45176,22 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.784680945781947</v>
+        <v>3.784680945781946</v>
       </c>
       <c r="C1897" t="n">
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.65595279521122</v>
+        <v>-10.49353405724177</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.099135904827833</v>
+        <v>-1.034168409640053</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.321913071841268</v>
+        <v>-3.236283372965239</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.17045379446564</v>
+        <v>1.221831613791257</v>
       </c>
     </row>
     <row r="1898">
@@ -45199,22 +45199,22 @@
         <v>45360</v>
       </c>
       <c r="B1898" t="n">
-        <v>3.800825778567242</v>
+        <v>3.800825778567241</v>
       </c>
       <c r="C1898" t="n">
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.63199925423526</v>
+        <v>-10.46958051626581</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.088885982291956</v>
+        <v>-1.023918487104176</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.297959530865311</v>
+        <v>-3.212329831989281</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.185494425196708</v>
+        <v>1.236872244522325</v>
       </c>
     </row>
     <row r="1899">
@@ -45222,22 +45222,22 @@
         <v>45361</v>
       </c>
       <c r="B1899" t="n">
-        <v>3.789307536487772</v>
+        <v>3.789307536487771</v>
       </c>
       <c r="C1899" t="n">
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.36793931591246</v>
+        <v>-10.20552057794301</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.9965223231245899</v>
+        <v>-0.93155482793681</v>
       </c>
       <c r="F1899" t="n">
-        <v>-3.033899592542515</v>
+        <v>-2.948269893666485</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.330670072028633</v>
+        <v>1.382047891354251</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.660859692407623</v>
+        <v>-9.498440954438173</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.7164775073829555</v>
+        <v>-0.6515100121951756</v>
       </c>
       <c r="F1900" t="n">
-        <v>-3.033899592542515</v>
+        <v>-2.948269893666485</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.327883038368332</v>
+        <v>1.37926085769395</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.620675394041433</v>
+        <v>-9.458256656071983</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.7000601641486379</v>
+        <v>-0.635092668960858</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.993715294176324</v>
+        <v>-2.908085595300294</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.352337241275888</v>
+        <v>1.403715060601506</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.540605598503628</v>
+        <v>-9.378186860534178</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6686654247127595</v>
+        <v>-0.6036979295249796</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.91364549863852</v>
+        <v>-2.82801579976249</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.399745939819327</v>
+        <v>1.451123759144946</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.307124376274029</v>
+        <v>-9.144705638304579</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.567348506983067</v>
+        <v>-0.5023810117952872</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.680164276408922</v>
+        <v>-2.594534577532892</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.547759101994939</v>
+        <v>1.599136921320557</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-9.127415846130155</v>
+        <v>-8.964997108160706</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4983573052384771</v>
+        <v>-0.4333898100506972</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.622992772246226</v>
+        <v>-2.537363073370196</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.579169794179597</v>
+        <v>1.630547613505215</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.995140372499268</v>
+        <v>-8.832721634529818</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.4500796290390952</v>
+        <v>-0.3851121338513153</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.490717298615339</v>
+        <v>-2.405087599739309</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.653902565105156</v>
+        <v>1.705280384430774</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.804540697826114</v>
+        <v>-8.642121959856665</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3710246984821968</v>
+        <v>-0.3060572032944169</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.300117623942187</v>
+        <v>-2.214487925066157</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.771077430596685</v>
+        <v>1.822455249922303</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.555540899142533</v>
+        <v>-8.393122161173084</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.258518437785106</v>
+        <v>-0.1935509425973261</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.300117623942187</v>
+        <v>-2.214487925066157</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.783983771820343</v>
+        <v>1.835361591145961</v>
       </c>
     </row>
     <row r="1908">
@@ -45429,22 +45429,22 @@
         <v>45370</v>
       </c>
       <c r="B1908" t="n">
-        <v>3.692928280077642</v>
+        <v>3.692928280077643</v>
       </c>
       <c r="C1908" t="n">
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.661130888915638</v>
+        <v>-8.498712150946188</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.4287303632935662</v>
+        <v>-0.3637628681057863</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.405707613715291</v>
+        <v>-2.320077914839261</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.592653848357262</v>
+        <v>1.64403166768288</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.679865791034235</v>
+        <v>-8.517447053064785</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3876799822639185</v>
+        <v>-0.3227124870761386</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.405707613715291</v>
+        <v>-2.320077914839261</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.641198190234348</v>
+        <v>1.692576009559966</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.403127616363422</v>
+        <v>-8.240708878393972</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2736057004095991</v>
+        <v>-0.2086382052218192</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.223890952605365</v>
+        <v>-2.138261253729335</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.753667198886298</v>
+        <v>1.805045018211916</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.276235209928352</v>
+        <v>-8.113816471958902</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.231562724089049</v>
+        <v>-0.1665952289012691</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.096998546170295</v>
+        <v>-2.011368847294265</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.821088656493862</v>
+        <v>1.87246647581948</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.232686803157661</v>
+        <v>-8.070268065188211</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.2211039734758655</v>
+        <v>-0.1561364782880856</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.096998546170295</v>
+        <v>-2.011368847294265</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.814128044398769</v>
+        <v>1.865505863724387</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.990538409703802</v>
+        <v>-7.828119671734353</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.1097822617131792</v>
+        <v>-0.04481476652539929</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.096998546170295</v>
+        <v>-2.011368847294265</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.828590398779912</v>
+        <v>1.87996821810553</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.927309037935454</v>
+        <v>-7.764890299966004</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.08995839254664473</v>
+        <v>-0.02499089735886484</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.096998546170295</v>
+        <v>-2.011368847294265</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.823122519239107</v>
+        <v>1.874500338564725</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.740821345558448</v>
+        <v>-7.578402607588998</v>
       </c>
       <c r="E1915" t="n">
-        <v>-0.01786522158526571</v>
+        <v>0.04710227360251418</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.910510853793289</v>
+        <v>-1.824881154917259</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.932513228675888</v>
+        <v>1.983891048001506</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.719672146655005</v>
+        <v>-7.557253408685555</v>
       </c>
       <c r="E1916" t="n">
-        <v>-0.001704563786562474</v>
+        <v>0.06326293140121741</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.889361654889846</v>
+        <v>-1.803731956013816</v>
       </c>
       <c r="G1916" t="n">
-        <v>1.95290372625528</v>
+        <v>2.004281545580898</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.47590670467156</v>
+        <v>-7.313487966702111</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.09158232135386557</v>
+        <v>0.1565498165416455</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.889361654889846</v>
+        <v>-1.803731956013816</v>
       </c>
       <c r="G1917" t="n">
-        <v>1.94868443460233</v>
+        <v>2.000062253927948</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.2118786374783</v>
+        <v>-7.04945989950885</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.1993178621511857</v>
+        <v>0.2642853573389656</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.687496256073892</v>
+        <v>-1.601866557197862</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.071927987811918</v>
+        <v>2.123305807137536</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.962028243529225</v>
+        <v>-6.799609505559776</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.2920000947145178</v>
+        <v>0.3569675899022977</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.687496256073892</v>
+        <v>-1.601866557197862</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.064670062795621</v>
+        <v>2.116047882121238</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.658460754525247</v>
+        <v>-6.496042016555797</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.417026213836758</v>
+        <v>0.4819937090245379</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.687496256073892</v>
+        <v>-1.601866557197862</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.068269186316269</v>
+        <v>2.119647005641887</v>
       </c>
     </row>
     <row r="1921">
@@ -45728,22 +45728,22 @@
         <v>45383</v>
       </c>
       <c r="B1921" t="n">
-        <v>3.780930335862983</v>
+        <v>3.780930335862982</v>
       </c>
       <c r="C1921" t="n">
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.584980845673233</v>
+        <v>-6.422562107703783</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.4597456834321174</v>
+        <v>0.5247131786198973</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.614016347221878</v>
+        <v>-1.528386648345848</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.125684637682031</v>
+        <v>2.177062457007649</v>
       </c>
     </row>
     <row r="1922">
@@ -45751,22 +45751,22 @@
         <v>45384</v>
       </c>
       <c r="B1922" t="n">
-        <v>3.773761647102778</v>
+        <v>3.773761647102777</v>
       </c>
       <c r="C1922" t="n">
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.35994784600441</v>
+        <v>-6.19752910803496</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.5487793609159435</v>
+        <v>0.6137468561037234</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.388983347553055</v>
+        <v>-1.303353648677025</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.259724915099622</v>
+        <v>2.31110273442524</v>
       </c>
     </row>
     <row r="1923">
@@ -45774,22 +45774,22 @@
         <v>45385</v>
       </c>
       <c r="B1923" t="n">
-        <v>3.764614304353071</v>
+        <v>3.76461430435307</v>
       </c>
       <c r="C1923" t="n">
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-6.145313468368003</v>
+        <v>-5.982894730398553</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.6393279130248235</v>
+        <v>0.7042954082126034</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.174348969916648</v>
+        <v>-1.088719271040618</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.393200342735784</v>
+        <v>2.444578162061402</v>
       </c>
     </row>
     <row r="1924">
@@ -45797,22 +45797,22 @@
         <v>45386</v>
       </c>
       <c r="B1924" t="n">
-        <v>3.798811195544779</v>
+        <v>3.798811195544778</v>
       </c>
       <c r="C1924" t="n">
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.878713111393651</v>
+        <v>-5.716294373424201</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.7271623145983601</v>
+        <v>0.79212980978614</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.174348969916648</v>
+        <v>-1.088719271040618</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.374394601519579</v>
+        <v>2.425772420845197</v>
       </c>
     </row>
     <row r="1925">
@@ -45820,22 +45820,22 @@
         <v>45387</v>
       </c>
       <c r="B1925" t="n">
-        <v>3.797691308712292</v>
+        <v>3.79769130871229</v>
       </c>
       <c r="C1925" t="n">
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.638282614588791</v>
+        <v>-5.475863876619341</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8250775899451814</v>
+        <v>0.8900450851329613</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.9339184731117878</v>
+        <v>-0.8482887742357579</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.520395976227373</v>
+        <v>2.571773795552991</v>
       </c>
     </row>
     <row r="1926">
@@ -45843,22 +45843,22 @@
         <v>45388</v>
       </c>
       <c r="B1926" t="n">
-        <v>3.821589933837682</v>
+        <v>3.82158993383768</v>
       </c>
       <c r="C1926" t="n">
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.395491806939345</v>
+        <v>-5.233073068969896</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9261232268397799</v>
+        <v>0.9910907220275598</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.9339184731117878</v>
+        <v>-0.8482887742357579</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.524325290062193</v>
+        <v>2.575703109387811</v>
       </c>
     </row>
     <row r="1927">
@@ -45866,22 +45866,22 @@
         <v>45389</v>
       </c>
       <c r="B1927" t="n">
-        <v>3.822323422349964</v>
+        <v>3.822323422349962</v>
       </c>
       <c r="C1927" t="n">
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-5.155886715332256</v>
+        <v>-4.993467977362807</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.022643847399956</v>
+        <v>1.087611342587735</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.8668705254432932</v>
+        <v>-0.7812408265672633</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.56523264258063</v>
+        <v>2.616610461906248</v>
       </c>
     </row>
     <row r="1928">
@@ -45889,22 +45889,22 @@
         <v>45390</v>
       </c>
       <c r="B1928" t="n">
-        <v>3.848613050972337</v>
+        <v>3.848613050972335</v>
       </c>
       <c r="C1928" t="n">
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.913231126909093</v>
+        <v>-4.750812388939643</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.116704153989214</v>
+        <v>1.181671649176994</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.8668705254432932</v>
+        <v>-0.7812408265672633</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.562230713800623</v>
+        <v>2.613608533126241</v>
       </c>
     </row>
     <row r="1929">
@@ -45912,22 +45912,22 @@
         <v>45391</v>
       </c>
       <c r="B1929" t="n">
-        <v>3.818665376145937</v>
+        <v>3.818665376145935</v>
       </c>
       <c r="C1929" t="n">
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.693210328872082</v>
+        <v>-4.530791590902632</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.206291510214633</v>
+        <v>1.271259005402413</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.725650680375313</v>
+        <v>-0.6400209814992831</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.648541657852026</v>
+        <v>2.699919477177644</v>
       </c>
     </row>
     <row r="1930">
@@ -45935,22 +45935,22 @@
         <v>45392</v>
       </c>
       <c r="B1930" t="n">
-        <v>3.843270952009949</v>
+        <v>3.843270952009947</v>
       </c>
       <c r="C1930" t="n">
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.493961698967273</v>
+        <v>-4.331542960997823</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.30188514497838</v>
+        <v>1.36685264016616</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.725650680375313</v>
+        <v>-0.6400209814992831</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.664435840653849</v>
+        <v>2.715813659979466</v>
       </c>
     </row>
     <row r="1931">
@@ -45958,22 +45958,22 @@
         <v>45393</v>
       </c>
       <c r="B1931" t="n">
-        <v>3.845043810966256</v>
+        <v>3.845043810966255</v>
       </c>
       <c r="C1931" t="n">
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.334446595447903</v>
+        <v>-4.172027857478454</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.366837030826429</v>
+        <v>1.431804526014209</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.5661355768559431</v>
+        <v>-0.4805058779799132</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.761290747205773</v>
+        <v>2.812668566531391</v>
       </c>
     </row>
     <row r="1932">
@@ -45981,22 +45981,22 @@
         <v>45394</v>
       </c>
       <c r="B1932" t="n">
-        <v>3.791269976046992</v>
+        <v>3.791269976046991</v>
       </c>
       <c r="C1932" t="n">
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.189774450348166</v>
+        <v>-4.027355712378716</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.434793991427764</v>
+        <v>1.499761486615544</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.4214634317562057</v>
+        <v>-0.3358337328801758</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.858182136827055</v>
+        <v>2.909559956152673</v>
       </c>
     </row>
     <row r="1933">
@@ -46004,22 +46004,22 @@
         <v>45395</v>
       </c>
       <c r="B1933" t="n">
-        <v>3.735835647412099</v>
+        <v>3.735835647412097</v>
       </c>
       <c r="C1933" t="n">
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.17200499141721</v>
+        <v>-4.00958625344776</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.357241467086868</v>
+        <v>1.422208962274648</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.4036939728252501</v>
+        <v>-0.3180642739492202</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.78418350427235</v>
+        <v>2.835561323597968</v>
       </c>
     </row>
     <row r="1934">
@@ -46027,22 +46027,22 @@
         <v>45396</v>
       </c>
       <c r="B1934" t="n">
-        <v>3.762643902144512</v>
+        <v>3.76264390214451</v>
       </c>
       <c r="C1934" t="n">
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-4.085205493638201</v>
+        <v>-3.922786755668751</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.414361759521038</v>
+        <v>1.479329254708818</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.4036939728252501</v>
+        <v>-0.3180642739492202</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.806583997594916</v>
+        <v>2.857961816920534</v>
       </c>
     </row>
     <row r="1935">
@@ -46050,22 +46050,22 @@
         <v>45397</v>
       </c>
       <c r="B1935" t="n">
-        <v>3.729142822900689</v>
+        <v>3.729142822900688</v>
       </c>
       <c r="C1935" t="n">
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.985512878909189</v>
+        <v>-3.82309414093974</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.454311206786055</v>
+        <v>1.519278701973835</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.3040013580962383</v>
+        <v>-0.2183716592202085</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.866471967805735</v>
+        <v>2.917849787131353</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.635130337990593</v>
+        <v>3.838656292625575</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.103308429829164</v>
+        <v>3.05987970513818</v>
       </c>
       <c r="D1936" t="n">
-        <v>-3.985512878909189</v>
+        <v>-4.007146951381117</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.454311206786055</v>
+        <v>1.456664500271986</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.3040013580962383</v>
+        <v>-0.266831249322602</v>
       </c>
       <c r="G1936" t="n">
-        <v>3.096372226815532</v>
+        <v>2.899780955544619</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240416.xlsx
+++ b/tame_output/ON/bt/strategyON_20240416.xlsx
@@ -600,17 +600,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>65.0%</t>
+          <t>61.5%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>66.3%</t>
+          <t>66.2%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>65.1%</t>
+          <t>65.0%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.6%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>18.2%</t>
+          <t>18.7%</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>55.8%</t>
+          <t>44.0%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>70.7%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>29.0%</t>
+          <t>29.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>31.3%</t>
+          <t>32.4%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>16.0%</t>
+          <t>24.8%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -811,25 +811,25 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-04-13</t>
+          <t>2024-04-16</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-15.6%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-6.0%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-2.3%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,7 +839,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-3.4%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -849,17 +849,17 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>56.0%</t>
+          <t>52.1%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>23.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.2</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -869,7 +869,7 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.9%</t>
+          <t>-4.4%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-5.6%</t>
+          <t>-19.2%</t>
         </is>
       </c>
     </row>
@@ -916,12 +916,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-79.7%</t>
+          <t>-79.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>119.6%</t>
+          <t>118.8%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>139.7%</t>
+          <t>138.8%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>98.0%</t>
+          <t>97.2%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -969,15 +969,15 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N4" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-705.7%</t>
+          <t>-722.5%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>-58.0%</t>
+          <t>-58.3%</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
@@ -1007,12 +1007,12 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-75.6%</t>
+          <t>-75.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>98.5%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>802.4%</t>
+          <t>784.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-2.5%</t>
+          <t>-1.5%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-562.3%</t>
+          <t>-571.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>8.2%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>57.9%</t>
+          <t>57.8%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>66.7%</t>
+          <t>67.2%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>46.4%</t>
+          <t>46.2%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1127,15 +1127,15 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>2024-02-27</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N5" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-276.9%</t>
+          <t>-283.6%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
@@ -1150,12 +1150,12 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>14.4%</t>
+          <t>14.1%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-45.3%</t>
+          <t>-45.6%</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>9.0%</t>
+          <t>5.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>46.7%</t>
+          <t>46.8%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-20.8%</t>
+          <t>-24.4%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>-74.0%</t>
+          <t>-26.4%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-230.6%</t>
+          <t>-247.7%</t>
         </is>
       </c>
     </row>
@@ -1232,12 +1232,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>-30.4%</t>
+          <t>-30.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>72.4%</t>
+          <t>72.0%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1265,12 +1265,12 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>73.3%</t>
+          <t>72.8%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>70.5%</t>
+          <t>70.3%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1285,15 +1285,15 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N6" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>-338.4%</t>
+          <t>-331.1%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1308,12 +1308,12 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>-38.8%</t>
+          <t>-39.3%</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-23.6%</t>
+          <t>-23.7%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>60.2%</t>
+          <t>59.8%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.6%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-163.3%</t>
+          <t>-159.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-250.7%</t>
+          <t>-254.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>49.2%</t>
+          <t>44.8%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,12 +1400,12 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.2%</t>
+          <t>59.1%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>41.9%</t>
+          <t>41.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1443,15 +1443,15 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-25</t>
+          <t>2024-02-28</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>-203.4%</t>
+          <t>-199.0%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12.4%</t>
+          <t>12.2%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-33.5%</t>
+          <t>-34.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>39.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.0</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -1501,12 +1501,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-16.4%</t>
+          <t>-16.7%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>34.9%</t>
+          <t>34.2%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-156.0%</t>
+          <t>-171.7%</t>
         </is>
       </c>
     </row>
@@ -44101,16 +44101,16 @@
         <v>3.116920267441865</v>
       </c>
       <c r="D1850" t="n">
-        <v>-1.426187684574097</v>
+        <v>-1.353006046298362</v>
       </c>
       <c r="E1850" t="n">
-        <v>2.546088769298478</v>
+        <v>2.575361424608772</v>
       </c>
       <c r="F1850" t="n">
-        <v>0.8051992100143204</v>
+        <v>0.8783808482900554</v>
       </c>
       <c r="G1850" t="n">
-        <v>3.600039793450457</v>
+        <v>3.643948776415898</v>
       </c>
     </row>
     <row r="1851">
@@ -44124,16 +44124,16 @@
         <v>3.110004566748314</v>
       </c>
       <c r="D1851" t="n">
-        <v>-1.765346062162619</v>
+        <v>-1.692164423886884</v>
       </c>
       <c r="E1851" t="n">
-        <v>2.403509717569519</v>
+        <v>2.432782372879812</v>
       </c>
       <c r="F1851" t="n">
-        <v>0.4660408324257983</v>
+        <v>0.5392224707015333</v>
       </c>
       <c r="G1851" t="n">
-        <v>3.389629066203793</v>
+        <v>3.433538049169234</v>
       </c>
     </row>
     <row r="1852">
@@ -44147,16 +44147,16 @@
         <v>3.130342856487082</v>
       </c>
       <c r="D1852" t="n">
-        <v>-2.093363283890098</v>
+        <v>-2.020181645614364</v>
       </c>
       <c r="E1852" t="n">
-        <v>2.292641118617295</v>
+        <v>2.321913773927589</v>
       </c>
       <c r="F1852" t="n">
-        <v>0.1380236106983191</v>
+        <v>0.2112052489740541</v>
       </c>
       <c r="G1852" t="n">
-        <v>3.213157022906074</v>
+        <v>3.257066005871515</v>
       </c>
     </row>
     <row r="1853">
@@ -44170,16 +44170,16 @@
         <v>3.13844160689565</v>
       </c>
       <c r="D1853" t="n">
-        <v>-2.586688155425276</v>
+        <v>-2.513506517149542</v>
       </c>
       <c r="E1853" t="n">
-        <v>2.103409920411792</v>
+        <v>2.132682575722086</v>
       </c>
       <c r="F1853" t="n">
-        <v>0.03303749645870041</v>
+        <v>0.1062191347344354</v>
       </c>
       <c r="G1853" t="n">
-        <v>3.158264104770871</v>
+        <v>3.202173087736312</v>
       </c>
     </row>
     <row r="1854">
@@ -44193,16 +44193,16 @@
         <v>3.139547998939383</v>
       </c>
       <c r="D1854" t="n">
-        <v>-3.079073183449373</v>
+        <v>-3.005891545173639</v>
       </c>
       <c r="E1854" t="n">
-        <v>1.907562301245886</v>
+        <v>1.93683495655618</v>
       </c>
       <c r="F1854" t="n">
-        <v>-0.4593475315653963</v>
+        <v>-0.3861658932896613</v>
       </c>
       <c r="G1854" t="n">
-        <v>2.863939480000145</v>
+        <v>2.907848462965586</v>
       </c>
     </row>
     <row r="1855">
@@ -44216,16 +44216,16 @@
         <v>3.138090537752246</v>
       </c>
       <c r="D1855" t="n">
-        <v>-3.464253574379446</v>
+        <v>-3.391071936103711</v>
       </c>
       <c r="E1855" t="n">
-        <v>1.75203268368672</v>
+        <v>1.781305338997014</v>
       </c>
       <c r="F1855" t="n">
-        <v>-0.4593475315653963</v>
+        <v>-0.3861658932896613</v>
       </c>
       <c r="G1855" t="n">
-        <v>2.862482018813008</v>
+        <v>2.90639100177845</v>
       </c>
     </row>
     <row r="1856">
@@ -44239,16 +44239,16 @@
         <v>3.139859661206862</v>
       </c>
       <c r="D1856" t="n">
-        <v>-3.807936347606109</v>
+        <v>-3.734754709330374</v>
       </c>
       <c r="E1856" t="n">
-        <v>1.616328697850671</v>
+        <v>1.645601353160965</v>
       </c>
       <c r="F1856" t="n">
-        <v>-0.5672535835926145</v>
+        <v>-0.4940719453168795</v>
       </c>
       <c r="G1856" t="n">
-        <v>2.799507511051294</v>
+        <v>2.843416494016735</v>
       </c>
     </row>
     <row r="1857">
@@ -44262,16 +44262,16 @@
         <v>3.13596571986312</v>
       </c>
       <c r="D1857" t="n">
-        <v>-4.165586697844457</v>
+        <v>-4.092405059568722</v>
       </c>
       <c r="E1857" t="n">
-        <v>1.46937461641159</v>
+        <v>1.498647271721884</v>
       </c>
       <c r="F1857" t="n">
-        <v>-0.9249039338309626</v>
+        <v>-0.8517222955552277</v>
       </c>
       <c r="G1857" t="n">
-        <v>2.581023359564543</v>
+        <v>2.624932342529983</v>
       </c>
     </row>
     <row r="1858">
@@ -44285,16 +44285,16 @@
         <v>3.137738646563379</v>
       </c>
       <c r="D1858" t="n">
-        <v>-4.474820800840508</v>
+        <v>-4.401639162564773</v>
       </c>
       <c r="E1858" t="n">
-        <v>1.347453901913429</v>
+        <v>1.376726557223723</v>
       </c>
       <c r="F1858" t="n">
-        <v>-0.9249039338309626</v>
+        <v>-0.8517222955552277</v>
       </c>
       <c r="G1858" t="n">
-        <v>2.582796286264802</v>
+        <v>2.626705269230243</v>
       </c>
     </row>
     <row r="1859">
@@ -44308,16 +44308,16 @@
         <v>3.124071534030784</v>
       </c>
       <c r="D1859" t="n">
-        <v>-4.906626593990295</v>
+        <v>-4.83344495571456</v>
       </c>
       <c r="E1859" t="n">
-        <v>1.161064472120918</v>
+        <v>1.190337127431213</v>
       </c>
       <c r="F1859" t="n">
-        <v>-1.06132143027223</v>
+        <v>-0.9881397919964947</v>
       </c>
       <c r="G1859" t="n">
-        <v>2.487278675867446</v>
+        <v>2.531187658832887</v>
       </c>
     </row>
     <row r="1860">
@@ -44331,16 +44331,16 @@
         <v>3.112356309032875</v>
       </c>
       <c r="D1860" t="n">
-        <v>-5.233059122858039</v>
+        <v>-5.159877484582304</v>
       </c>
       <c r="E1860" t="n">
-        <v>1.018776235575912</v>
+        <v>1.048048890886206</v>
       </c>
       <c r="F1860" t="n">
-        <v>-1.143789680779378</v>
+        <v>-1.070608042503643</v>
       </c>
       <c r="G1860" t="n">
-        <v>2.426082500565248</v>
+        <v>2.469991483530689</v>
       </c>
     </row>
     <row r="1861">
@@ -44354,16 +44354,16 @@
         <v>3.11093690068884</v>
       </c>
       <c r="D1861" t="n">
-        <v>-5.568721770088492</v>
+        <v>-5.495540131812756</v>
       </c>
       <c r="E1861" t="n">
-        <v>0.8830917683396957</v>
+        <v>0.9123644236499899</v>
       </c>
       <c r="F1861" t="n">
-        <v>-1.143789680779378</v>
+        <v>-1.070608042503643</v>
       </c>
       <c r="G1861" t="n">
-        <v>2.424663092221214</v>
+        <v>2.468572075186654</v>
       </c>
     </row>
     <row r="1862">
@@ -44377,16 +44377,16 @@
         <v>3.117424460923081</v>
       </c>
       <c r="D1862" t="n">
-        <v>-5.932348014988805</v>
+        <v>-5.85916637671307</v>
       </c>
       <c r="E1862" t="n">
-        <v>0.7441288306138119</v>
+        <v>0.7734014859241061</v>
       </c>
       <c r="F1862" t="n">
-        <v>-1.242011317646504</v>
+        <v>-1.168829679370769</v>
       </c>
       <c r="G1862" t="n">
-        <v>2.372217670335179</v>
+        <v>2.41612665330062</v>
       </c>
     </row>
     <row r="1863">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-6.297475397627552</v>
+        <v>-6.224293759351816</v>
       </c>
       <c r="E1863" t="n">
-        <v>0.5973323925641445</v>
+        <v>0.6266050478744387</v>
       </c>
       <c r="F1863" t="n">
-        <v>-1.538322101945516</v>
+        <v>-1.465140463669781</v>
       </c>
       <c r="G1863" t="n">
-        <v>2.193685714761603</v>
+        <v>2.237594697727044</v>
       </c>
     </row>
     <row r="1864">
@@ -44423,16 +44423,16 @@
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-6.70606417480823</v>
+        <v>-6.632882536532495</v>
       </c>
       <c r="E1864" t="n">
-        <v>0.4326584257066326</v>
+        <v>0.4619310810169264</v>
       </c>
       <c r="F1864" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.87372924085046</v>
       </c>
       <c r="G1864" t="n">
-        <v>1.947293992467955</v>
+        <v>1.991202975433396</v>
       </c>
     </row>
     <row r="1865">
@@ -44446,16 +44446,16 @@
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-7.119046658949324</v>
+        <v>-7.045865020673589</v>
       </c>
       <c r="E1865" t="n">
-        <v>0.2626508645216554</v>
+        <v>0.2919235198319492</v>
       </c>
       <c r="F1865" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.87372924085046</v>
       </c>
       <c r="G1865" t="n">
-        <v>1.942479424939416</v>
+        <v>1.986388407904857</v>
       </c>
     </row>
     <row r="1866">
@@ -44469,16 +44469,16 @@
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-7.535438533236321</v>
+        <v>-7.462256894960587</v>
       </c>
       <c r="E1866" t="n">
-        <v>0.09408816541573373</v>
+        <v>0.1233608207260275</v>
       </c>
       <c r="F1866" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.87372924085046</v>
       </c>
       <c r="G1866" t="n">
-        <v>1.940473475548293</v>
+        <v>1.984382458513734</v>
       </c>
     </row>
     <row r="1867">
@@ -44492,16 +44492,16 @@
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-7.912115543766165</v>
+        <v>-7.838933905490431</v>
       </c>
       <c r="E1867" t="n">
-        <v>-0.04632394812752505</v>
+        <v>-0.01705129281723128</v>
       </c>
       <c r="F1867" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.87372924085046</v>
       </c>
       <c r="G1867" t="n">
-        <v>1.950732166216972</v>
+        <v>1.994641149182413</v>
       </c>
     </row>
     <row r="1868">
@@ -44515,16 +44515,16 @@
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-8.257990365750974</v>
+        <v>-8.184808727475239</v>
       </c>
       <c r="E1868" t="n">
-        <v>-0.1885743117757532</v>
+        <v>-0.1593016564654595</v>
       </c>
       <c r="F1868" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.87372924085046</v>
       </c>
       <c r="G1868" t="n">
-        <v>1.946831731362668</v>
+        <v>1.990740714328108</v>
       </c>
     </row>
     <row r="1869">
@@ -44538,16 +44538,16 @@
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-8.570815164995953</v>
+        <v>-8.497633526720218</v>
       </c>
       <c r="E1869" t="n">
-        <v>-0.3152993114187437</v>
+        <v>-0.2860266561084499</v>
       </c>
       <c r="F1869" t="n">
-        <v>-1.946910879126194</v>
+        <v>-1.87372924085046</v>
       </c>
       <c r="G1869" t="n">
-        <v>1.945236651417669</v>
+        <v>1.989145634383109</v>
       </c>
     </row>
     <row r="1870">
@@ -44561,16 +44561,16 @@
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-8.867476506806151</v>
+        <v>-8.794294868530416</v>
       </c>
       <c r="E1870" t="n">
-        <v>-0.4301848722136148</v>
+        <v>-0.400912216903321</v>
       </c>
       <c r="F1870" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.942472376584338</v>
       </c>
       <c r="G1870" t="n">
-        <v>1.907769745906549</v>
+        <v>1.951678728871991</v>
       </c>
     </row>
     <row r="1871">
@@ -44584,16 +44584,16 @@
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-9.300825614916386</v>
+        <v>-9.227643976640652</v>
       </c>
       <c r="E1871" t="n">
-        <v>-0.6075508199921118</v>
+        <v>-0.578278164681818</v>
       </c>
       <c r="F1871" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.942472376584338</v>
       </c>
       <c r="G1871" t="n">
-        <v>1.903743441372146</v>
+        <v>1.947652424337587</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-9.683827003659017</v>
+        <v>-9.610645365383283</v>
       </c>
       <c r="E1872" t="n">
-        <v>-0.7608534768107482</v>
+        <v>-0.7315808215004544</v>
       </c>
       <c r="F1872" t="n">
-        <v>-2.015654014860073</v>
+        <v>-1.942472376584338</v>
       </c>
       <c r="G1872" t="n">
-        <v>1.903641340050562</v>
+        <v>1.947550323016003</v>
       </c>
     </row>
     <row r="1873">
@@ -44630,16 +44630,16 @@
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-10.05881232983029</v>
+        <v>-9.98563069155456</v>
       </c>
       <c r="E1873" t="n">
-        <v>-0.9082760913078292</v>
+        <v>-0.8790034359975354</v>
       </c>
       <c r="F1873" t="n">
-        <v>-2.39063934103135</v>
+        <v>-2.317457702755616</v>
       </c>
       <c r="G1873" t="n">
-        <v>1.681221660319226</v>
+        <v>1.725130643284667</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-10.4183426523343</v>
+        <v>-10.34516101405856</v>
       </c>
       <c r="E1874" t="n">
-        <v>-1.04673791701138</v>
+        <v>-1.017465261701086</v>
       </c>
       <c r="F1874" t="n">
-        <v>-2.39063934103135</v>
+        <v>-2.317457702755616</v>
       </c>
       <c r="G1874" t="n">
-        <v>1.686571963617276</v>
+        <v>1.730480946582717</v>
       </c>
     </row>
     <row r="1875">
@@ -44676,16 +44676,16 @@
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-10.74474268099931</v>
+        <v>-10.67156104272357</v>
       </c>
       <c r="E1875" t="n">
-        <v>-1.169381908520208</v>
+        <v>-1.140109253209914</v>
       </c>
       <c r="F1875" t="n">
-        <v>-2.717039369696364</v>
+        <v>-2.643857731420629</v>
       </c>
       <c r="G1875" t="n">
-        <v>1.498647966375446</v>
+        <v>1.542556949340887</v>
       </c>
     </row>
     <row r="1876">
@@ -44699,16 +44699,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-10.96389164907351</v>
+        <v>-10.89071001079777</v>
       </c>
       <c r="E1876" t="n">
-        <v>-1.253999745128117</v>
+        <v>-1.224727089817824</v>
       </c>
       <c r="F1876" t="n">
-        <v>-2.936188337770561</v>
+        <v>-2.863006699494826</v>
       </c>
       <c r="G1876" t="n">
-        <v>1.370200336152696</v>
+        <v>1.414109319118137</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-10.9602007241171</v>
+        <v>-10.88701908584136</v>
       </c>
       <c r="E1877" t="n">
-        <v>-1.252523375145553</v>
+        <v>-1.22325071983526</v>
       </c>
       <c r="F1877" t="n">
-        <v>-2.936188337770561</v>
+        <v>-2.863006699494826</v>
       </c>
       <c r="G1877" t="n">
-        <v>1.370200336152696</v>
+        <v>1.414109319118137</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-11.16445889944696</v>
+        <v>-11.09127726117122</v>
       </c>
       <c r="E1878" t="n">
-        <v>-1.328713448158856</v>
+        <v>-1.299440792848563</v>
       </c>
       <c r="F1878" t="n">
-        <v>-3.06382728238455</v>
+        <v>-2.990645644108815</v>
       </c>
       <c r="G1878" t="n">
-        <v>1.299130166502945</v>
+        <v>1.343039149468386</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-11.38249667107814</v>
+        <v>-11.3093150328024</v>
       </c>
       <c r="E1879" t="n">
-        <v>-1.411446002326891</v>
+        <v>-1.382173347016597</v>
       </c>
       <c r="F1879" t="n">
-        <v>-3.238598050480449</v>
+        <v>-3.165416412204714</v>
       </c>
       <c r="G1879" t="n">
-        <v>1.198750260129842</v>
+        <v>1.242659243095283</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-11.30902683941069</v>
+        <v>-11.23584520113495</v>
       </c>
       <c r="E1880" t="n">
-        <v>-1.366686368166491</v>
+        <v>-1.337413712856197</v>
       </c>
       <c r="F1880" t="n">
-        <v>-3.165128218813</v>
+        <v>-3.091946580537265</v>
       </c>
       <c r="G1880" t="n">
-        <v>1.258203860623732</v>
+        <v>1.302112843589173</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-11.48415125679723</v>
+        <v>-11.4109696185215</v>
       </c>
       <c r="E1881" t="n">
-        <v>-1.422180914373591</v>
+        <v>-1.392908259063297</v>
       </c>
       <c r="F1881" t="n">
-        <v>-3.340252636199544</v>
+        <v>-3.267070997923809</v>
       </c>
       <c r="G1881" t="n">
-        <v>1.167684430939323</v>
+        <v>1.211593413904763</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-11.71860335081172</v>
+        <v>-11.64542171253599</v>
       </c>
       <c r="E1882" t="n">
-        <v>-1.523180916880983</v>
+        <v>-1.493908261570689</v>
       </c>
       <c r="F1882" t="n">
-        <v>-3.340252636199544</v>
+        <v>-3.267070997923809</v>
       </c>
       <c r="G1882" t="n">
-        <v>1.160465266037727</v>
+        <v>1.204374249003167</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-12.00640719534896</v>
+        <v>-11.93322555707323</v>
       </c>
       <c r="E1883" t="n">
-        <v>-1.644974645469854</v>
+        <v>-1.615701990159561</v>
       </c>
       <c r="F1883" t="n">
-        <v>-3.628056480736782</v>
+        <v>-3.554874842461047</v>
       </c>
       <c r="G1883" t="n">
-        <v>0.9811107685414076</v>
+        <v>1.025019751506849</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-12.23623164251278</v>
+        <v>-12.16305000423705</v>
       </c>
       <c r="E1884" t="n">
-        <v>-1.735788634496829</v>
+        <v>-1.706515979186535</v>
       </c>
       <c r="F1884" t="n">
-        <v>-3.790704017806943</v>
+        <v>-3.717522379531208</v>
       </c>
       <c r="G1884" t="n">
-        <v>0.8846380361378676</v>
+        <v>0.9285470191033083</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-12.46826056224905</v>
+        <v>-12.39507892397331</v>
       </c>
       <c r="E1885" t="n">
-        <v>-1.825906473762218</v>
+        <v>-1.796633818451924</v>
       </c>
       <c r="F1885" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.779535076719631</v>
       </c>
       <c r="G1885" t="n">
-        <v>0.8501241464539282</v>
+        <v>0.8940331294193693</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-12.41624504828023</v>
+        <v>-12.3430634100045</v>
       </c>
       <c r="E1886" t="n">
-        <v>-1.801109932488292</v>
+        <v>-1.771837277177998</v>
       </c>
       <c r="F1886" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.779535076719631</v>
       </c>
       <c r="G1886" t="n">
-        <v>0.854114482140329</v>
+        <v>0.8980234651057701</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-12.55791689000435</v>
+        <v>-12.48473525172862</v>
       </c>
       <c r="E1887" t="n">
-        <v>-1.859253896076682</v>
+        <v>-1.829981240766388</v>
       </c>
       <c r="F1887" t="n">
-        <v>-3.852716714995366</v>
+        <v>-3.779535076719631</v>
       </c>
       <c r="G1887" t="n">
-        <v>0.8526392552415873</v>
+        <v>0.8965482382070284</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-12.48969465407134</v>
+        <v>-12.58364199218789</v>
       </c>
       <c r="E1888" t="n">
-        <v>-1.816911591538603</v>
+        <v>-1.854490526785227</v>
       </c>
       <c r="F1888" t="n">
-        <v>-3.784494479062348</v>
+        <v>-3.878441817178907</v>
       </c>
       <c r="G1888" t="n">
-        <v>0.9086260069662706</v>
+        <v>0.8522576040963354</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-12.29054254683424</v>
+        <v>-12.3844898849508</v>
       </c>
       <c r="E1889" t="n">
-        <v>-1.750301882290446</v>
+        <v>-1.78788081753707</v>
       </c>
       <c r="F1889" t="n">
-        <v>-3.619171953112534</v>
+        <v>-3.713119291229094</v>
       </c>
       <c r="G1889" t="n">
-        <v>0.9947683888894758</v>
+        <v>0.9383999860195402</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-12.06469739411483</v>
+        <v>-12.15864473223138</v>
       </c>
       <c r="E1890" t="n">
-        <v>-1.650384748166474</v>
+        <v>-1.687963683413096</v>
       </c>
       <c r="F1890" t="n">
-        <v>-3.577245277525371</v>
+        <v>-3.67119261564193</v>
       </c>
       <c r="G1890" t="n">
-        <v>1.029503467277983</v>
+        <v>0.973135064408047</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-11.77842258179213</v>
+        <v>-11.87236991990869</v>
       </c>
       <c r="E1891" t="n">
-        <v>-1.534735678681337</v>
+        <v>-1.572314613927959</v>
       </c>
       <c r="F1891" t="n">
-        <v>-3.577245277525371</v>
+        <v>-3.67119261564193</v>
       </c>
       <c r="G1891" t="n">
-        <v>1.030642611834041</v>
+        <v>0.9742742089641059</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-11.83131786983642</v>
+        <v>-11.92526520795298</v>
       </c>
       <c r="E1892" t="n">
-        <v>-1.553260019736943</v>
+        <v>-1.590838954983567</v>
       </c>
       <c r="F1892" t="n">
-        <v>-3.572289931436925</v>
+        <v>-3.666237269553484</v>
       </c>
       <c r="G1892" t="n">
-        <v>1.036249593649217</v>
+        <v>0.9798811907792815</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-11.54740913890767</v>
+        <v>-11.64135647702423</v>
       </c>
       <c r="E1893" t="n">
-        <v>-1.433962823126808</v>
+        <v>-1.47154175837343</v>
       </c>
       <c r="F1893" t="n">
-        <v>-3.572289931436925</v>
+        <v>-3.666237269553484</v>
       </c>
       <c r="G1893" t="n">
-        <v>1.041983297887853</v>
+        <v>0.985614895017918</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-11.30042188871472</v>
+        <v>-11.39436922683127</v>
       </c>
       <c r="E1894" t="n">
-        <v>-1.344905185443492</v>
+        <v>-1.382484120690115</v>
       </c>
       <c r="F1894" t="n">
-        <v>-3.325302681243973</v>
+        <v>-3.419250019360532</v>
       </c>
       <c r="G1894" t="n">
-        <v>1.180438385609759</v>
+        <v>1.124069982739824</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-11.03658502151065</v>
+        <v>-11.1305323596272</v>
       </c>
       <c r="E1895" t="n">
-        <v>-1.249253919874772</v>
+        <v>-1.286832855121394</v>
       </c>
       <c r="F1895" t="n">
-        <v>-3.325302681243973</v>
+        <v>-3.419250019360532</v>
       </c>
       <c r="G1895" t="n">
-        <v>1.170554904296852</v>
+        <v>1.114186501426916</v>
       </c>
     </row>
     <row r="1896">
@@ -45159,16 +45159,16 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-10.76934322064225</v>
+        <v>-10.86329055875881</v>
       </c>
       <c r="E1896" t="n">
-        <v>-1.144191760026786</v>
+        <v>-1.181770695273409</v>
       </c>
       <c r="F1896" t="n">
-        <v>-3.325302681243973</v>
+        <v>-3.419250019360532</v>
       </c>
       <c r="G1896" t="n">
-        <v>1.168720343797478</v>
+        <v>1.112351940927542</v>
       </c>
     </row>
     <row r="1897">
@@ -45182,16 +45182,16 @@
         <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-10.49353405724177</v>
+        <v>-10.58748139535832</v>
       </c>
       <c r="E1897" t="n">
-        <v>-1.034168409640053</v>
+        <v>-1.071747344886676</v>
       </c>
       <c r="F1897" t="n">
-        <v>-3.236283372965239</v>
+        <v>-3.330230711081798</v>
       </c>
       <c r="G1897" t="n">
-        <v>1.221831613791257</v>
+        <v>1.165463210921322</v>
       </c>
     </row>
     <row r="1898">
@@ -45205,16 +45205,16 @@
         <v>3.164270143715894</v>
       </c>
       <c r="D1898" t="n">
-        <v>-10.46958051626581</v>
+        <v>-10.56352785438236</v>
       </c>
       <c r="E1898" t="n">
-        <v>-1.023918487104176</v>
+        <v>-1.061497422350799</v>
       </c>
       <c r="F1898" t="n">
-        <v>-3.212329831989281</v>
+        <v>-3.306277170105841</v>
       </c>
       <c r="G1898" t="n">
-        <v>1.236872244522325</v>
+        <v>1.18050384165239</v>
       </c>
     </row>
     <row r="1899">
@@ -45228,16 +45228,16 @@
         <v>3.151009827554142</v>
       </c>
       <c r="D1899" t="n">
-        <v>-10.20552057794301</v>
+        <v>-10.29946791605957</v>
       </c>
       <c r="E1899" t="n">
-        <v>-0.93155482793681</v>
+        <v>-0.9691337631834323</v>
       </c>
       <c r="F1899" t="n">
-        <v>-2.948269893666485</v>
+        <v>-3.042217231783045</v>
       </c>
       <c r="G1899" t="n">
-        <v>1.382047891354251</v>
+        <v>1.325679488484315</v>
       </c>
     </row>
     <row r="1900">
@@ -45251,16 +45251,16 @@
         <v>3.148222793893841</v>
       </c>
       <c r="D1900" t="n">
-        <v>-9.498440954438173</v>
+        <v>-9.59238829255473</v>
       </c>
       <c r="E1900" t="n">
-        <v>-0.6515100121951756</v>
+        <v>-0.6890889474417987</v>
       </c>
       <c r="F1900" t="n">
-        <v>-2.948269893666485</v>
+        <v>-3.042217231783045</v>
       </c>
       <c r="G1900" t="n">
-        <v>1.37926085769395</v>
+        <v>1.322892454824014</v>
       </c>
     </row>
     <row r="1901">
@@ -45274,16 +45274,16 @@
         <v>3.148566417781682</v>
       </c>
       <c r="D1901" t="n">
-        <v>-9.458256656071983</v>
+        <v>-9.55220399418854</v>
       </c>
       <c r="E1901" t="n">
-        <v>-0.635092668960858</v>
+        <v>-0.6726716042074812</v>
       </c>
       <c r="F1901" t="n">
-        <v>-2.908085595300294</v>
+        <v>-3.002032933416854</v>
       </c>
       <c r="G1901" t="n">
-        <v>1.403715060601506</v>
+        <v>1.34734665773157</v>
       </c>
     </row>
     <row r="1902">
@@ -45297,16 +45297,16 @@
         <v>3.147933239002439</v>
       </c>
       <c r="D1902" t="n">
-        <v>-9.378186860534178</v>
+        <v>-9.472134198650735</v>
       </c>
       <c r="E1902" t="n">
-        <v>-0.6036979295249796</v>
+        <v>-0.6412768647716023</v>
       </c>
       <c r="F1902" t="n">
-        <v>-2.82801579976249</v>
+        <v>-2.92196313787905</v>
       </c>
       <c r="G1902" t="n">
-        <v>1.451123759144946</v>
+        <v>1.39475535627501</v>
       </c>
     </row>
     <row r="1903">
@@ -45320,16 +45320,16 @@
         <v>3.155857667840292</v>
       </c>
       <c r="D1903" t="n">
-        <v>-9.144705638304579</v>
+        <v>-9.238652976421136</v>
       </c>
       <c r="E1903" t="n">
-        <v>-0.5023810117952872</v>
+        <v>-0.5399599470419103</v>
       </c>
       <c r="F1903" t="n">
-        <v>-2.594534577532892</v>
+        <v>-2.688481915649451</v>
       </c>
       <c r="G1903" t="n">
-        <v>1.599136921320557</v>
+        <v>1.542768518450621</v>
       </c>
     </row>
     <row r="1904">
@@ -45343,16 +45343,16 @@
         <v>3.152965457527332</v>
       </c>
       <c r="D1904" t="n">
-        <v>-8.964997108160706</v>
+        <v>-9.058944446277263</v>
       </c>
       <c r="E1904" t="n">
-        <v>-0.4333898100506972</v>
+        <v>-0.4709687452973199</v>
       </c>
       <c r="F1904" t="n">
-        <v>-2.537363073370196</v>
+        <v>-2.631310411486755</v>
       </c>
       <c r="G1904" t="n">
-        <v>1.630547613505215</v>
+        <v>1.57417921063528</v>
       </c>
     </row>
     <row r="1905">
@@ -45366,16 +45366,16 @@
         <v>3.14833294427436</v>
       </c>
       <c r="D1905" t="n">
-        <v>-8.832721634529818</v>
+        <v>-8.926668972646375</v>
       </c>
       <c r="E1905" t="n">
-        <v>-0.3851121338513153</v>
+        <v>-0.422691069097938</v>
       </c>
       <c r="F1905" t="n">
-        <v>-2.405087599739309</v>
+        <v>-2.499034937855869</v>
       </c>
       <c r="G1905" t="n">
-        <v>1.705280384430774</v>
+        <v>1.648911981560838</v>
       </c>
     </row>
     <row r="1906">
@@ -45389,16 +45389,16 @@
         <v>3.151148004961996</v>
       </c>
       <c r="D1906" t="n">
-        <v>-8.642121959856665</v>
+        <v>-8.736069297973222</v>
       </c>
       <c r="E1906" t="n">
-        <v>-0.3060572032944169</v>
+        <v>-0.34363613854104</v>
       </c>
       <c r="F1906" t="n">
-        <v>-2.214487925066157</v>
+        <v>-2.308435263182716</v>
       </c>
       <c r="G1906" t="n">
-        <v>1.822455249922303</v>
+        <v>1.766086847052367</v>
       </c>
     </row>
     <row r="1907">
@@ -45412,16 +45412,16 @@
         <v>3.164054346185655</v>
       </c>
       <c r="D1907" t="n">
-        <v>-8.393122161173084</v>
+        <v>-8.487069499289641</v>
       </c>
       <c r="E1907" t="n">
-        <v>-0.1935509425973261</v>
+        <v>-0.2311298778439488</v>
       </c>
       <c r="F1907" t="n">
-        <v>-2.214487925066157</v>
+        <v>-2.308435263182716</v>
       </c>
       <c r="G1907" t="n">
-        <v>1.835361591145961</v>
+        <v>1.778993188276025</v>
       </c>
     </row>
     <row r="1908">
@@ -45435,16 +45435,16 @@
         <v>3.036078416586436</v>
       </c>
       <c r="D1908" t="n">
-        <v>-8.498712150946188</v>
+        <v>-8.592659489062745</v>
       </c>
       <c r="E1908" t="n">
-        <v>-0.3637628681057863</v>
+        <v>-0.401341803352409</v>
       </c>
       <c r="F1908" t="n">
-        <v>-2.320077914839261</v>
+        <v>-2.414025252955821</v>
       </c>
       <c r="G1908" t="n">
-        <v>1.64403166768288</v>
+        <v>1.587663264812944</v>
       </c>
     </row>
     <row r="1909">
@@ -45458,16 +45458,16 @@
         <v>3.084622758463523</v>
       </c>
       <c r="D1909" t="n">
-        <v>-8.517447053064785</v>
+        <v>-8.611394391181342</v>
       </c>
       <c r="E1909" t="n">
-        <v>-0.3227124870761386</v>
+        <v>-0.3602914223227618</v>
       </c>
       <c r="F1909" t="n">
-        <v>-2.320077914839261</v>
+        <v>-2.414025252955821</v>
       </c>
       <c r="G1909" t="n">
-        <v>1.692576009559966</v>
+        <v>1.63620760669003</v>
       </c>
     </row>
     <row r="1910">
@@ -45481,16 +45481,16 @@
         <v>3.088001770449517</v>
       </c>
       <c r="D1910" t="n">
-        <v>-8.240708878393972</v>
+        <v>-8.334656216510529</v>
       </c>
       <c r="E1910" t="n">
-        <v>-0.2086382052218192</v>
+        <v>-0.2462171404684419</v>
       </c>
       <c r="F1910" t="n">
-        <v>-2.138261253729335</v>
+        <v>-2.232208591845895</v>
       </c>
       <c r="G1910" t="n">
-        <v>1.805045018211916</v>
+        <v>1.748676615341981</v>
       </c>
     </row>
     <row r="1911">
@@ -45504,16 +45504,16 @@
         <v>3.079287784196039</v>
       </c>
       <c r="D1911" t="n">
-        <v>-8.113816471958902</v>
+        <v>-8.207763810075459</v>
       </c>
       <c r="E1911" t="n">
-        <v>-0.1665952289012691</v>
+        <v>-0.2041741641478918</v>
       </c>
       <c r="F1911" t="n">
-        <v>-2.011368847294265</v>
+        <v>-2.105316185410825</v>
       </c>
       <c r="G1911" t="n">
-        <v>1.87246647581948</v>
+        <v>1.816098072949544</v>
       </c>
     </row>
     <row r="1912">
@@ -45527,16 +45527,16 @@
         <v>3.072327172100946</v>
       </c>
       <c r="D1912" t="n">
-        <v>-8.070268065188211</v>
+        <v>-8.164215403304768</v>
       </c>
       <c r="E1912" t="n">
-        <v>-0.1561364782880856</v>
+        <v>-0.1937154135347083</v>
       </c>
       <c r="F1912" t="n">
-        <v>-2.011368847294265</v>
+        <v>-2.105316185410825</v>
       </c>
       <c r="G1912" t="n">
-        <v>1.865505863724387</v>
+        <v>1.809137460854451</v>
       </c>
     </row>
     <row r="1913">
@@ -45550,16 +45550,16 @@
         <v>3.086789526482089</v>
       </c>
       <c r="D1913" t="n">
-        <v>-7.828119671734353</v>
+        <v>-7.92206700985091</v>
       </c>
       <c r="E1913" t="n">
-        <v>-0.04481476652539929</v>
+        <v>-0.08239370177202199</v>
       </c>
       <c r="F1913" t="n">
-        <v>-2.011368847294265</v>
+        <v>-2.105316185410825</v>
       </c>
       <c r="G1913" t="n">
-        <v>1.87996821810553</v>
+        <v>1.823599815235594</v>
       </c>
     </row>
     <row r="1914">
@@ -45573,16 +45573,16 @@
         <v>3.081321646941284</v>
       </c>
       <c r="D1914" t="n">
-        <v>-7.764890299966004</v>
+        <v>-7.858837638082561</v>
       </c>
       <c r="E1914" t="n">
-        <v>-0.02499089735886484</v>
+        <v>-0.06256983260548798</v>
       </c>
       <c r="F1914" t="n">
-        <v>-2.011368847294265</v>
+        <v>-2.105316185410825</v>
       </c>
       <c r="G1914" t="n">
-        <v>1.874500338564725</v>
+        <v>1.818131935694789</v>
       </c>
     </row>
     <row r="1915">
@@ -45596,16 +45596,16 @@
         <v>3.078819740951861</v>
       </c>
       <c r="D1915" t="n">
-        <v>-7.578402607588998</v>
+        <v>-7.672349945705555</v>
       </c>
       <c r="E1915" t="n">
-        <v>0.04710227360251418</v>
+        <v>0.009523338355891475</v>
       </c>
       <c r="F1915" t="n">
-        <v>-1.824881154917259</v>
+        <v>-1.918828493033819</v>
       </c>
       <c r="G1915" t="n">
-        <v>1.983891048001506</v>
+        <v>1.92752264513157</v>
       </c>
     </row>
     <row r="1916">
@@ -45619,16 +45619,16 @@
         <v>3.086520719189187</v>
       </c>
       <c r="D1916" t="n">
-        <v>-7.557253408685555</v>
+        <v>-7.651200746802112</v>
       </c>
       <c r="E1916" t="n">
-        <v>0.06326293140121741</v>
+        <v>0.02568399615459427</v>
       </c>
       <c r="F1916" t="n">
-        <v>-1.803731956013816</v>
+        <v>-1.897679294130376</v>
       </c>
       <c r="G1916" t="n">
-        <v>2.004281545580898</v>
+        <v>1.947913142710961</v>
       </c>
     </row>
     <row r="1917">
@@ -45642,16 +45642,16 @@
         <v>3.082301427536237</v>
       </c>
       <c r="D1917" t="n">
-        <v>-7.313487966702111</v>
+        <v>-7.407435304818668</v>
       </c>
       <c r="E1917" t="n">
-        <v>0.1565498165416455</v>
+        <v>0.1189708812950228</v>
       </c>
       <c r="F1917" t="n">
-        <v>-1.803731956013816</v>
+        <v>-1.897679294130376</v>
       </c>
       <c r="G1917" t="n">
-        <v>2.000062253927948</v>
+        <v>1.943693851058012</v>
       </c>
     </row>
     <row r="1918">
@@ -45665,16 +45665,16 @@
         <v>3.084425741456253</v>
       </c>
       <c r="D1918" t="n">
-        <v>-7.04945989950885</v>
+        <v>-7.143407237625407</v>
       </c>
       <c r="E1918" t="n">
-        <v>0.2642853573389656</v>
+        <v>0.2267064220923429</v>
       </c>
       <c r="F1918" t="n">
-        <v>-1.601866557197862</v>
+        <v>-1.695813895314422</v>
       </c>
       <c r="G1918" t="n">
-        <v>2.123305807137536</v>
+        <v>2.0669374042676</v>
       </c>
     </row>
     <row r="1919">
@@ -45688,16 +45688,16 @@
         <v>3.077167816439955</v>
       </c>
       <c r="D1919" t="n">
-        <v>-6.799609505559776</v>
+        <v>-7.003967629159499</v>
       </c>
       <c r="E1919" t="n">
-        <v>0.3569675899022977</v>
+        <v>0.2752243404624086</v>
       </c>
       <c r="F1919" t="n">
-        <v>-1.601866557197862</v>
+        <v>-1.695813895314422</v>
       </c>
       <c r="G1919" t="n">
-        <v>2.116047882121238</v>
+        <v>2.059679479251303</v>
       </c>
     </row>
     <row r="1920">
@@ -45711,16 +45711,16 @@
         <v>3.080766939960604</v>
       </c>
       <c r="D1920" t="n">
-        <v>-6.496042016555797</v>
+        <v>-6.70040014015552</v>
       </c>
       <c r="E1920" t="n">
-        <v>0.4819937090245379</v>
+        <v>0.4002504595846488</v>
       </c>
       <c r="F1920" t="n">
-        <v>-1.601866557197862</v>
+        <v>-1.695813895314422</v>
       </c>
       <c r="G1920" t="n">
-        <v>2.119647005641887</v>
+        <v>2.063278602771951</v>
       </c>
     </row>
     <row r="1921">
@@ -45734,16 +45734,16 @@
         <v>3.094094446015158</v>
       </c>
       <c r="D1921" t="n">
-        <v>-6.422562107703783</v>
+        <v>-6.626920231303506</v>
       </c>
       <c r="E1921" t="n">
-        <v>0.5247131786198973</v>
+        <v>0.4429699291800078</v>
       </c>
       <c r="F1921" t="n">
-        <v>-1.528386648345848</v>
+        <v>-1.622333986462408</v>
       </c>
       <c r="G1921" t="n">
-        <v>2.177062457007649</v>
+        <v>2.120694054137714</v>
       </c>
     </row>
     <row r="1922">
@@ -45757,16 +45757,16 @@
         <v>3.093114923631455</v>
       </c>
       <c r="D1922" t="n">
-        <v>-6.19752910803496</v>
+        <v>-6.401887231634683</v>
       </c>
       <c r="E1922" t="n">
-        <v>0.6137468561037234</v>
+        <v>0.5320036066638343</v>
       </c>
       <c r="F1922" t="n">
-        <v>-1.303353648677025</v>
+        <v>-1.397300986793585</v>
       </c>
       <c r="G1922" t="n">
-        <v>2.31110273442524</v>
+        <v>2.254734331555304</v>
       </c>
     </row>
     <row r="1923">
@@ -45780,16 +45780,16 @@
         <v>3.097809724685772</v>
       </c>
       <c r="D1923" t="n">
-        <v>-5.982894730398553</v>
+        <v>-6.187252853998277</v>
       </c>
       <c r="E1923" t="n">
-        <v>0.7042954082126034</v>
+        <v>0.6225521587727143</v>
       </c>
       <c r="F1923" t="n">
-        <v>-1.088719271040618</v>
+        <v>-1.182666609157178</v>
       </c>
       <c r="G1923" t="n">
-        <v>2.444578162061402</v>
+        <v>2.388209759191466</v>
       </c>
     </row>
     <row r="1924">
@@ -45803,16 +45803,16 @@
         <v>3.079003983469568</v>
       </c>
       <c r="D1924" t="n">
-        <v>-5.716294373424201</v>
+        <v>-5.920652497023925</v>
       </c>
       <c r="E1924" t="n">
-        <v>0.79212980978614</v>
+        <v>0.7103865603462505</v>
       </c>
       <c r="F1924" t="n">
-        <v>-1.088719271040618</v>
+        <v>-1.182666609157178</v>
       </c>
       <c r="G1924" t="n">
-        <v>2.425772420845197</v>
+        <v>2.369404017975262</v>
       </c>
     </row>
     <row r="1925">
@@ -45826,16 +45826,16 @@
         <v>3.080747060094445</v>
       </c>
       <c r="D1925" t="n">
-        <v>-5.475863876619341</v>
+        <v>-5.680222000219064</v>
       </c>
       <c r="E1925" t="n">
-        <v>0.8900450851329613</v>
+        <v>0.8083018356930722</v>
       </c>
       <c r="F1925" t="n">
-        <v>-0.8482887742357579</v>
+        <v>-0.9422361123523175</v>
       </c>
       <c r="G1925" t="n">
-        <v>2.571773795552991</v>
+        <v>2.515405392683055</v>
       </c>
     </row>
     <row r="1926">
@@ -45849,16 +45849,16 @@
         <v>3.084676373929265</v>
       </c>
       <c r="D1926" t="n">
-        <v>-5.233073068969896</v>
+        <v>-5.437431192569619</v>
       </c>
       <c r="E1926" t="n">
-        <v>0.9910907220275598</v>
+        <v>0.9093474725876702</v>
       </c>
       <c r="F1926" t="n">
-        <v>-0.8482887742357579</v>
+        <v>-0.9422361123523175</v>
       </c>
       <c r="G1926" t="n">
-        <v>2.575703109387811</v>
+        <v>2.519334706517875</v>
       </c>
     </row>
     <row r="1927">
@@ -45872,16 +45872,16 @@
         <v>3.085354957846605</v>
       </c>
       <c r="D1927" t="n">
-        <v>-4.993467977362807</v>
+        <v>-5.19782610096253</v>
       </c>
       <c r="E1927" t="n">
-        <v>1.087611342587735</v>
+        <v>1.005868093147846</v>
       </c>
       <c r="F1927" t="n">
-        <v>-0.7812408265672633</v>
+        <v>-0.875188164683823</v>
       </c>
       <c r="G1927" t="n">
-        <v>2.616610461906248</v>
+        <v>2.560242059036312</v>
       </c>
     </row>
     <row r="1928">
@@ -45895,16 +45895,16 @@
         <v>3.082353029066599</v>
       </c>
       <c r="D1928" t="n">
-        <v>-4.750812388939643</v>
+        <v>-4.955170512539366</v>
       </c>
       <c r="E1928" t="n">
-        <v>1.181671649176994</v>
+        <v>1.099928399737105</v>
       </c>
       <c r="F1928" t="n">
-        <v>-0.7812408265672633</v>
+        <v>-0.875188164683823</v>
       </c>
       <c r="G1928" t="n">
-        <v>2.613608533126241</v>
+        <v>2.557240130256305</v>
       </c>
     </row>
     <row r="1929">
@@ -45918,16 +45918,16 @@
         <v>3.083932066077213</v>
       </c>
       <c r="D1929" t="n">
-        <v>-4.530791590902632</v>
+        <v>-4.735149714502356</v>
       </c>
       <c r="E1929" t="n">
-        <v>1.271259005402413</v>
+        <v>1.189515755962523</v>
       </c>
       <c r="F1929" t="n">
-        <v>-0.6400209814992831</v>
+        <v>-0.7339683196158427</v>
       </c>
       <c r="G1929" t="n">
-        <v>2.699919477177644</v>
+        <v>2.643551074307708</v>
       </c>
     </row>
     <row r="1930">
@@ -45941,16 +45941,16 @@
         <v>3.099826248879036</v>
       </c>
       <c r="D1930" t="n">
-        <v>-4.331542960997823</v>
+        <v>-4.535901084597547</v>
       </c>
       <c r="E1930" t="n">
-        <v>1.36685264016616</v>
+        <v>1.28510939072627</v>
       </c>
       <c r="F1930" t="n">
-        <v>-0.6400209814992831</v>
+        <v>-0.7339683196158427</v>
       </c>
       <c r="G1930" t="n">
-        <v>2.715813659979466</v>
+        <v>2.659445257109531</v>
       </c>
     </row>
     <row r="1931">
@@ -45964,16 +45964,16 @@
         <v>3.100972093319338</v>
       </c>
       <c r="D1931" t="n">
-        <v>-4.172027857478454</v>
+        <v>-4.376385981078177</v>
       </c>
       <c r="E1931" t="n">
-        <v>1.431804526014209</v>
+        <v>1.35006127657432</v>
       </c>
       <c r="F1931" t="n">
-        <v>-0.4805058779799132</v>
+        <v>-0.5744532160964728</v>
       </c>
       <c r="G1931" t="n">
-        <v>2.812668566531391</v>
+        <v>2.756300163661455</v>
       </c>
     </row>
     <row r="1932">
@@ -45987,16 +45987,16 @@
         <v>3.111060195880778</v>
       </c>
       <c r="D1932" t="n">
-        <v>-4.027355712378716</v>
+        <v>-4.231713835978439</v>
       </c>
       <c r="E1932" t="n">
-        <v>1.499761486615544</v>
+        <v>1.418018237175655</v>
       </c>
       <c r="F1932" t="n">
-        <v>-0.3358337328801758</v>
+        <v>-0.4297810709967354</v>
       </c>
       <c r="G1932" t="n">
-        <v>2.909559956152673</v>
+        <v>2.853191553282737</v>
       </c>
     </row>
     <row r="1933">
@@ -46010,16 +46010,16 @@
         <v>3.0263998879675</v>
       </c>
       <c r="D1933" t="n">
-        <v>-4.00958625344776</v>
+        <v>-4.213944377047484</v>
       </c>
       <c r="E1933" t="n">
-        <v>1.422208962274648</v>
+        <v>1.340465712834759</v>
       </c>
       <c r="F1933" t="n">
-        <v>-0.3180642739492202</v>
+        <v>-0.4120116120657799</v>
       </c>
       <c r="G1933" t="n">
-        <v>2.835561323597968</v>
+        <v>2.779192920728032</v>
       </c>
     </row>
     <row r="1934">
@@ -46033,16 +46033,16 @@
         <v>3.048800381290066</v>
       </c>
       <c r="D1934" t="n">
-        <v>-3.922786755668751</v>
+        <v>-4.127144879268474</v>
       </c>
       <c r="E1934" t="n">
-        <v>1.479329254708818</v>
+        <v>1.397586005268929</v>
       </c>
       <c r="F1934" t="n">
-        <v>-0.3180642739492202</v>
+        <v>-0.4120116120657799</v>
       </c>
       <c r="G1934" t="n">
-        <v>2.857961816920534</v>
+        <v>2.801593414050598</v>
       </c>
     </row>
     <row r="1935">
@@ -46056,16 +46056,16 @@
         <v>3.048872782663478</v>
       </c>
       <c r="D1935" t="n">
-        <v>-3.82309414093974</v>
+        <v>-4.027452264539463</v>
       </c>
       <c r="E1935" t="n">
-        <v>1.519278701973835</v>
+        <v>1.437535452533945</v>
       </c>
       <c r="F1935" t="n">
-        <v>-0.2183716592202085</v>
+        <v>-0.3123189973367681</v>
       </c>
       <c r="G1935" t="n">
-        <v>2.917849787131353</v>
+        <v>2.861481384261417</v>
       </c>
     </row>
     <row r="1936">
@@ -46073,22 +46073,22 @@
         <v>45398</v>
       </c>
       <c r="B1936" t="n">
-        <v>3.838656292625575</v>
+        <v>3.720821296755444</v>
       </c>
       <c r="C1936" t="n">
-        <v>3.05987970513818</v>
+        <v>2.924306271643955</v>
       </c>
       <c r="D1936" t="n">
-        <v>-4.007146951381117</v>
+        <v>-4.097058462054222</v>
       </c>
       <c r="E1936" t="n">
-        <v>1.456664500271986</v>
+        <v>1.285126462508519</v>
       </c>
       <c r="F1936" t="n">
-        <v>-0.266831249322602</v>
+        <v>-0.3025819880801974</v>
       </c>
       <c r="G1936" t="n">
-        <v>2.899780955544619</v>
+        <v>2.742757078795837</v>
       </c>
     </row>
   </sheetData>
